--- a/CVT-MES项目资料/04_墨西哥CVT线现场实施计划_V2.xlsx
+++ b/CVT-MES项目资料/04_墨西哥CVT线现场实施计划_V2.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'甘特（周）'!$1:$2</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">硬件清单!$1:$2</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">计划!$1:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">计划!$A$4:$L$53</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">计划!$A$4:$L$52</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="840" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="448">
   <si>
     <r>
       <rPr>
@@ -704,31 +704,16 @@
   <si>
     <r>
       <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">安装</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Windows Server 2016</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，激活、打补丁，设置主机名、固定</t>
-    </r>
-    <r>
-      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服务器系统与数据库复核（国内已安装）：核对主机名、固定</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
         <sz val="9"/>
         <rFont val="微软雅黑"/>
         <family val="0"/>
@@ -738,85 +723,67 @@
     </r>
     <r>
       <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、防火墙、远程桌面</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">系统安装记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">服务器硬件自检正常，安装介质可用</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">安装</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SQL Server 2019/2016</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">及以上，配置实例、账号、端口、备份策略</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">数据库配置记录</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Windows Server</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">安装完成</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">协议约定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MS SQL Server 2019</t>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、防火墙、远程桌面、实例、账号、端口、备份策略；异常时按镜像或配置基线恢复</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">系统与数据库复核记录</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务器硬件自检正常；国内已完成系统与数据库安装，具备镜像或配置基线</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★国内已调过一轮，原“装</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Windows Server”“</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">装</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SQL Server”</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">两条合并为复核；若硬件变更再重新安装</t>
     </r>
   </si>
   <si>
@@ -3334,7 +3301,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">安装</t>
+      <t xml:space="preserve">服务器系统与数据库复核（国内已安装）：核对主机名、固定</t>
     </r>
     <r>
       <rPr>
@@ -3343,7 +3310,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Windows Server 2016</t>
+      <t xml:space="preserve">IP</t>
     </r>
     <r>
       <rPr>
@@ -3351,51 +3318,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">，激活、打补丁，设置主机名、固定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、防火墙、远程桌面</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">安装</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SQL Server 2019/2016</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">及以上，配置实例、账号、端口、备份策略</t>
+      <t xml:space="preserve">、防火墙、远程桌面、实例、账号、端口、备份策略；异常时按镜像或配置基线恢复</t>
     </r>
   </si>
   <si>
@@ -6804,6 +6727,94 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">秒、并发、故障恢复、数据不丢失的测试记录要求</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">“安装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Windows Server 2016”“</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">安装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SQL Server”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">拆为两条独立任务</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">国内已完成一轮调试：合并为“服务器系统与数据库复核”</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天，保留镜像</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置基线恢复兜底；仅硬件变更时才重新安装</t>
     </r>
   </si>
   <si>
@@ -7545,10 +7556,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7562,14 +7569,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7591,6 +7590,18 @@
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -8118,7 +8129,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -8221,7 +8232,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -8264,7 +8275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
         <v>23</v>
       </c>
@@ -8307,7 +8318,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="9" t="n">
         <v>3</v>
@@ -8348,222 +8359,222 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
-      <c r="B8" s="14" t="n">
+      <c r="B8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="17" t="n">
         <f aca="false">说明与修订!$B$5+M8</f>
         <v>46333</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="17" t="n">
         <f aca="false">F8+E8-1</f>
         <v>46333</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="I8" s="14" t="s">
+      <c r="I8" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="J8" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="L8" s="12"/>
+      <c r="L8" s="16" t="s">
+        <v>40</v>
+      </c>
       <c r="M8" s="0" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="9" t="n">
         <v>5</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E9" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M9</f>
-        <v>46334</v>
+        <v>46332</v>
       </c>
       <c r="G9" s="8" t="n">
         <f aca="false">F9+E9-1</f>
-        <v>46334</v>
+        <v>46333</v>
       </c>
       <c r="H9" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="15" t="s">
-        <v>42</v>
+      <c r="K9" s="7" t="s">
+        <v>44</v>
       </c>
       <c r="L9" s="7" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M9" s="0" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="14" t="n">
         <v>6</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>47</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M10</f>
-        <v>46332</v>
+        <v>46334</v>
       </c>
       <c r="G10" s="13" t="n">
         <f aca="false">F10+E10-1</f>
-        <v>46333</v>
+        <v>46337</v>
       </c>
       <c r="H10" s="12" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>28</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L10" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M10" s="0" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="8" t="n">
+      <c r="C11" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="22" t="n">
         <f aca="false">说明与修订!$B$5+M11</f>
-        <v>46334</v>
-      </c>
-      <c r="G11" s="8" t="n">
+        <v>46336</v>
+      </c>
+      <c r="G11" s="22" t="n">
         <f aca="false">F11+E11-1</f>
-        <v>46337</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="L11" s="7" t="s">
+        <v>46338</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="23" t="s">
         <v>53</v>
       </c>
+      <c r="J11" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="L11" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="M11" s="0" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
-      <c r="B12" s="16" t="n">
+      <c r="B12" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="C12" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="18" t="n">
+      <c r="C12" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M12</f>
-        <v>46336</v>
-      </c>
-      <c r="G12" s="18" t="n">
+        <v>46338</v>
+      </c>
+      <c r="G12" s="13" t="n">
         <f aca="false">F12+E12-1</f>
         <v>46338</v>
       </c>
-      <c r="H12" s="17" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="J12" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="L12" s="17" t="s">
+      <c r="H12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="14" t="s">
         <v>58</v>
       </c>
+      <c r="J12" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="L12" s="12"/>
       <c r="M12" s="0" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="9" t="n">
         <v>9</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E13" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M13</f>
@@ -8571,109 +8582,109 @@
       </c>
       <c r="G13" s="8" t="n">
         <f aca="false">F13+E13-1</f>
-        <v>46338</v>
+        <v>46339</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I13" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="J13" s="9" t="s">
-        <v>28</v>
+        <v>62</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>20</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="L13" s="7"/>
+        <v>63</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="M13" s="0" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="14" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="F14" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M14</f>
-        <v>46338</v>
+        <v>46333</v>
       </c>
       <c r="G14" s="13" t="n">
         <f aca="false">F14+E14-1</f>
-        <v>46339</v>
+        <v>46334</v>
       </c>
       <c r="H14" s="12" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>65</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>20</v>
+        <v>58</v>
+      </c>
+      <c r="J14" s="14" t="s">
+        <v>28</v>
       </c>
       <c r="K14" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="L14" s="12" t="s">
         <v>67</v>
       </c>
+      <c r="L14" s="12"/>
       <c r="M14" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="25" t="s">
+        <v>68</v>
+      </c>
       <c r="B15" s="9" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E15" s="9" t="n">
         <v>2</v>
       </c>
       <c r="F15" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M15</f>
-        <v>46333</v>
+        <v>46340</v>
       </c>
       <c r="G15" s="8" t="n">
         <f aca="false">F15+E15-1</f>
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="L15" s="7"/>
       <c r="M15" s="0" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
-        <v>71</v>
-      </c>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="25"/>
       <c r="B16" s="14" t="n">
         <v>12</v>
       </c>
@@ -8706,32 +8717,34 @@
       <c r="K16" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="L16" s="12"/>
+      <c r="L16" s="12" t="s">
+        <v>75</v>
+      </c>
       <c r="M16" s="0" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21"/>
+      <c r="A17" s="25"/>
       <c r="B17" s="9" t="n">
         <v>13</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E17" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F17" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M17</f>
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="G17" s="8" t="n">
         <f aca="false">F17+E17-1</f>
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="H17" s="7" t="s">
         <v>33</v>
@@ -8742,26 +8755,26 @@
       <c r="J17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K17" s="7" t="s">
-        <v>77</v>
+      <c r="K17" s="26" t="s">
+        <v>78</v>
       </c>
       <c r="L17" s="7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="M17" s="0" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25"/>
       <c r="B18" s="14" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E18" s="14" t="n">
         <v>1</v>
@@ -8783,18 +8796,16 @@
       <c r="J18" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K18" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="L18" s="12" t="s">
+      <c r="K18" s="12" t="s">
         <v>82</v>
       </c>
+      <c r="L18" s="12"/>
       <c r="M18" s="0" t="n">
         <v>14</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21"/>
+    <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25"/>
       <c r="B19" s="9" t="n">
         <v>15</v>
       </c>
@@ -8809,11 +8820,11 @@
       </c>
       <c r="F19" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M19</f>
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="G19" s="8" t="n">
         <f aca="false">F19+E19-1</f>
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>33</v>
@@ -8829,11 +8840,11 @@
       </c>
       <c r="L19" s="7"/>
       <c r="M19" s="0" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25"/>
       <c r="B20" s="14" t="n">
         <v>16</v>
       </c>
@@ -8848,11 +8859,11 @@
       </c>
       <c r="F20" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M20</f>
-        <v>46343</v>
+        <v>46344</v>
       </c>
       <c r="G20" s="13" t="n">
         <f aca="false">F20+E20-1</f>
-        <v>46343</v>
+        <v>46344</v>
       </c>
       <c r="H20" s="12" t="s">
         <v>33</v>
@@ -8868,11 +8879,11 @@
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="0" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21"/>
+      <c r="A21" s="25"/>
       <c r="B21" s="9" t="n">
         <v>17</v>
       </c>
@@ -8910,8 +8921,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21"/>
+    <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="25"/>
       <c r="B22" s="14" t="n">
         <v>18</v>
       </c>
@@ -8926,11 +8937,11 @@
       </c>
       <c r="F22" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M22</f>
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="G22" s="13" t="n">
         <f aca="false">F22+E22-1</f>
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="H22" s="12" t="s">
         <v>33</v>
@@ -8946,18 +8957,18 @@
       </c>
       <c r="L22" s="12"/>
       <c r="M22" s="0" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="25"/>
       <c r="B23" s="9" t="n">
         <v>19</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="D23" s="26" t="s">
         <v>96</v>
       </c>
       <c r="E23" s="9" t="n">
@@ -8965,11 +8976,11 @@
       </c>
       <c r="F23" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M23</f>
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="G23" s="8" t="n">
         <f aca="false">F23+E23-1</f>
-        <v>46345</v>
+        <v>46346</v>
       </c>
       <c r="H23" s="7" t="s">
         <v>33</v>
@@ -8980,23 +8991,23 @@
       <c r="J23" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="K23" s="7" t="s">
+      <c r="K23" s="26" t="s">
         <v>97</v>
       </c>
       <c r="L23" s="7"/>
       <c r="M23" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25"/>
       <c r="B24" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C24" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="12" t="s">
         <v>99</v>
       </c>
       <c r="E24" s="14" t="n">
@@ -9019,35 +9030,37 @@
       <c r="J24" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K24" s="22" t="s">
+      <c r="K24" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="L24" s="12"/>
+      <c r="L24" s="19" t="s">
+        <v>101</v>
+      </c>
       <c r="M24" s="0" t="n">
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21"/>
+    <row r="25" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="25"/>
       <c r="B25" s="9" t="n">
         <v>21</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E25" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M25</f>
-        <v>46346</v>
+        <v>46347</v>
       </c>
       <c r="G25" s="8" t="n">
         <f aca="false">F25+E25-1</f>
-        <v>46346</v>
+        <v>46348</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>33</v>
@@ -9059,28 +9072,28 @@
         <v>28</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="L25" s="15" t="s">
         <v>104</v>
       </c>
+      <c r="L25" s="7" t="s">
+        <v>105</v>
+      </c>
       <c r="M25" s="0" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21"/>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25"/>
       <c r="B26" s="14" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E26" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F26" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M26</f>
@@ -9088,7 +9101,7 @@
       </c>
       <c r="G26" s="13" t="n">
         <f aca="false">F26+E26-1</f>
-        <v>46348</v>
+        <v>46347</v>
       </c>
       <c r="H26" s="12" t="s">
         <v>33</v>
@@ -9100,17 +9113,15 @@
         <v>28</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="L26" s="12" t="s">
         <v>108</v>
       </c>
+      <c r="L26" s="12"/>
       <c r="M26" s="0" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21"/>
+    <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25"/>
       <c r="B27" s="9" t="n">
         <v>23</v>
       </c>
@@ -9125,11 +9136,11 @@
       </c>
       <c r="F27" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M27</f>
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="G27" s="8" t="n">
         <f aca="false">F27+E27-1</f>
-        <v>46347</v>
+        <v>46348</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>33</v>
@@ -9145,11 +9156,11 @@
       </c>
       <c r="L27" s="7"/>
       <c r="M27" s="0" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25"/>
       <c r="B28" s="14" t="n">
         <v>24</v>
       </c>
@@ -9164,11 +9175,11 @@
       </c>
       <c r="F28" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M28</f>
-        <v>46348</v>
+        <v>46349</v>
       </c>
       <c r="G28" s="13" t="n">
         <f aca="false">F28+E28-1</f>
-        <v>46348</v>
+        <v>46349</v>
       </c>
       <c r="H28" s="12" t="s">
         <v>33</v>
@@ -9182,32 +9193,36 @@
       <c r="K28" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="L28" s="12"/>
+      <c r="L28" s="12" t="s">
+        <v>115</v>
+      </c>
       <c r="M28" s="0" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21"/>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="5" t="s">
+        <v>116</v>
+      </c>
       <c r="B29" s="9" t="n">
         <v>25</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E29" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M29</f>
-        <v>46349</v>
+        <v>46350</v>
       </c>
       <c r="G29" s="8" t="n">
         <f aca="false">F29+E29-1</f>
-        <v>46349</v>
+        <v>46350</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>33</v>
@@ -9219,19 +9234,15 @@
         <v>28</v>
       </c>
       <c r="K29" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>118</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="L29" s="7"/>
       <c r="M29" s="0" t="n">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="5" t="s">
-        <v>119</v>
-      </c>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5"/>
       <c r="B30" s="14" t="n">
         <v>26</v>
       </c>
@@ -9242,15 +9253,15 @@
         <v>121</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M30</f>
-        <v>46350</v>
+        <v>46351</v>
       </c>
       <c r="G30" s="13" t="n">
         <f aca="false">F30+E30-1</f>
-        <v>46350</v>
+        <v>46352</v>
       </c>
       <c r="H30" s="12" t="s">
         <v>33</v>
@@ -9264,24 +9275,26 @@
       <c r="K30" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="L30" s="12"/>
+      <c r="L30" s="12" t="s">
+        <v>123</v>
+      </c>
       <c r="M30" s="0" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="9" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E31" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M31</f>
@@ -9289,28 +9302,26 @@
       </c>
       <c r="G31" s="8" t="n">
         <f aca="false">F31+E31-1</f>
-        <v>46352</v>
+        <v>46351</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K31" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="L31" s="7" t="s">
         <v>126</v>
       </c>
+      <c r="L31" s="7"/>
       <c r="M31" s="0" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
       <c r="B32" s="14" t="n">
         <v>28</v>
@@ -9326,17 +9337,17 @@
       </c>
       <c r="F32" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M32</f>
-        <v>46351</v>
+        <v>46352</v>
       </c>
       <c r="G32" s="13" t="n">
         <f aca="false">F32+E32-1</f>
-        <v>46351</v>
+        <v>46352</v>
       </c>
       <c r="H32" s="12" t="s">
         <v>33</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J32" s="14" t="s">
         <v>28</v>
@@ -9344,32 +9355,34 @@
       <c r="K32" s="12" t="s">
         <v>129</v>
       </c>
-      <c r="L32" s="12"/>
+      <c r="L32" s="12" t="s">
+        <v>130</v>
+      </c>
       <c r="M32" s="0" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
       <c r="B33" s="9" t="n">
         <v>29</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E33" s="9" t="n">
         <v>1</v>
       </c>
       <c r="F33" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M33</f>
-        <v>46352</v>
+        <v>46353</v>
       </c>
       <c r="G33" s="8" t="n">
         <f aca="false">F33+E33-1</f>
-        <v>46352</v>
+        <v>46353</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>33</v>
@@ -9381,16 +9394,14 @@
         <v>28</v>
       </c>
       <c r="K33" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="L33" s="7" t="s">
         <v>133</v>
       </c>
+      <c r="L33" s="7"/>
       <c r="M33" s="0" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
       <c r="B34" s="14" t="n">
         <v>30</v>
@@ -9406,11 +9417,11 @@
       </c>
       <c r="F34" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M34</f>
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="G34" s="13" t="n">
         <f aca="false">F34+E34-1</f>
-        <v>46353</v>
+        <v>46354</v>
       </c>
       <c r="H34" s="12" t="s">
         <v>33</v>
@@ -9424,94 +9435,94 @@
       <c r="K34" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="L34" s="12"/>
+      <c r="L34" s="19" t="s">
+        <v>137</v>
+      </c>
       <c r="M34" s="0" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
-      <c r="B35" s="9" t="n">
+      <c r="B35" s="23" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="D35" s="7" t="s">
+      <c r="C35" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="E35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="8" t="n">
+      <c r="D35" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="E35" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="22" t="n">
         <f aca="false">说明与修订!$B$5+M35</f>
         <v>46354</v>
       </c>
-      <c r="G35" s="8" t="n">
+      <c r="G35" s="22" t="n">
         <f aca="false">F35+E35-1</f>
-        <v>46354</v>
-      </c>
-      <c r="H35" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J35" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K35" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="L35" s="15" t="s">
+        <v>46355</v>
+      </c>
+      <c r="H35" s="21" t="s">
         <v>140</v>
+      </c>
+      <c r="I35" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="J35" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="L35" s="21" t="s">
+        <v>143</v>
       </c>
       <c r="M35" s="0" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
-      <c r="B36" s="19" t="n">
+      <c r="B36" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="C36" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="D36" s="17" t="s">
-        <v>142</v>
-      </c>
-      <c r="E36" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F36" s="18" t="n">
+      <c r="C36" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M36</f>
-        <v>46354</v>
-      </c>
-      <c r="G36" s="18" t="n">
+        <v>46355</v>
+      </c>
+      <c r="G36" s="13" t="n">
         <f aca="false">F36+E36-1</f>
         <v>46355</v>
       </c>
-      <c r="H36" s="17" t="s">
-        <v>143</v>
-      </c>
-      <c r="I36" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="J36" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="L36" s="17" t="s">
+      <c r="H36" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I36" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="K36" s="12" t="s">
         <v>146</v>
       </c>
+      <c r="L36" s="12"/>
       <c r="M36" s="0" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
       <c r="B37" s="9" t="n">
         <v>33</v>
@@ -9527,11 +9538,11 @@
       </c>
       <c r="F37" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M37</f>
-        <v>46355</v>
+        <v>46356</v>
       </c>
       <c r="G37" s="8" t="n">
         <f aca="false">F37+E37-1</f>
-        <v>46355</v>
+        <v>46356</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>33</v>
@@ -9547,10 +9558,10 @@
       </c>
       <c r="L37" s="7"/>
       <c r="M37" s="0" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
       <c r="B38" s="14" t="n">
         <v>34</v>
@@ -9589,7 +9600,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
       <c r="B39" s="9" t="n">
         <v>35</v>
@@ -9605,11 +9616,11 @@
       </c>
       <c r="F39" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M39</f>
-        <v>46356</v>
+        <v>46357</v>
       </c>
       <c r="G39" s="8" t="n">
         <f aca="false">F39+E39-1</f>
-        <v>46356</v>
+        <v>46357</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>33</v>
@@ -9623,71 +9634,71 @@
       <c r="K39" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="L39" s="7"/>
+      <c r="L39" s="7" t="s">
+        <v>156</v>
+      </c>
       <c r="M39" s="0" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="5"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="5" t="s">
+        <v>157</v>
+      </c>
       <c r="B40" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>157</v>
+      <c r="C40" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>159</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F40" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M40</f>
-        <v>46357</v>
+        <v>46358</v>
       </c>
       <c r="G40" s="13" t="n">
         <f aca="false">F40+E40-1</f>
-        <v>46357</v>
+        <v>46359</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>33</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="J40" s="14" t="s">
         <v>28</v>
       </c>
       <c r="K40" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L40" s="12" t="s">
-        <v>159</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="L40" s="12"/>
       <c r="M40" s="0" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5" t="s">
-        <v>160</v>
-      </c>
+      <c r="A41" s="5"/>
       <c r="B41" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="7" t="s">
         <v>162</v>
       </c>
       <c r="E41" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F41" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M41</f>
-        <v>46358</v>
+        <v>46359</v>
       </c>
       <c r="G41" s="8" t="n">
         <f aca="false">F41+E41-1</f>
@@ -9705,35 +9716,37 @@
       <c r="K41" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="L41" s="7"/>
+      <c r="L41" s="7" t="s">
+        <v>164</v>
+      </c>
       <c r="M41" s="0" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
       <c r="B42" s="14" t="n">
         <v>38</v>
       </c>
-      <c r="C42" s="22" t="s">
-        <v>164</v>
+      <c r="C42" s="12" t="s">
+        <v>165</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E42" s="14" t="n">
         <v>1</v>
       </c>
       <c r="F42" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M42</f>
-        <v>46359</v>
+        <v>46360</v>
       </c>
       <c r="G42" s="13" t="n">
         <f aca="false">F42+E42-1</f>
-        <v>46359</v>
+        <v>46360</v>
       </c>
       <c r="H42" s="12" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I42" s="14" t="s">
         <v>19</v>
@@ -9742,96 +9755,94 @@
         <v>28</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="L42" s="12" t="s">
         <v>167</v>
       </c>
+      <c r="L42" s="12"/>
       <c r="M42" s="0" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
-      <c r="B43" s="9" t="n">
+      <c r="B43" s="23" t="n">
         <v>39</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="7" t="s">
+      <c r="D43" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="E43" s="9" t="n">
+      <c r="E43" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="22" t="n">
+        <f aca="false">说明与修订!$B$5+M43</f>
+        <v>46361</v>
+      </c>
+      <c r="G43" s="22" t="n">
+        <f aca="false">F43+E43-1</f>
+        <v>46362</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="J43" s="23" t="s">
+        <v>28</v>
+      </c>
+      <c r="K43" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="L43" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="M43" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="5"/>
+      <c r="B44" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="E44" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M43</f>
-        <v>46360</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <f aca="false">F43+E43-1</f>
-        <v>46360</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J43" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K43" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="L43" s="7"/>
-      <c r="M43" s="0" t="n">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
-      <c r="B44" s="19" t="n">
-        <v>40</v>
-      </c>
-      <c r="C44" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="D44" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="E44" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="F44" s="18" t="n">
+      <c r="F44" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M44</f>
         <v>46361</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="G44" s="13" t="n">
         <f aca="false">F44+E44-1</f>
-        <v>46362</v>
-      </c>
-      <c r="H44" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I44" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="J44" s="19" t="s">
+        <v>46361</v>
+      </c>
+      <c r="H44" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="J44" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K44" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="L44" s="17" t="s">
+      <c r="K44" s="12" t="s">
         <v>174</v>
       </c>
+      <c r="L44" s="12"/>
       <c r="M44" s="0" t="n">
         <v>33</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
       <c r="B45" s="9" t="n">
         <v>41</v>
@@ -9847,11 +9858,11 @@
       </c>
       <c r="F45" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M45</f>
-        <v>46361</v>
+        <v>46363</v>
       </c>
       <c r="G45" s="8" t="n">
         <f aca="false">F45+E45-1</f>
-        <v>46361</v>
+        <v>46363</v>
       </c>
       <c r="H45" s="7" t="s">
         <v>33</v>
@@ -9867,184 +9878,186 @@
       </c>
       <c r="L45" s="7"/>
       <c r="M45" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
-      <c r="B46" s="14" t="n">
+      <c r="B46" s="18" t="n">
         <v>42</v>
       </c>
-      <c r="C46" s="12" t="s">
+      <c r="C46" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="16" t="s">
         <v>179</v>
       </c>
-      <c r="E46" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="13" t="n">
+      <c r="E46" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="17" t="n">
         <f aca="false">说明与修订!$B$5+M46</f>
         <v>46363</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="G46" s="17" t="n">
         <f aca="false">F46+E46-1</f>
-        <v>46363</v>
-      </c>
-      <c r="H46" s="12" t="s">
+        <v>46364</v>
+      </c>
+      <c r="H46" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="I46" s="14" t="s">
+      <c r="I46" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J46" s="14" t="s">
+      <c r="J46" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="K46" s="12" t="s">
+      <c r="K46" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="L46" s="12"/>
+      <c r="L46" s="16" t="s">
+        <v>181</v>
+      </c>
       <c r="M46" s="0" t="n">
         <v>35</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
       <c r="B47" s="23" t="n">
         <v>43</v>
       </c>
-      <c r="C47" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="D47" s="24" t="s">
+      <c r="C47" s="21" t="s">
         <v>182</v>
       </c>
+      <c r="D47" s="21" t="s">
+        <v>183</v>
+      </c>
       <c r="E47" s="23" t="n">
-        <v>2</v>
-      </c>
-      <c r="F47" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="22" t="n">
         <f aca="false">说明与修订!$B$5+M47</f>
-        <v>46363</v>
-      </c>
-      <c r="G47" s="25" t="n">
+        <v>46364</v>
+      </c>
+      <c r="G47" s="22" t="n">
         <f aca="false">F47+E47-1</f>
         <v>46364</v>
       </c>
-      <c r="H47" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="I47" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="J47" s="26" t="s">
+      <c r="H47" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="I47" s="23" t="s">
+        <v>19</v>
+      </c>
+      <c r="J47" s="27" t="s">
+        <v>184</v>
+      </c>
+      <c r="K47" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="L47" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="M47" s="0" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="5"/>
+      <c r="B48" s="14" t="n">
+        <v>44</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="E48" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+M48</f>
+        <v>46365</v>
+      </c>
+      <c r="G48" s="13" t="n">
+        <f aca="false">F48+E48-1</f>
+        <v>46365</v>
+      </c>
+      <c r="H48" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="I48" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="J48" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="K47" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="L47" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="M47" s="0" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
-      <c r="B48" s="19" t="n">
-        <v>44</v>
-      </c>
-      <c r="C48" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="D48" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="E48" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="18" t="n">
-        <f aca="false">说明与修订!$B$5+M48</f>
-        <v>46364</v>
-      </c>
-      <c r="G48" s="18" t="n">
-        <f aca="false">F48+E48-1</f>
-        <v>46364</v>
-      </c>
-      <c r="H48" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I48" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="J48" s="27" t="s">
-        <v>187</v>
-      </c>
-      <c r="K48" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="L48" s="17" t="s">
+      <c r="K48" s="12" t="s">
         <v>189</v>
       </c>
+      <c r="L48" s="12"/>
       <c r="M48" s="0" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="5" t="s">
+        <v>190</v>
+      </c>
       <c r="B49" s="9" t="n">
         <v>45</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E49" s="9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F49" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M49</f>
-        <v>46365</v>
+        <v>46366</v>
       </c>
       <c r="G49" s="8" t="n">
         <f aca="false">F49+E49-1</f>
-        <v>46365</v>
+        <v>46385</v>
       </c>
       <c r="H49" s="7" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>19</v>
+        <v>193</v>
       </c>
       <c r="J49" s="9" t="s">
         <v>28</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="L49" s="7"/>
+        <v>194</v>
+      </c>
+      <c r="L49" s="7" t="s">
+        <v>195</v>
+      </c>
       <c r="M49" s="0" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5" t="s">
-        <v>193</v>
-      </c>
+      <c r="A50" s="5"/>
       <c r="B50" s="14" t="n">
         <v>46</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F50" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M50</f>
@@ -10052,22 +10065,22 @@
       </c>
       <c r="G50" s="13" t="n">
         <f aca="false">F50+E50-1</f>
-        <v>46385</v>
+        <v>46455</v>
       </c>
       <c r="H50" s="12" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>196</v>
+        <v>19</v>
       </c>
       <c r="J50" s="14" t="s">
         <v>28</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="L50" s="12" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="M50" s="0" t="n">
         <v>38</v>
@@ -10079,21 +10092,21 @@
         <v>47</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="E51" s="9" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="F51" s="8" t="n">
         <f aca="false">说明与修订!$B$5+M51</f>
-        <v>46366</v>
+        <v>46456</v>
       </c>
       <c r="G51" s="8" t="n">
         <f aca="false">F51+E51-1</f>
-        <v>46455</v>
+        <v>46456</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>19</v>
@@ -10105,128 +10118,87 @@
         <v>28</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="L51" s="7" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M51" s="0" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
       <c r="B52" s="14" t="n">
         <v>48</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>1</v>
+        <v>365</v>
       </c>
       <c r="F52" s="13" t="n">
         <f aca="false">说明与修订!$B$5+M52</f>
-        <v>46456</v>
+        <v>46457</v>
       </c>
       <c r="G52" s="13" t="n">
         <f aca="false">F52+E52-1</f>
-        <v>46456</v>
+        <v>46821</v>
       </c>
       <c r="H52" s="12" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J52" s="14" t="s">
         <v>28</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="L52" s="12" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M52" s="0" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="5"/>
-      <c r="B53" s="9" t="n">
-        <v>49</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="D53" s="7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="28" t="s">
         <v>208</v>
       </c>
-      <c r="E53" s="9" t="n">
-        <v>365</v>
-      </c>
-      <c r="F53" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M53</f>
-        <v>46457</v>
-      </c>
-      <c r="G53" s="8" t="n">
-        <f aca="false">F53+E53-1</f>
-        <v>46821</v>
-      </c>
-      <c r="H53" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="I53" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J53" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K53" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L53" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="M53" s="0" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="28" t="s">
-        <v>211</v>
-      </c>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
-      <c r="D54" s="28"/>
-      <c r="E54" s="29"/>
-      <c r="F54" s="29"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="29"/>
-      <c r="I54" s="29"/>
-      <c r="J54" s="29"/>
-      <c r="K54" s="29"/>
-      <c r="L54" s="29"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
+      <c r="D53" s="28"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
+      <c r="G53" s="29"/>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="29"/>
+      <c r="K53" s="29"/>
+      <c r="L53" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L53"/>
+  <autoFilter ref="A4:L52"/>
   <mergeCells count="9">
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A6:A15"/>
-    <mergeCell ref="A16:A29"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="A41:A49"/>
-    <mergeCell ref="A50:A53"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="A15:A28"/>
+    <mergeCell ref="A29:A39"/>
+    <mergeCell ref="A40:A48"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="A53:D53"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J53" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J52" type="list">
       <formula1>"未开始,进行中,已完成,受阻,待客户确认,待确认"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10247,7 +10219,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:X52"/>
+  <dimension ref="A1:X51"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -10259,7 +10231,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -10296,7 +10268,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E2" s="32" t="str">
         <f aca="false">TEXT(说明与修订!$B$5+7*0,"mm/dd")</f>
@@ -10387,7 +10359,7 @@
         <v>15</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D3" s="33" t="n">
         <v>2</v>
@@ -10421,7 +10393,7 @@
         <v>23</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D4" s="33" t="n">
         <v>2</v>
@@ -10455,7 +10427,7 @@
         <v>23</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D5" s="33" t="n">
         <v>1</v>
@@ -10489,7 +10461,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D6" s="33" t="n">
         <v>1</v>
@@ -10523,10 +10495,10 @@
         <v>23</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D7" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="38"/>
       <c r="F7" s="37"/>
@@ -10557,13 +10529,13 @@
         <v>23</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D8" s="33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E8" s="38"/>
-      <c r="F8" s="37"/>
+      <c r="F8" s="38"/>
       <c r="G8" s="37"/>
       <c r="H8" s="37"/>
       <c r="I8" s="37"/>
@@ -10591,12 +10563,12 @@
         <v>23</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D9" s="33" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" s="38"/>
+        <v>3</v>
+      </c>
+      <c r="E9" s="37"/>
       <c r="F9" s="38"/>
       <c r="G9" s="37"/>
       <c r="H9" s="37"/>
@@ -10625,10 +10597,10 @@
         <v>23</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D10" s="33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" s="37"/>
       <c r="F10" s="38"/>
@@ -10659,10 +10631,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D11" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="37"/>
       <c r="F11" s="38"/>
@@ -10693,13 +10665,13 @@
         <v>23</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>223</v>
+        <v>65</v>
       </c>
       <c r="D12" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="37"/>
-      <c r="F12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="37"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37"/>
       <c r="I12" s="37"/>
@@ -10723,17 +10695,17 @@
       <c r="A13" s="33" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="34" t="s">
-        <v>23</v>
+      <c r="B13" s="39" t="s">
+        <v>220</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>68</v>
+        <v>221</v>
       </c>
       <c r="D13" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E13" s="38"/>
-      <c r="F13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="40"/>
       <c r="G13" s="37"/>
       <c r="H13" s="37"/>
       <c r="I13" s="37"/>
@@ -10758,10 +10730,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D14" s="33" t="n">
         <v>2</v>
@@ -10792,17 +10764,17 @@
         <v>13</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>226</v>
+        <v>76</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" s="37"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="37"/>
+      <c r="F15" s="37"/>
+      <c r="G15" s="40"/>
       <c r="H15" s="37"/>
       <c r="I15" s="37"/>
       <c r="J15" s="37"/>
@@ -10826,10 +10798,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>79</v>
+        <v>223</v>
       </c>
       <c r="D16" s="33" t="n">
         <v>1</v>
@@ -10860,10 +10832,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17" s="35" t="s">
         <v>224</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>227</v>
       </c>
       <c r="D17" s="33" t="n">
         <v>1</v>
@@ -10894,10 +10866,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>228</v>
+        <v>86</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>1</v>
@@ -10928,7 +10900,7 @@
         <v>17</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C19" s="35" t="s">
         <v>89</v>
@@ -10962,7 +10934,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C20" s="35" t="s">
         <v>92</v>
@@ -10996,10 +10968,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>95</v>
+        <v>225</v>
       </c>
       <c r="D21" s="33" t="n">
         <v>1</v>
@@ -11030,10 +11002,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>229</v>
+        <v>98</v>
       </c>
       <c r="D22" s="33" t="n">
         <v>1</v>
@@ -11064,13 +11036,13 @@
         <v>21</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>101</v>
+        <v>226</v>
       </c>
       <c r="D23" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="37"/>
       <c r="F23" s="37"/>
@@ -11098,13 +11070,13 @@
         <v>22</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>230</v>
+        <v>106</v>
       </c>
       <c r="D24" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E24" s="37"/>
       <c r="F24" s="37"/>
@@ -11132,10 +11104,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>109</v>
+        <v>227</v>
       </c>
       <c r="D25" s="33" t="n">
         <v>1</v>
@@ -11166,18 +11138,18 @@
         <v>24</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="D26" s="33" t="n">
         <v>1</v>
       </c>
       <c r="E26" s="37"/>
       <c r="F26" s="37"/>
-      <c r="G26" s="40"/>
-      <c r="H26" s="37"/>
+      <c r="G26" s="37"/>
+      <c r="H26" s="40"/>
       <c r="I26" s="37"/>
       <c r="J26" s="37"/>
       <c r="K26" s="37"/>
@@ -11199,11 +11171,11 @@
       <c r="A27" s="33" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="39" t="s">
-        <v>224</v>
+      <c r="B27" s="34" t="s">
+        <v>116</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>232</v>
+        <v>117</v>
       </c>
       <c r="D27" s="33" t="n">
         <v>1</v>
@@ -11211,7 +11183,7 @@
       <c r="E27" s="37"/>
       <c r="F27" s="37"/>
       <c r="G27" s="37"/>
-      <c r="H27" s="40"/>
+      <c r="H27" s="41"/>
       <c r="I27" s="37"/>
       <c r="J27" s="37"/>
       <c r="K27" s="37"/>
@@ -11234,13 +11206,13 @@
         <v>26</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>120</v>
+        <v>229</v>
       </c>
       <c r="D28" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="37"/>
       <c r="F28" s="37"/>
@@ -11268,13 +11240,13 @@
         <v>27</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D29" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E29" s="37"/>
       <c r="F29" s="37"/>
@@ -11302,10 +11274,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>234</v>
+        <v>127</v>
       </c>
       <c r="D30" s="33" t="n">
         <v>1</v>
@@ -11336,10 +11308,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D31" s="33" t="n">
         <v>1</v>
@@ -11370,7 +11342,7 @@
         <v>30</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C32" s="35" t="s">
         <v>134</v>
@@ -11404,13 +11376,13 @@
         <v>31</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D33" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
@@ -11438,13 +11410,13 @@
         <v>32</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>141</v>
+        <v>231</v>
       </c>
       <c r="D34" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E34" s="37"/>
       <c r="F34" s="37"/>
@@ -11472,10 +11444,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D35" s="33" t="n">
         <v>1</v>
@@ -11483,8 +11455,8 @@
       <c r="E35" s="37"/>
       <c r="F35" s="37"/>
       <c r="G35" s="37"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="37"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="41"/>
       <c r="J35" s="37"/>
       <c r="K35" s="37"/>
       <c r="L35" s="37"/>
@@ -11506,10 +11478,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D36" s="33" t="n">
         <v>1</v>
@@ -11540,10 +11512,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D37" s="33" t="n">
         <v>1</v>
@@ -11574,19 +11546,19 @@
         <v>36</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>119</v>
-      </c>
-      <c r="C38" s="35" t="s">
-        <v>238</v>
+        <v>157</v>
+      </c>
+      <c r="C38" s="42" t="s">
+        <v>235</v>
       </c>
       <c r="D38" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="37"/>
       <c r="F38" s="37"/>
       <c r="G38" s="37"/>
       <c r="H38" s="37"/>
-      <c r="I38" s="41"/>
+      <c r="I38" s="43"/>
       <c r="J38" s="37"/>
       <c r="K38" s="37"/>
       <c r="L38" s="37"/>
@@ -11608,13 +11580,13 @@
         <v>37</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D39" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E39" s="37"/>
       <c r="F39" s="37"/>
@@ -11642,10 +11614,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>160</v>
-      </c>
-      <c r="C40" s="42" t="s">
-        <v>240</v>
+        <v>157</v>
+      </c>
+      <c r="C40" s="35" t="s">
+        <v>165</v>
       </c>
       <c r="D40" s="33" t="n">
         <v>1</v>
@@ -11676,13 +11648,13 @@
         <v>39</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="D41" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="37"/>
       <c r="F41" s="37"/>
@@ -11710,13 +11682,13 @@
         <v>40</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>241</v>
+        <v>172</v>
       </c>
       <c r="D42" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E42" s="37"/>
       <c r="F42" s="37"/>
@@ -11744,10 +11716,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>175</v>
+        <v>238</v>
       </c>
       <c r="D43" s="33" t="n">
         <v>1</v>
@@ -11756,8 +11728,8 @@
       <c r="F43" s="37"/>
       <c r="G43" s="37"/>
       <c r="H43" s="37"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="43"/>
       <c r="K43" s="37"/>
       <c r="L43" s="37"/>
       <c r="M43" s="37"/>
@@ -11778,13 +11750,13 @@
         <v>42</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="D44" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="37"/>
       <c r="F44" s="37"/>
@@ -11812,13 +11784,13 @@
         <v>43</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D45" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E45" s="37"/>
       <c r="F45" s="37"/>
@@ -11846,10 +11818,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="D46" s="33" t="n">
         <v>1</v>
@@ -11880,23 +11852,23 @@
         <v>45</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>190</v>
+        <v>239</v>
       </c>
       <c r="D47" s="33" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E47" s="37"/>
       <c r="F47" s="37"/>
       <c r="G47" s="37"/>
       <c r="H47" s="37"/>
       <c r="I47" s="37"/>
-      <c r="J47" s="43"/>
-      <c r="K47" s="37"/>
-      <c r="L47" s="37"/>
-      <c r="M47" s="37"/>
+      <c r="J47" s="44"/>
+      <c r="K47" s="44"/>
+      <c r="L47" s="44"/>
+      <c r="M47" s="44"/>
       <c r="N47" s="37"/>
       <c r="O47" s="37"/>
       <c r="P47" s="37"/>
@@ -11914,13 +11886,13 @@
         <v>46</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>243</v>
+        <v>196</v>
       </c>
       <c r="D48" s="33" t="n">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="E48" s="37"/>
       <c r="F48" s="37"/>
@@ -11931,16 +11903,16 @@
       <c r="K48" s="44"/>
       <c r="L48" s="44"/>
       <c r="M48" s="44"/>
-      <c r="N48" s="37"/>
-      <c r="O48" s="37"/>
-      <c r="P48" s="37"/>
-      <c r="Q48" s="37"/>
-      <c r="R48" s="37"/>
-      <c r="S48" s="37"/>
-      <c r="T48" s="37"/>
-      <c r="U48" s="37"/>
-      <c r="V48" s="37"/>
-      <c r="W48" s="37"/>
+      <c r="N48" s="44"/>
+      <c r="O48" s="44"/>
+      <c r="P48" s="44"/>
+      <c r="Q48" s="44"/>
+      <c r="R48" s="44"/>
+      <c r="S48" s="44"/>
+      <c r="T48" s="44"/>
+      <c r="U48" s="44"/>
+      <c r="V48" s="44"/>
+      <c r="W48" s="44"/>
       <c r="X48" s="37"/>
     </row>
     <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11948,72 +11920,38 @@
         <v>47</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D49" s="33" t="n">
-        <v>90</v>
+        <v>1</v>
       </c>
       <c r="E49" s="37"/>
       <c r="F49" s="37"/>
       <c r="G49" s="37"/>
       <c r="H49" s="37"/>
       <c r="I49" s="37"/>
-      <c r="J49" s="44"/>
-      <c r="K49" s="44"/>
-      <c r="L49" s="44"/>
-      <c r="M49" s="44"/>
-      <c r="N49" s="44"/>
-      <c r="O49" s="44"/>
-      <c r="P49" s="44"/>
-      <c r="Q49" s="44"/>
-      <c r="R49" s="44"/>
-      <c r="S49" s="44"/>
-      <c r="T49" s="44"/>
-      <c r="U49" s="44"/>
-      <c r="V49" s="44"/>
+      <c r="J49" s="37"/>
+      <c r="K49" s="37"/>
+      <c r="L49" s="37"/>
+      <c r="M49" s="37"/>
+      <c r="N49" s="37"/>
+      <c r="O49" s="37"/>
+      <c r="P49" s="37"/>
+      <c r="Q49" s="37"/>
+      <c r="R49" s="37"/>
+      <c r="S49" s="37"/>
+      <c r="T49" s="37"/>
+      <c r="U49" s="37"/>
+      <c r="V49" s="37"/>
       <c r="W49" s="44"/>
       <c r="X49" s="37"/>
     </row>
-    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="33" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="C50" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="D50" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="37"/>
-      <c r="K50" s="37"/>
-      <c r="L50" s="37"/>
-      <c r="M50" s="37"/>
-      <c r="N50" s="37"/>
-      <c r="O50" s="37"/>
-      <c r="P50" s="37"/>
-      <c r="Q50" s="37"/>
-      <c r="R50" s="37"/>
-      <c r="S50" s="37"/>
-      <c r="T50" s="37"/>
-      <c r="U50" s="37"/>
-      <c r="V50" s="37"/>
-      <c r="W50" s="44"/>
-      <c r="X50" s="37"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="45" t="s">
-        <v>244</v>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="45" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -12052,7 +11990,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -12067,507 +12005,507 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="F2" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="G2" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="H2" s="47" t="s">
         <v>249</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="I2" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="K2" s="4" t="s">
         <v>252</v>
-      </c>
-      <c r="H2" s="47" t="s">
-        <v>253</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="48" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G3" s="50" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H3" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I3" s="50" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J3" s="50"/>
       <c r="K3" s="50"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="51" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E4" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I4" s="53" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J4" s="53"/>
       <c r="K4" s="53"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G5" s="50" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I5" s="50" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J5" s="50"/>
       <c r="K5" s="50"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I6" s="53" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J6" s="53"/>
       <c r="K6" s="53"/>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="48" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G7" s="50" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I7" s="50" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J7" s="50"/>
       <c r="K7" s="50"/>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I8" s="53" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J8" s="53"/>
       <c r="K8" s="53"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H9" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I9" s="50" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J9" s="50"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J10" s="53"/>
       <c r="K10" s="53"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F11" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H11" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J11" s="50"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="51" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I12" s="53" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J12" s="53"/>
       <c r="K12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H13" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I13" s="55" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J13" s="50"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I14" s="55" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J14" s="53"/>
       <c r="K14" s="53"/>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G15" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H15" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I15" s="55" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J15" s="50"/>
       <c r="K15" s="50"/>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="51" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G16" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I16" s="55" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J16" s="53"/>
       <c r="K16" s="53"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H17" s="49" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="I17" s="55" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J17" s="50"/>
       <c r="K17" s="50"/>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="56" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="B19" s="56"/>
       <c r="C19" s="56"/>
@@ -12616,7 +12554,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="57" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -12632,36 +12570,36 @@
         <v>4</v>
       </c>
       <c r="B2" s="58" t="s">
+        <v>275</v>
+      </c>
+      <c r="C2" s="58" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2" s="58" t="s">
+        <v>277</v>
+      </c>
+      <c r="E2" s="58" t="s">
+        <v>278</v>
+      </c>
+      <c r="F2" s="58" t="s">
         <v>279</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="G2" s="58" t="s">
         <v>280</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="H2" s="58" t="s">
         <v>281</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="I2" s="58" t="s">
         <v>282</v>
-      </c>
-      <c r="F2" s="58" t="s">
-        <v>283</v>
-      </c>
-      <c r="G2" s="58" t="s">
-        <v>284</v>
-      </c>
-      <c r="H2" s="58" t="s">
-        <v>285</v>
-      </c>
-      <c r="I2" s="58" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="59" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -12676,16 +12614,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>291</v>
+        <v>286</v>
+      </c>
+      <c r="D4" s="26" t="s">
+        <v>287</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1</v>
@@ -12694,7 +12632,7 @@
         <v>34</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -12703,16 +12641,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>295</v>
+        <v>290</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>291</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>1</v>
@@ -12721,7 +12659,7 @@
         <v>34</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -12730,16 +12668,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>298</v>
+        <v>293</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>294</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>1</v>
@@ -12748,7 +12686,7 @@
         <v>34</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -12757,16 +12695,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>302</v>
+        <v>297</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>298</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>1</v>
@@ -12775,7 +12713,7 @@
         <v>34</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I7" s="7"/>
     </row>
@@ -12784,16 +12722,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>304</v>
+        <v>299</v>
+      </c>
+      <c r="C8" s="26" t="s">
+        <v>300</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1</v>
@@ -12802,7 +12740,7 @@
         <v>34</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I8" s="7"/>
     </row>
@@ -12811,45 +12749,45 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>307</v>
+        <v>302</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>303</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>311</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>312</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>313</v>
+      <c r="B10" s="26" t="s">
+        <v>307</v>
+      </c>
+      <c r="C10" s="26" t="s">
+        <v>308</v>
+      </c>
+      <c r="D10" s="26" t="s">
+        <v>309</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1</v>
@@ -12858,16 +12796,16 @@
         <v>34</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -12882,7 +12820,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -12897,28 +12835,28 @@
         <v>1.1</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>318</v>
+        <v>313</v>
+      </c>
+      <c r="C13" s="26" t="s">
+        <v>314</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H13" s="61" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12926,28 +12864,28 @@
         <v>2</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>322</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>323</v>
+        <v>318</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>319</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H14" s="62" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12955,25 +12893,25 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>328</v>
+        <v>323</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>324</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I15" s="7"/>
     </row>
@@ -12982,23 +12920,23 @@
         <v>5</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -13007,32 +12945,32 @@
         <v>6</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
@@ -13047,14 +12985,14 @@
         <v>1</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1</v>
@@ -13063,7 +13001,7 @@
         <v>34</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I19" s="7"/>
     </row>
@@ -13072,14 +13010,14 @@
         <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>1</v>
@@ -13088,10 +13026,10 @@
         <v>34</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13099,14 +13037,14 @@
         <v>3</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1</v>
@@ -13115,7 +13053,7 @@
         <v>34</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I21" s="7"/>
     </row>
@@ -13124,14 +13062,14 @@
         <v>4</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1</v>
@@ -13140,7 +13078,7 @@
         <v>34</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I22" s="7"/>
     </row>
@@ -13149,14 +13087,14 @@
         <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>1</v>
@@ -13165,7 +13103,7 @@
         <v>34</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I23" s="7"/>
     </row>
@@ -13174,14 +13112,14 @@
         <v>6</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1</v>
@@ -13190,7 +13128,7 @@
         <v>34</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I24" s="7"/>
     </row>
@@ -13199,14 +13137,14 @@
         <v>7</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1</v>
@@ -13215,7 +13153,7 @@
         <v>34</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I25" s="7"/>
     </row>
@@ -13224,14 +13162,14 @@
         <v>8</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>1</v>
@@ -13240,7 +13178,7 @@
         <v>34</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I26" s="7"/>
     </row>
@@ -13249,12 +13187,12 @@
         <v>9</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1</v>
@@ -13263,7 +13201,7 @@
         <v>34</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I27" s="7"/>
     </row>
@@ -13272,14 +13210,14 @@
         <v>9.1</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>5</v>
@@ -13288,10 +13226,10 @@
         <v>34</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>357</v>
+        <v>334</v>
+      </c>
+      <c r="I28" s="26" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13299,14 +13237,14 @@
         <v>9.2</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>358</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>359</v>
+        <v>354</v>
+      </c>
+      <c r="C29" s="26" t="s">
+        <v>355</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>1</v>
@@ -13315,10 +13253,10 @@
         <v>34</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>338</v>
-      </c>
-      <c r="I29" s="15" t="s">
-        <v>360</v>
+        <v>334</v>
+      </c>
+      <c r="I29" s="26" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13326,14 +13264,14 @@
         <v>9.3</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>1</v>
@@ -13342,7 +13280,7 @@
         <v>34</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I30" s="7"/>
     </row>
@@ -13351,14 +13289,14 @@
         <v>9.4</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="9" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2</v>
@@ -13367,7 +13305,7 @@
         <v>34</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="I31" s="7"/>
     </row>
@@ -13390,7 +13328,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C55"/>
+  <dimension ref="A1:C56"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -13400,187 +13338,187 @@
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="63" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="64" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="65" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B5" s="66" t="n">
         <v>46328</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="65" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B6" s="65" t="n">
-        <f aca="false">MAX(计划!G5:G49)-MIN(计划!F5:F49)+1</f>
+        <f aca="false">MAX(计划!G5:G48)-MIN(计划!F5:F48)+1</f>
         <v>38</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="65" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B7" s="65" t="n">
         <v>90</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="65" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="63" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="65" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B12" s="68" t="n">
         <f aca="false">计划!G5</f>
         <v>46329</v>
       </c>
       <c r="C12" s="65" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="65" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B13" s="68" t="n">
         <f aca="false">计划!G7</f>
         <v>46332</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B14" s="68" t="n">
-        <f aca="false">计划!G17</f>
+        <f aca="false">计划!G16</f>
         <v>46341</v>
       </c>
       <c r="C14" s="67" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B15" s="68" t="n">
-        <f aca="false">计划!G29</f>
+        <f aca="false">计划!G28</f>
         <v>46349</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="65" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B16" s="68" t="n">
-        <f aca="false">计划!G40</f>
+        <f aca="false">计划!G39</f>
         <v>46357</v>
       </c>
       <c r="C16" s="65" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="65" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B17" s="68" t="n">
-        <f aca="false">计划!G44</f>
+        <f aca="false">计划!G43</f>
         <v>46362</v>
       </c>
       <c r="C17" s="65" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="65" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B18" s="68" t="n">
-        <f aca="false">计划!G49</f>
+        <f aca="false">计划!G48</f>
         <v>46365</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="65" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B19" s="68" t="n">
-        <f aca="false">计划!G52</f>
+        <f aca="false">计划!G51</f>
         <v>46456</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="63" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13588,10 +13526,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13599,10 +13537,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="C23" s="70" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13610,10 +13548,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="70" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="C24" s="70" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13621,10 +13559,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="70" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="C25" s="70" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13632,10 +13570,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="70" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="C26" s="70" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13643,10 +13581,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="70" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="C27" s="70" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13654,10 +13592,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="70" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="C28" s="70" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13665,10 +13603,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="70" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="C29" s="70" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13676,10 +13614,10 @@
         <v>8</v>
       </c>
       <c r="B30" s="70" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="C30" s="70" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13687,10 +13625,10 @@
         <v>9</v>
       </c>
       <c r="B31" s="70" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="C31" s="70" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13698,10 +13636,10 @@
         <v>10</v>
       </c>
       <c r="B32" s="70" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="C32" s="70" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13709,10 +13647,10 @@
         <v>11</v>
       </c>
       <c r="B33" s="70" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="C33" s="70" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13720,10 +13658,10 @@
         <v>12</v>
       </c>
       <c r="B34" s="70" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C34" s="70" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13731,10 +13669,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="70" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="C35" s="70" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13742,10 +13680,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="70" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C36" s="70" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13753,10 +13691,10 @@
         <v>15</v>
       </c>
       <c r="B37" s="70" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C37" s="70" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13764,135 +13702,146 @@
         <v>16</v>
       </c>
       <c r="B38" s="70" t="s">
+        <v>428</v>
+      </c>
+      <c r="C38" s="70" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="70" t="n">
+        <v>17</v>
+      </c>
+      <c r="B39" s="70" t="s">
+        <v>430</v>
+      </c>
+      <c r="C39" s="70" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="63" t="s">
         <v>432</v>
       </c>
-      <c r="C38" s="70" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="63" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="71" t="s">
-        <v>435</v>
-      </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="71" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="B42" s="71"/>
       <c r="C42" s="71"/>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="71" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B43" s="71"/>
       <c r="C43" s="71"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="71" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="B44" s="71"/>
       <c r="C44" s="71"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="71" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="B45" s="71"/>
       <c r="C45" s="71"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="71" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="B46" s="71"/>
       <c r="C46" s="71"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="71" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="B47" s="71"/>
       <c r="C47" s="71"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="63" t="s">
+    <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="71" t="s">
+        <v>439</v>
+      </c>
+      <c r="B48" s="71"/>
+      <c r="C48" s="71"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="63" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="72"/>
+      <c r="B51" s="65" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="73" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="74"/>
+      <c r="B52" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="C52" s="73" t="s">
         <v>442</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="72"/>
-      <c r="B50" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="C50" s="73" t="s">
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="75"/>
+      <c r="B53" s="67" t="s">
         <v>443</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="74"/>
-      <c r="B51" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="C51" s="73" t="s">
+      <c r="C53" s="73" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="75"/>
-      <c r="B52" s="67" t="s">
+    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A54" s="76"/>
+      <c r="B54" s="65" t="s">
+        <v>116</v>
+      </c>
+      <c r="C54" s="73" t="s">
         <v>445</v>
       </c>
-      <c r="C52" s="73" t="s">
+    </row>
+    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="77"/>
+      <c r="B55" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="78" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="76"/>
-      <c r="B53" s="65" t="s">
-        <v>119</v>
-      </c>
-      <c r="C53" s="73" t="s">
+    <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="79"/>
+      <c r="B56" s="65" t="s">
+        <v>190</v>
+      </c>
+      <c r="C56" s="73" t="s">
         <v>447</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="77"/>
-      <c r="B54" s="65" t="s">
-        <v>160</v>
-      </c>
-      <c r="C54" s="78" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="79"/>
-      <c r="B55" s="65" t="s">
-        <v>193</v>
-      </c>
-      <c r="C55" s="73" t="s">
-        <v>449</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A41:C41"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:C48"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>

--- a/CVT-MES项目资料/04_墨西哥CVT线现场实施计划_V2.xlsx
+++ b/CVT-MES项目资料/04_墨西哥CVT线现场实施计划_V2.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'甘特（周）'!$1:$2</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">硬件清单!$1:$2</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">计划!$1:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">计划!$A$4:$L$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">计划!$A$4:$K$52</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="399">
   <si>
     <r>
       <rPr>
@@ -165,7 +165,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">V2.0</t>
+      <t xml:space="preserve">V2.1</t>
     </r>
     <r>
       <rPr>
@@ -299,36 +299,6 @@
   </si>
   <si>
     <t xml:space="preserve">工作内容</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">输出物 </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">验收标准</t>
-    </r>
   </si>
   <si>
     <r>
@@ -448,33 +418,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">《到货清点单》《</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">环境确认单》</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">递缇项目经理</t>
   </si>
   <si>
@@ -561,9 +504,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">机柜与设备安装记录</t>
-  </si>
-  <si>
     <t xml:space="preserve">以弗德安装组</t>
   </si>
   <si>
@@ -663,9 +603,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">上电自检记录</t>
-  </si>
-  <si>
     <t xml:space="preserve">递缇实施工程师</t>
   </si>
   <si>
@@ -732,9 +669,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">系统与数据库复核记录</t>
-  </si>
-  <si>
     <t xml:space="preserve">服务器硬件自检正常；国内已完成系统与数据库安装，具备镜像或配置基线</t>
   </si>
   <si>
@@ -848,33 +782,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">网络拓扑与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">IP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">规划表</t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve">甲方提供交换机，双方配置</t>
   </si>
   <si>
@@ -914,6 +821,14 @@
     <r>
       <rPr>
         <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">以弗德（一体机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
         <rFont val="微软雅黑"/>
         <family val="0"/>
         <charset val="1"/>
@@ -926,17 +841,462 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">站安装上电记录</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">以弗德（一体机</t>
+      <t xml:space="preserve">台已到货）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">一体机、支架到位，工位供电与网络到位</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★一体机原未发运、后补发到货，集中安装，窗口后移</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">安装并调试扫码枪：到场</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把有线</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">无线连接、扫码识别、条码类型；缺口</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把按借用</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">串口枪</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">补发处置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">递缇</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">甲方</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">扫码枪到位，工位一体机系统就绪</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★实到</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把，缺</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把；斑马清关受阻，建议递缇人员随行带</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把串口枪，其余向其他工位借用或本地采购</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">安装</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">75</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">寸大屏电视</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">盒式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">，配置浏览器、网络、看板显示</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">以弗德</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">大屏、盒式</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">到位，网络连通</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配合调试上线打码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">标签打印：标签模板、条码规则、总成二维码打印</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">甲方提供打码设备</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">打印</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">打码设备到位，条码规则确认</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">★合同仅含标签打印与条码规则，打码硬件未在供货清单，需甲方提供</t>
+  </si>
+  <si>
+    <t xml:space="preserve">检查桥架、网线、电源线等安装辅材，确认工位网络与供电稳定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">辅材到位，现场施工完成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">软件部署与基础配置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部署</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服务端：软件包、组件、依赖环境，初始化数据库</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服务器系统、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SQL Server</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">就绪</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部署工控机客户端到</t>
     </r>
     <r>
       <rPr>
@@ -953,14 +1313,722 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">台已到货）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">一体机、支架到位，工位供电与网络到位</t>
-  </si>
-  <si>
-    <t xml:space="preserve">★一体机原未发运、后补发到货，集中安装，窗口后移</t>
+      <t xml:space="preserve">个工位一体机，配置启动项、客户端参数</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">工位一体机系统与网络就绪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一体机后到货，客户端镜像建议用同型号测试机提前验证</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配置系统语言：中文、西班牙文切换</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服务端部署完成</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">协议要求软件支持中西文切换</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置用户管理：用户、角色、权限、员工、工位技能、班组长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">质检</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出库等角色</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最终用户提供组织架构与权限需求</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置主动轮工艺：产品型号、编号、组件、厂商、重量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">扭力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动平衡上下限</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最终用户提供主动轮工艺参数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配置从动轮工艺：产品型号、编号、组件、厂商、工艺参数上下限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最终用户提供从动轮工艺参数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配置条码规则、标签模板、上线打印功能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">条码规则、标签模板确认</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配置工艺路线、工序、工位、启用状态、异常关联工位、干涉工位跳过逻辑</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工艺路线、工位定义确认</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置电子作业指导书：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">图、预装提示、按车型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工序切换</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">图、作业指导书资料齐全</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">配置拧紧工艺：拧紧枪、程序号、拧紧数量、不合格次数、使能控制、数据采集</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拧紧枪接口协议、程序号确认</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ATLAS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">拧紧枪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把（主动轮）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置设备采集接口：伺服压机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台、拧紧枪</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把、检测设备</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通讯参数</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">设备接口协议、通讯参数确认</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">压机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CVT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">二线；国外调试费用未含，需甲方</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">设备商配合</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">配置订单管理：生产计划、工单、计划编号规则、终端客户、产品型号、数量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">订单管理规则确认</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置质量报表、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">统计、电子看板、日志管理、追溯查询</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">报表格式、看板内容确认</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与工厂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES/SAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">预留接口、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">标准接口协议</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工厂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES/SAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">接口文档、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">协议确认</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">预留接口，联调视甲方系统可用性</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工位单机与设备采集调试</t>
+  </si>
+  <si>
+    <t xml:space="preserve">服务器本地功能验证：登录、订单、工艺、报表、追溯、用户权限、日志</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基础配置完成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">逐工位验证客户端：启动、扫码、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SOP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">显示、防错、过站、数据上传</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">工位客户端部署完成，网络连通</t>
+  </si>
+  <si>
+    <t xml:space="preserve">缺枪工位先用手工录入模式，签认表标注</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上线打码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条码绑定测试：总成二维码生成、打印、扫描、绑定</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">打码设备、扫码枪就绪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">零件条码采集测试：零件二维码、批次码、重复校验、数量校验、特征码校验</t>
+  </si>
+  <si>
+    <t xml:space="preserve">零件条码规则确认，扫码枪就绪</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★缺</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把扫码枪的工位无法完成条码防错验证</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">过程数据采集测试：进站、出站、过站信息、工单号、序列号、工站、人员、时间</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工位客户端与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通讯正常</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">拧紧数据采集测试：扭矩、角度、曲线、合格状态、螺栓遗漏查询</t>
+  </si>
+  <si>
+    <t xml:space="preserve">拧紧枪通讯正常，程序号配置完成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ATLAS 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">把（主动轮）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">伺服压机数据采集验证：压力、位移、通讯稳定性、数据上传</t>
   </si>
   <si>
     <r>
@@ -970,7 +2038,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">安装并调试扫码枪：到场</t>
+      <t xml:space="preserve">甲方</t>
     </r>
     <r>
       <rPr>
@@ -980,7 +2048,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -989,12 +2057,23 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">把有线</t>
-    </r>
+      <t xml:space="preserve">设备商主责，递缇远程协助</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">甲方</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
         <rFont val="微软雅黑"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1008,12 +2087,26 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">无线连接、扫码识别、条码类型；缺口</t>
-    </r>
+      <t xml:space="preserve">设备商</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">压机通电、网络连通、接口协议开放</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★报价明确</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="9"/>
         <rFont val="微软雅黑"/>
         <family val="0"/>
         <charset val="1"/>
@@ -1027,134 +2120,424 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">把按借用</t>
-    </r>
+      <t xml:space="preserve">台压机仅国内调试、不含国外调试费用，现场责任界面需书面确认</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">检测设备数据采集验证：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台检测设备数据上传、结果绑定</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">检测设备接口开放、通讯正常</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">电子看板验证：订单内容、计划产量、实际产量、不良率、工位状态、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">图</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">看板数据源配置完成，大屏就绪</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">质量报告与追溯验证：正反向追溯、树形展示、报表导出</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Excel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、工号姓名显示</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">质量数据采集完成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">性能验证：操作延时≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒、数据库查询≤</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">秒、并发访问、故障恢复、数据不丢失</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">系统稳定运行，测试数据准备</t>
+  </si>
+  <si>
+    <t xml:space="preserve">判定方法需双方事先约定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全线联调与试生产</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">联调：工件到位、保存数据、保存完成、验证完成、设备监控、生产控制</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">单机调试完成，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">通讯正常</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">与工厂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES/SAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">接口联调（如有）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工厂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES/SAP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">接口可用</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">甲方系统不具备时列为遗留项</t>
+  </si>
+  <si>
+    <t xml:space="preserve">全线空运行：订单下发→打码→扫码→装配→数据采集→过站→下线→追溯</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">各工位、设备、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">联调完成</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">带产品试生产：小批量验证，记录</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">串口枪</t>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
     </r>
     <r>
       <rPr>
         <b val="true"/>
         <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">补发处置</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">扫码枪调试记录</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">递缇</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">甲方</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">扫码枪到位，工位一体机系统就绪</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">★实到</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">10</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">把，缺</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">把；斑马清关受阻，建议递缇人员随行带</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">问题、设备采集问题、网络问题</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">空运行无重大异常，试生产物料准备</t>
+  </si>
+  <si>
+    <t xml:space="preserve">试生产物料由甲方准备</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常场景测试：设备异常、质量异常、数据异常、安灯报警、不合格拦截、高权限跳站</t>
+  </si>
+  <si>
+    <t xml:space="preserve">异常处理逻辑配置完成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">生产报表、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、看板、日志、用户权限综合验证</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">试生产数据积累</t>
+  </si>
+  <si>
+    <t xml:space="preserve">分角色培训：操作工、班组长、质量、维护，并交付用户操作手册</t>
+  </si>
+  <si>
+    <t xml:space="preserve">系统功能验证完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★原计划缺培训任务，按交付物要求补充</t>
+  </si>
+  <si>
+    <t xml:space="preserve">预验收：按技术协议在杭州国内工厂进行；如已完成则做资料归档与遗留项确认</t>
+  </si>
+  <si>
+    <t xml:space="preserve">待确认</t>
+  </si>
+  <si>
+    <t xml:space="preserve">杭州阶段单机部署完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★需确认预验收是否已随一体机后到而顺延</t>
+  </si>
+  <si>
+    <t xml:space="preserve">现场实施完成确认与交接：遗留问题清单、备件与工具移交</t>
+  </si>
+  <si>
+    <t xml:space="preserve">试生产与培训完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">试运行、验收与运维</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">远程调试：缺陷修复、参数优化、陪产支持（</t>
+    </r>
+    <r>
+      <rPr>
         <sz val="9"/>
         <rFont val="微软雅黑"/>
         <family val="0"/>
@@ -1164,574 +2547,11 @@
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">把串口枪，其余向其他工位借用或本地采购</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">安装</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">75</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">寸大屏电视</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">+</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">盒式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">，配置浏览器、网络、看板显示</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">大屏显示确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">以弗德</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">大屏、盒式</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">到位，网络连通</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配合调试上线打码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">标签打印：标签模板、条码规则、总成二维码打印</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">打码打印测试记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">甲方提供打码设备</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">打印</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">打码设备到位，条码规则确认</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">★合同仅含标签打印与条码规则，打码硬件未在供货清单，需甲方提供</t>
-  </si>
-  <si>
-    <t xml:space="preserve">检查桥架、网线、电源线等安装辅材，确认工位网络与供电稳定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">辅材与布线检查表</t>
-  </si>
-  <si>
-    <t xml:space="preserve">辅材到位，现场施工完成</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">软件部署与基础配置</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部署</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服务端：软件包、组件、依赖环境，初始化数据库</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">服务端部署清单</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服务器系统、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SQL Server</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">就绪</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部署工控机客户端到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个工位一体机，配置启动项、客户端参数</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">客户端部署记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工位一体机系统与网络就绪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一体机后到货，客户端镜像建议用同型号测试机提前验证</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置系统语言：中文、西班牙文切换</t>
-  </si>
-  <si>
-    <t xml:space="preserve">双语切换确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服务端部署完成</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">协议要求软件支持中西文切换</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置用户管理：用户、角色、权限、员工、工位技能、班组长</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">质检</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出库等角色</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">权限配置确认单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供组织架构与权限需求</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置主动轮工艺：产品型号、编号、组件、厂商、重量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">扭力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动平衡上下限</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">主动轮工艺配置单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供主动轮工艺参数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置从动轮工艺：产品型号、编号、组件、厂商、工艺参数上下限</t>
-  </si>
-  <si>
-    <t xml:space="preserve">从动轮工艺配置单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供从动轮工艺参数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置条码规则、标签模板、上线打印功能</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条码规则与标签模板</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条码规则、标签模板确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置工艺路线、工序、工位、启用状态、异常关联工位、干涉工位跳过逻辑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工艺路线配置单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工艺路线、工位定义确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置电子作业指导书：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PDM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">图、预装提示、按车型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工序切换</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ESOP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置确认</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PDM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">图、作业指导书资料齐全</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">配置拧紧工艺：拧紧枪、程序号、拧紧数量、不合格次数、使能控制、数据采集</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拧紧工艺配置单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拧紧枪接口协议、程序号确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ATLAS</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">拧紧枪</t>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">人</t>
     </r>
     <r>
       <rPr>
@@ -1748,34 +2568,17 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">把（主动轮）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置设备采集接口：伺服压机</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台、拧紧枪</t>
+      <t xml:space="preserve">个月）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">递缇（报价含</t>
     </r>
     <r>
       <rPr>
@@ -1792,663 +2595,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">把、检测设备</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通讯参数</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">接口配置清单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">设备接口协议、通讯参数确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">压机</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CVT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">二线；国外调试费用未含，需甲方</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">设备商配合</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">配置订单管理：生产计划、工单、计划编号规则、终端客户、产品型号、数量</t>
-  </si>
-  <si>
-    <t xml:space="preserve">订单规则配置单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">订单管理规则确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置质量报表、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SPC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">统计、电子看板、日志管理、追溯查询</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">报表与看板配置单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">报表格式、看板内容确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与工厂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES/SAP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">预留接口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">标准接口协议</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">接口文档</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工厂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES/SAP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">接口文档、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">协议确认</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">预留接口，联调视甲方系统可用性</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工位单机与设备采集调试</t>
-  </si>
-  <si>
-    <t xml:space="preserve">服务器本地功能验证：登录、订单、工艺、报表、追溯、用户权限、日志</t>
-  </si>
-  <si>
-    <t xml:space="preserve">功能验证记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">基础配置完成</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">逐工位验证客户端：启动、扫码、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SOP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">显示、防错、过站、数据上传</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工位签认表</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">×15</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">工位客户端部署完成，网络连通</t>
-  </si>
-  <si>
-    <t xml:space="preserve">缺枪工位先用手工录入模式，签认表标注</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">上线打码</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">条码绑定测试：总成二维码生成、打印、扫描、绑定</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">打码绑定测试记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">打码设备、扫码枪就绪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">零件条码采集测试：零件二维码、批次码、重复校验、数量校验、特征码校验</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条码防错测试记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">零件条码规则确认，扫码枪就绪</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">★缺</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">把扫码枪的工位无法完成条码防错验证</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">过程数据采集测试：进站、出站、过站信息、工单号、序列号、工站、人员、时间</t>
-  </si>
-  <si>
-    <t xml:space="preserve">过站数据核对</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工位客户端与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通讯正常</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">拧紧数据采集测试：扭矩、角度、曲线、合格状态、螺栓遗漏查询</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拧紧曲线核对</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拧紧枪通讯正常，程序号配置完成</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ATLAS 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">把（主动轮）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">伺服压机数据采集验证：压力、位移、通讯稳定性、数据上传</t>
-  </si>
-  <si>
-    <t xml:space="preserve">压机采集记录</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">甲方</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">设备商主责，递缇远程协助</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">甲方</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">设备商</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">压机通电、网络连通、接口协议开放</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">★报价明确</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台压机仅国内调试、不含国外调试费用，现场责任界面需书面确认</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">检测设备数据采集验证：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台检测设备数据上传、结果绑定</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">检测数据记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">检测设备接口开放、通讯正常</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">电子看板验证：订单内容、计划产量、实际产量、不良率、工位状态、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SPC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">图</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">看板上线确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">看板数据源配置完成，大屏就绪</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">质量报告与追溯验证：正反向追溯、树形展示、报表导出</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Excel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、工号姓名显示</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">追溯报表核对</t>
-  </si>
-  <si>
-    <t xml:space="preserve">质量数据采集完成</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">性能验证：操作延时≤</t>
+      <t xml:space="preserve">人</t>
     </r>
     <r>
       <rPr>
@@ -2465,7 +2612,116 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">秒、数据库查询≤</t>
+      <t xml:space="preserve">个月）</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">现场交接完成，远程通道可用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">按墨西哥时差排班</t>
+  </si>
+  <si>
+    <t xml:space="preserve">试运行：连续生产，问题闭环，免费修改与升级</t>
+  </si>
+  <si>
+    <t xml:space="preserve">远程调试启动</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">生产</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个月或</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1000</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台，以先到为准</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">终验收：按技术协议逐项验收</t>
+  </si>
+  <si>
+    <t xml:space="preserve">试运行达标</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不组织验收则视为合格；争议期间除外</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">质保与运维：终验收合格起</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">年，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7×24</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">支持，</t>
     </r>
     <r>
       <rPr>
@@ -2482,574 +2738,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">秒、并发访问、故障恢复、数据不丢失</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">性能测试报告</t>
-  </si>
-  <si>
-    <t xml:space="preserve">系统稳定运行，测试数据准备</t>
-  </si>
-  <si>
-    <t xml:space="preserve">判定方法需双方事先约定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全线联调与试生产</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">联调：工件到位、保存数据、保存完成、验证完成、设备监控、生产控制</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">联调记录</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">单机调试完成，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通讯正常</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与工厂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES/SAP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">接口联调（如有）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">接口联调记录</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工厂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES/SAP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">接口可用</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">甲方系统不具备时列为遗留项</t>
-  </si>
-  <si>
-    <t xml:space="preserve">全线空运行：订单下发→打码→扫码→装配→数据采集→过站→下线→追溯</t>
-  </si>
-  <si>
-    <t xml:space="preserve">空运行记录</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">各工位、设备、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">联调完成</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">带产品试生产：小批量验证，记录</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">问题、设备采集问题、网络问题</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">试生产问题清单</t>
-  </si>
-  <si>
-    <t xml:space="preserve">空运行无重大异常，试生产物料准备</t>
-  </si>
-  <si>
-    <t xml:space="preserve">试生产物料由甲方准备</t>
-  </si>
-  <si>
-    <t xml:space="preserve">异常场景测试：设备异常、质量异常、数据异常、安灯报警、不合格拦截、高权限跳站</t>
-  </si>
-  <si>
-    <t xml:space="preserve">异常场景测试记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">异常处理逻辑配置完成</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">生产报表、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SPC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">、看板、日志、用户权限综合验证</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">综合验证记录</t>
-  </si>
-  <si>
-    <t xml:space="preserve">试生产数据积累</t>
-  </si>
-  <si>
-    <t xml:space="preserve">分角色培训：操作工、班组长、质量、维护，并交付用户操作手册</t>
-  </si>
-  <si>
-    <t xml:space="preserve">《培训计划》《用户操作手册》</t>
-  </si>
-  <si>
-    <t xml:space="preserve">系统功能验证完成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">★原计划缺培训任务，按交付物要求补充</t>
-  </si>
-  <si>
-    <t xml:space="preserve">预验收：按技术协议在杭州国内工厂进行；如已完成则做资料归档与遗留项确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">《项目预验收报告》</t>
-  </si>
-  <si>
-    <t xml:space="preserve">待确认</t>
-  </si>
-  <si>
-    <t xml:space="preserve">杭州阶段单机部署完成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">★需确认预验收是否已随一体机后到而顺延</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现场实施完成确认与交接：遗留问题清单、备件与工具移交</t>
-  </si>
-  <si>
-    <t xml:space="preserve">现场实施完成确认书</t>
-  </si>
-  <si>
-    <t xml:space="preserve">试生产与培训完成</t>
-  </si>
-  <si>
-    <t xml:space="preserve">试运行、验收与运维</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">远程调试：缺陷修复、参数优化、陪产支持（</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个月）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">调试周报</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">问题闭环记录</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">递缇（报价含</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个月）</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">现场交接完成，远程通道可用</t>
-  </si>
-  <si>
-    <t xml:space="preserve">按墨西哥时差排班</t>
-  </si>
-  <si>
-    <t xml:space="preserve">试运行：连续生产，问题闭环，免费修改与升级</t>
-  </si>
-  <si>
-    <t xml:space="preserve">《系统运行报告》</t>
-  </si>
-  <si>
-    <t xml:space="preserve">远程调试启动</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">生产</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个月或</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1000</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台，以先到为准</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">终验收：按技术协议逐项验收</t>
-  </si>
-  <si>
-    <t xml:space="preserve">《项目终验收报告》</t>
-  </si>
-  <si>
-    <t xml:space="preserve">试运行达标</t>
-  </si>
-  <si>
-    <t xml:space="preserve">不组织验收则视为合格；争议期间除外</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">质保与运维：终验收合格起</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">年，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">7×24</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">支持，</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">小时内出方案</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">《系统运维报告》</t>
   </si>
   <si>
     <t xml:space="preserve">终验收合格</t>
@@ -6205,7 +5895,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">新增“输出物”列，逐项挂接《项目实施方案》《需求报告》《蓝图设计》《详细设计方案》《实施报告》《培训计划》《用户操作手册》《系统上线报告》《安装配置维护手册》《预验收</t>
+      <t xml:space="preserve">文档按合同交付物清单单独提交（《项目实施方案》《系统需求报告》《蓝图设计》《详细设计方案》《实施报告》《培训计划》《用户操作手册》《系统上线报告》《安装配置维护手册》《预验收</t>
     </r>
     <r>
       <rPr>
@@ -6239,7 +5929,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">运维报告》</t>
+      <t xml:space="preserve">运维报告》），计划页不再单列</t>
     </r>
   </si>
   <si>
@@ -7572,10 +7262,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -7601,6 +7287,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8129,21 +7819,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="13" min="13" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="12" min="12" style="0" width="13"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8160,7 +7849,6 @@
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -8176,7 +7864,6 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -8192,7 +7879,6 @@
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
@@ -8228,134 +7914,122 @@
       <c r="K4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L5</f>
+        <v>46328</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <f aca="false">E5+D5-1</f>
+        <v>46329</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="H5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M5</f>
-        <v>46328</v>
-      </c>
-      <c r="G5" s="8" t="n">
-        <f aca="false">F5+E5-1</f>
-        <v>46329</v>
-      </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="10" t="s">
+      <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="0" t="n">
+      <c r="L5" s="0" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L6</f>
+        <v>46330</v>
+      </c>
+      <c r="F6" s="13" t="n">
+        <f aca="false">E6+D6-1</f>
+        <v>46331</v>
+      </c>
+      <c r="G6" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="I6" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="J6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="L6" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M6</f>
-        <v>46330</v>
-      </c>
-      <c r="G6" s="13" t="n">
-        <f aca="false">F6+E6-1</f>
-        <v>46331</v>
-      </c>
-      <c r="H6" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K6" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="9" t="n">
         <v>3</v>
       </c>
       <c r="C7" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L7</f>
+        <v>46332</v>
+      </c>
+      <c r="F7" s="8" t="n">
+        <f aca="false">E7+D7-1</f>
+        <v>46332</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="K7" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F7" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M7</f>
-        <v>46332</v>
-      </c>
-      <c r="G7" s="8" t="n">
-        <f aca="false">F7+E7-1</f>
-        <v>46332</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="M7" s="0" t="n">
+      <c r="L7" s="0" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8365,38 +8039,35 @@
         <v>4</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" s="15" t="n">
+        <v>33</v>
+      </c>
+      <c r="D8" s="15" t="n">
         <v>1</v>
       </c>
+      <c r="E8" s="17" t="n">
+        <f aca="false">说明与修订!$B$5+L8</f>
+        <v>46333</v>
+      </c>
       <c r="F8" s="17" t="n">
-        <f aca="false">说明与修订!$B$5+M8</f>
+        <f aca="false">E8+D8-1</f>
         <v>46333</v>
       </c>
-      <c r="G8" s="17" t="n">
-        <f aca="false">F8+E8-1</f>
-        <v>46333</v>
-      </c>
-      <c r="H8" s="16" t="s">
-        <v>33</v>
+      <c r="G8" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="I8" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="J8" s="18" t="s">
-        <v>28</v>
-      </c>
       <c r="K8" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="M8" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="L8" s="0" t="n">
         <v>5</v>
       </c>
     </row>
@@ -8406,38 +8077,35 @@
         <v>5</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9" s="9" t="n">
+        <v>36</v>
+      </c>
+      <c r="D9" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="E9" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L9</f>
+        <v>46332</v>
+      </c>
       <c r="F9" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M9</f>
-        <v>46332</v>
-      </c>
-      <c r="G9" s="8" t="n">
-        <f aca="false">F9+E9-1</f>
+        <f aca="false">E9+D9-1</f>
         <v>46333</v>
       </c>
-      <c r="H9" s="7" t="s">
-        <v>33</v>
+      <c r="G9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>37</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>38</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="M9" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="L9" s="0" t="n">
         <v>4</v>
       </c>
     </row>
@@ -8447,118 +8115,109 @@
         <v>6</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="E10" s="14" t="n">
+        <v>40</v>
+      </c>
+      <c r="D10" s="14" t="n">
         <v>4</v>
       </c>
+      <c r="E10" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L10</f>
+        <v>46334</v>
+      </c>
       <c r="F10" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M10</f>
-        <v>46334</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <f aca="false">F10+E10-1</f>
+        <f aca="false">E10+D10-1</f>
         <v>46337</v>
       </c>
-      <c r="H10" s="12" t="s">
-        <v>26</v>
+      <c r="G10" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="14" t="s">
+        <v>41</v>
       </c>
       <c r="I10" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J10" s="12" t="s">
+        <v>42</v>
       </c>
       <c r="K10" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="M10" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="L10" s="0" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="C11" s="21" t="s">
-        <v>51</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="E11" s="20" t="n">
+      <c r="C11" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="22" t="n">
-        <f aca="false">说明与修订!$B$5+M11</f>
+      <c r="E11" s="21" t="n">
+        <f aca="false">说明与修订!$B$5+L11</f>
         <v>46336</v>
       </c>
-      <c r="G11" s="22" t="n">
-        <f aca="false">F11+E11-1</f>
+      <c r="F11" s="21" t="n">
+        <f aca="false">E11+D11-1</f>
         <v>46338</v>
       </c>
-      <c r="H11" s="21" t="s">
-        <v>33</v>
+      <c r="G11" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="22" t="s">
+        <v>45</v>
       </c>
       <c r="I11" s="23" t="s">
-        <v>53</v>
-      </c>
-      <c r="J11" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="L11" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="M11" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="L11" s="0" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="14" t="n">
         <v>8</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="14" t="n">
+        <v>48</v>
+      </c>
+      <c r="D12" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E12" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L12</f>
+        <v>46338</v>
+      </c>
       <c r="F12" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M12</f>
+        <f aca="false">E12+D12-1</f>
         <v>46338</v>
       </c>
-      <c r="G12" s="13" t="n">
-        <f aca="false">F12+E12-1</f>
-        <v>46338</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>26</v>
+      <c r="G12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="I12" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K12" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" s="12"/>
-      <c r="M12" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J12" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="K12" s="12"/>
+      <c r="L12" s="0" t="n">
         <v>10</v>
       </c>
     </row>
@@ -8568,676 +8227,625 @@
         <v>9</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="9" t="n">
+        <v>51</v>
+      </c>
+      <c r="D13" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="E13" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L13</f>
+        <v>46338</v>
+      </c>
       <c r="F13" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M13</f>
-        <v>46338</v>
-      </c>
-      <c r="G13" s="8" t="n">
-        <f aca="false">F13+E13-1</f>
+        <f aca="false">E13+D13-1</f>
         <v>46339</v>
       </c>
-      <c r="H13" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>20</v>
+      <c r="G13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="K13" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="M13" s="0" t="n">
+        <v>54</v>
+      </c>
+      <c r="L13" s="0" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="14" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="14" t="n">
+        <v>55</v>
+      </c>
+      <c r="D14" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="E14" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L14</f>
+        <v>46333</v>
+      </c>
       <c r="F14" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M14</f>
-        <v>46333</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <f aca="false">F14+E14-1</f>
+        <f aca="false">E14+D14-1</f>
         <v>46334</v>
       </c>
-      <c r="H14" s="12" t="s">
-        <v>26</v>
+      <c r="G14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>49</v>
       </c>
       <c r="I14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K14" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="L14" s="12"/>
-      <c r="M14" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J14" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="K14" s="12"/>
+      <c r="L14" s="0" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25" t="s">
-        <v>68</v>
+      <c r="A15" s="24" t="s">
+        <v>57</v>
       </c>
       <c r="B15" s="9" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="9" t="n">
+        <v>58</v>
+      </c>
+      <c r="D15" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="E15" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L15</f>
+        <v>46340</v>
+      </c>
       <c r="F15" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M15</f>
-        <v>46340</v>
-      </c>
-      <c r="G15" s="8" t="n">
-        <f aca="false">F15+E15-1</f>
+        <f aca="false">E15+D15-1</f>
         <v>46341</v>
       </c>
-      <c r="H15" s="7" t="s">
-        <v>33</v>
+      <c r="G15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="L15" s="7"/>
-      <c r="M15" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="0" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25"/>
+      <c r="A16" s="24"/>
       <c r="B16" s="14" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="14" t="n">
+        <v>60</v>
+      </c>
+      <c r="D16" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="E16" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L16</f>
+        <v>46340</v>
+      </c>
       <c r="F16" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M16</f>
-        <v>46340</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <f aca="false">F16+E16-1</f>
+        <f aca="false">E16+D16-1</f>
         <v>46341</v>
       </c>
-      <c r="H16" s="12" t="s">
-        <v>33</v>
+      <c r="G16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J16" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J16" s="12" t="s">
+        <v>61</v>
       </c>
       <c r="K16" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="M16" s="0" t="n">
+        <v>62</v>
+      </c>
+      <c r="L16" s="0" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25"/>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="24"/>
       <c r="B17" s="9" t="n">
         <v>13</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="E17" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="D17" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E17" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L17</f>
+        <v>46342</v>
+      </c>
       <c r="F17" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M17</f>
+        <f aca="false">E17+D17-1</f>
         <v>46342</v>
       </c>
-      <c r="G17" s="8" t="n">
-        <f aca="false">F17+E17-1</f>
-        <v>46342</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>33</v>
+      <c r="G17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I17" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J17" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K17" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="M17" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="L17" s="0" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25"/>
+      <c r="A18" s="24"/>
       <c r="B18" s="14" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="14" t="n">
+        <v>66</v>
+      </c>
+      <c r="D18" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E18" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L18</f>
+        <v>46342</v>
+      </c>
       <c r="F18" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M18</f>
+        <f aca="false">E18+D18-1</f>
         <v>46342</v>
       </c>
-      <c r="G18" s="13" t="n">
-        <f aca="false">F18+E18-1</f>
-        <v>46342</v>
-      </c>
-      <c r="H18" s="12" t="s">
-        <v>33</v>
+      <c r="G18" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I18" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J18" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K18" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J18" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="K18" s="12"/>
+      <c r="L18" s="0" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="25"/>
+      <c r="A19" s="24"/>
       <c r="B19" s="9" t="n">
         <v>15</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E19" s="9" t="n">
+        <v>68</v>
+      </c>
+      <c r="D19" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E19" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L19</f>
+        <v>46343</v>
+      </c>
       <c r="F19" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M19</f>
+        <f aca="false">E19+D19-1</f>
         <v>46343</v>
       </c>
-      <c r="G19" s="8" t="n">
-        <f aca="false">F19+E19-1</f>
-        <v>46343</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>33</v>
+      <c r="G19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J19" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="L19" s="7"/>
-      <c r="M19" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="0" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="25"/>
+      <c r="A20" s="24"/>
       <c r="B20" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="E20" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="D20" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E20" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L20</f>
+        <v>46344</v>
+      </c>
       <c r="F20" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M20</f>
+        <f aca="false">E20+D20-1</f>
         <v>46344</v>
       </c>
-      <c r="G20" s="13" t="n">
-        <f aca="false">F20+E20-1</f>
-        <v>46344</v>
-      </c>
-      <c r="H20" s="12" t="s">
-        <v>33</v>
+      <c r="G20" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I20" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J20" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K20" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="L20" s="12"/>
-      <c r="M20" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J20" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="K20" s="12"/>
+      <c r="L20" s="0" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="25"/>
+    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="24"/>
       <c r="B21" s="9" t="n">
         <v>17</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21" s="9" t="n">
+        <v>72</v>
+      </c>
+      <c r="D21" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E21" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L21</f>
+        <v>46344</v>
+      </c>
       <c r="F21" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M21</f>
+        <f aca="false">E21+D21-1</f>
         <v>46344</v>
       </c>
-      <c r="G21" s="8" t="n">
-        <f aca="false">F21+E21-1</f>
-        <v>46344</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>33</v>
+      <c r="G21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H21" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I21" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J21" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="L21" s="7"/>
-      <c r="M21" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="0" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25"/>
+      <c r="A22" s="24"/>
       <c r="B22" s="14" t="n">
         <v>18</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E22" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="D22" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E22" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L22</f>
+        <v>46345</v>
+      </c>
       <c r="F22" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M22</f>
+        <f aca="false">E22+D22-1</f>
         <v>46345</v>
       </c>
-      <c r="G22" s="13" t="n">
-        <f aca="false">F22+E22-1</f>
-        <v>46345</v>
-      </c>
-      <c r="H22" s="12" t="s">
-        <v>33</v>
+      <c r="G22" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I22" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J22" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K22" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="L22" s="12"/>
-      <c r="M22" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J22" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="K22" s="12"/>
+      <c r="L22" s="0" t="n">
         <v>17</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25"/>
+      <c r="A23" s="24"/>
       <c r="B23" s="9" t="n">
         <v>19</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E23" s="9" t="n">
+        <v>76</v>
+      </c>
+      <c r="D23" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E23" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L23</f>
+        <v>46346</v>
+      </c>
       <c r="F23" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M23</f>
+        <f aca="false">E23+D23-1</f>
         <v>46346</v>
       </c>
-      <c r="G23" s="8" t="n">
-        <f aca="false">F23+E23-1</f>
-        <v>46346</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>33</v>
+      <c r="G23" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I23" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K23" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="L23" s="7"/>
-      <c r="M23" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J23" s="25" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="0" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="25"/>
+      <c r="A24" s="24"/>
       <c r="B24" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="D24" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E24" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L24</f>
+        <v>46346</v>
+      </c>
       <c r="F24" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M24</f>
+        <f aca="false">E24+D24-1</f>
         <v>46346</v>
       </c>
-      <c r="G24" s="13" t="n">
-        <f aca="false">F24+E24-1</f>
-        <v>46346</v>
-      </c>
-      <c r="H24" s="12" t="s">
-        <v>33</v>
+      <c r="G24" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J24" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K24" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="L24" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="M24" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J24" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="K24" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="L24" s="0" t="n">
         <v>18</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="25"/>
+      <c r="A25" s="24"/>
       <c r="B25" s="9" t="n">
         <v>21</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="E25" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="D25" s="9" t="n">
         <v>2</v>
       </c>
+      <c r="E25" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L25</f>
+        <v>46347</v>
+      </c>
       <c r="F25" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M25</f>
-        <v>46347</v>
-      </c>
-      <c r="G25" s="8" t="n">
-        <f aca="false">F25+E25-1</f>
+        <f aca="false">E25+D25-1</f>
         <v>46348</v>
       </c>
-      <c r="H25" s="7" t="s">
-        <v>33</v>
+      <c r="G25" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J25" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>82</v>
       </c>
       <c r="K25" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="M25" s="0" t="n">
+        <v>83</v>
+      </c>
+      <c r="L25" s="0" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25"/>
+      <c r="A26" s="24"/>
       <c r="B26" s="14" t="n">
         <v>22</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E26" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="D26" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E26" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L26</f>
+        <v>46347</v>
+      </c>
       <c r="F26" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M26</f>
+        <f aca="false">E26+D26-1</f>
         <v>46347</v>
       </c>
-      <c r="G26" s="13" t="n">
-        <f aca="false">F26+E26-1</f>
-        <v>46347</v>
-      </c>
-      <c r="H26" s="12" t="s">
-        <v>33</v>
+      <c r="G26" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J26" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="L26" s="12"/>
-      <c r="M26" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J26" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="K26" s="12"/>
+      <c r="L26" s="0" t="n">
         <v>19</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25"/>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24"/>
       <c r="B27" s="9" t="n">
         <v>23</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E27" s="9" t="n">
+        <v>86</v>
+      </c>
+      <c r="D27" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E27" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L27</f>
+        <v>46348</v>
+      </c>
       <c r="F27" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M27</f>
+        <f aca="false">E27+D27-1</f>
         <v>46348</v>
       </c>
-      <c r="G27" s="8" t="n">
-        <f aca="false">F27+E27-1</f>
-        <v>46348</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>33</v>
+      <c r="G27" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J27" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="L27" s="7"/>
-      <c r="M27" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J27" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="K27" s="7"/>
+      <c r="L27" s="0" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="25"/>
+      <c r="A28" s="24"/>
       <c r="B28" s="14" t="n">
         <v>24</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>113</v>
-      </c>
-      <c r="E28" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="D28" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E28" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L28</f>
+        <v>46349</v>
+      </c>
       <c r="F28" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M28</f>
+        <f aca="false">E28+D28-1</f>
         <v>46349</v>
       </c>
-      <c r="G28" s="13" t="n">
-        <f aca="false">F28+E28-1</f>
-        <v>46349</v>
-      </c>
-      <c r="H28" s="12" t="s">
-        <v>33</v>
+      <c r="G28" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I28" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J28" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>89</v>
       </c>
       <c r="K28" s="12" t="s">
-        <v>114</v>
-      </c>
-      <c r="L28" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="M28" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="L28" s="0" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="B29" s="9" t="n">
         <v>25</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E29" s="9" t="n">
+        <v>92</v>
+      </c>
+      <c r="D29" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E29" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L29</f>
+        <v>46350</v>
+      </c>
       <c r="F29" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M29</f>
+        <f aca="false">E29+D29-1</f>
         <v>46350</v>
       </c>
-      <c r="G29" s="8" t="n">
-        <f aca="false">F29+E29-1</f>
-        <v>46350</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>33</v>
+      <c r="G29" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I29" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="L29" s="7"/>
-      <c r="M29" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J29" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="0" t="n">
         <v>22</v>
       </c>
     </row>
@@ -9247,77 +8855,71 @@
         <v>26</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>121</v>
-      </c>
-      <c r="E30" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="D30" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="E30" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L30</f>
+        <v>46351</v>
+      </c>
       <c r="F30" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M30</f>
-        <v>46351</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <f aca="false">F30+E30-1</f>
+        <f aca="false">E30+D30-1</f>
         <v>46352</v>
       </c>
-      <c r="H30" s="12" t="s">
-        <v>33</v>
+      <c r="G30" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I30" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J30" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J30" s="12" t="s">
+        <v>95</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="M30" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="L30" s="0" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="9" t="n">
         <v>27</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="E31" s="9" t="n">
+        <v>97</v>
+      </c>
+      <c r="D31" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E31" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L31</f>
+        <v>46351</v>
+      </c>
       <c r="F31" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M31</f>
+        <f aca="false">E31+D31-1</f>
         <v>46351</v>
       </c>
-      <c r="G31" s="8" t="n">
-        <f aca="false">F31+E31-1</f>
-        <v>46351</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>33</v>
+      <c r="G31" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H31" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="I31" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J31" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="L31" s="7"/>
-      <c r="M31" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="0" t="n">
         <v>23</v>
       </c>
     </row>
@@ -9327,38 +8929,35 @@
         <v>28</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="E32" s="14" t="n">
+        <v>99</v>
+      </c>
+      <c r="D32" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E32" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L32</f>
+        <v>46352</v>
+      </c>
       <c r="F32" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M32</f>
+        <f aca="false">E32+D32-1</f>
         <v>46352</v>
       </c>
-      <c r="G32" s="13" t="n">
-        <f aca="false">F32+E32-1</f>
-        <v>46352</v>
-      </c>
-      <c r="H32" s="12" t="s">
-        <v>33</v>
+      <c r="G32" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I32" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J32" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J32" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="L32" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="M32" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="L32" s="0" t="n">
         <v>24</v>
       </c>
     </row>
@@ -9368,36 +8967,33 @@
         <v>29</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="E33" s="9" t="n">
+        <v>102</v>
+      </c>
+      <c r="D33" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E33" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L33</f>
+        <v>46353</v>
+      </c>
       <c r="F33" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M33</f>
+        <f aca="false">E33+D33-1</f>
         <v>46353</v>
       </c>
-      <c r="G33" s="8" t="n">
-        <f aca="false">F33+E33-1</f>
-        <v>46353</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>33</v>
+      <c r="G33" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J33" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="L33" s="7"/>
-      <c r="M33" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="0" t="n">
         <v>25</v>
       </c>
     </row>
@@ -9407,118 +9003,109 @@
         <v>30</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="E34" s="14" t="n">
+        <v>104</v>
+      </c>
+      <c r="D34" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E34" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L34</f>
+        <v>46354</v>
+      </c>
       <c r="F34" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M34</f>
+        <f aca="false">E34+D34-1</f>
         <v>46354</v>
       </c>
-      <c r="G34" s="13" t="n">
-        <f aca="false">F34+E34-1</f>
-        <v>46354</v>
-      </c>
-      <c r="H34" s="12" t="s">
-        <v>33</v>
+      <c r="G34" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H34" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I34" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J34" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K34" s="12" t="s">
-        <v>136</v>
-      </c>
-      <c r="L34" s="19" t="s">
-        <v>137</v>
-      </c>
-      <c r="M34" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J34" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="K34" s="26" t="s">
+        <v>106</v>
+      </c>
+      <c r="L34" s="0" t="n">
         <v>26</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
-      <c r="B35" s="23" t="n">
+      <c r="B35" s="22" t="n">
         <v>31</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>138</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="23" t="n">
+      <c r="C35" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="D35" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="F35" s="22" t="n">
-        <f aca="false">说明与修订!$B$5+M35</f>
+      <c r="E35" s="21" t="n">
+        <f aca="false">说明与修订!$B$5+L35</f>
         <v>46354</v>
       </c>
-      <c r="G35" s="22" t="n">
-        <f aca="false">F35+E35-1</f>
+      <c r="F35" s="21" t="n">
+        <f aca="false">E35+D35-1</f>
         <v>46355</v>
       </c>
-      <c r="H35" s="21" t="s">
-        <v>140</v>
+      <c r="G35" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H35" s="22" t="s">
+        <v>109</v>
       </c>
       <c r="I35" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="J35" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="L35" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="M35" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="L35" s="0" t="n">
         <v>26</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
       <c r="B36" s="14" t="n">
         <v>32</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="E36" s="14" t="n">
+        <v>112</v>
+      </c>
+      <c r="D36" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E36" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L36</f>
+        <v>46355</v>
+      </c>
       <c r="F36" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M36</f>
+        <f aca="false">E36+D36-1</f>
         <v>46355</v>
       </c>
-      <c r="G36" s="13" t="n">
-        <f aca="false">F36+E36-1</f>
-        <v>46355</v>
-      </c>
-      <c r="H36" s="12" t="s">
-        <v>33</v>
+      <c r="G36" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H36" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I36" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J36" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K36" s="12" t="s">
-        <v>146</v>
-      </c>
-      <c r="L36" s="12"/>
-      <c r="M36" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J36" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="K36" s="12"/>
+      <c r="L36" s="0" t="n">
         <v>27</v>
       </c>
     </row>
@@ -9528,36 +9115,33 @@
         <v>33</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="E37" s="9" t="n">
+        <v>114</v>
+      </c>
+      <c r="D37" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E37" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L37</f>
+        <v>46356</v>
+      </c>
       <c r="F37" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M37</f>
+        <f aca="false">E37+D37-1</f>
         <v>46356</v>
       </c>
-      <c r="G37" s="8" t="n">
-        <f aca="false">F37+E37-1</f>
-        <v>46356</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>33</v>
+      <c r="G37" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I37" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J37" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K37" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="L37" s="7"/>
-      <c r="M37" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="K37" s="7"/>
+      <c r="L37" s="0" t="n">
         <v>28</v>
       </c>
     </row>
@@ -9567,36 +9151,33 @@
         <v>34</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="E38" s="14" t="n">
+        <v>116</v>
+      </c>
+      <c r="D38" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E38" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L38</f>
+        <v>46356</v>
+      </c>
       <c r="F38" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M38</f>
+        <f aca="false">E38+D38-1</f>
         <v>46356</v>
       </c>
-      <c r="G38" s="13" t="n">
-        <f aca="false">F38+E38-1</f>
-        <v>46356</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>33</v>
+      <c r="G38" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H38" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I38" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K38" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="L38" s="12"/>
-      <c r="M38" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="K38" s="12"/>
+      <c r="L38" s="0" t="n">
         <v>28</v>
       </c>
     </row>
@@ -9606,120 +9187,111 @@
         <v>35</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="E39" s="9" t="n">
+        <v>118</v>
+      </c>
+      <c r="D39" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E39" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L39</f>
+        <v>46357</v>
+      </c>
       <c r="F39" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M39</f>
+        <f aca="false">E39+D39-1</f>
         <v>46357</v>
       </c>
-      <c r="G39" s="8" t="n">
-        <f aca="false">F39+E39-1</f>
-        <v>46357</v>
-      </c>
-      <c r="H39" s="7" t="s">
-        <v>33</v>
+      <c r="G39" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I39" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J39" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>119</v>
       </c>
       <c r="K39" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="L39" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="M39" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="L39" s="0" t="n">
         <v>29</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="C40" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="E40" s="14" t="n">
+      <c r="C40" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="D40" s="14" t="n">
         <v>2</v>
       </c>
+      <c r="E40" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L40</f>
+        <v>46358</v>
+      </c>
       <c r="F40" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M40</f>
-        <v>46358</v>
-      </c>
-      <c r="G40" s="13" t="n">
-        <f aca="false">F40+E40-1</f>
+        <f aca="false">E40+D40-1</f>
         <v>46359</v>
       </c>
-      <c r="H40" s="12" t="s">
-        <v>33</v>
+      <c r="G40" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H40" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="I40" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K40" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="L40" s="12"/>
-      <c r="M40" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="K40" s="12"/>
+      <c r="L40" s="0" t="n">
         <v>30</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
       <c r="B41" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="E41" s="9" t="n">
+      <c r="C41" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D41" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E41" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L41</f>
+        <v>46359</v>
+      </c>
       <c r="F41" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M41</f>
+        <f aca="false">E41+D41-1</f>
         <v>46359</v>
       </c>
-      <c r="G41" s="8" t="n">
-        <f aca="false">F41+E41-1</f>
-        <v>46359</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>33</v>
+      <c r="G41" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="I41" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J41" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="L41" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="M41" s="0" t="n">
+        <v>126</v>
+      </c>
+      <c r="L41" s="0" t="n">
         <v>31</v>
       </c>
     </row>
@@ -9729,77 +9301,71 @@
         <v>38</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>165</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E42" s="14" t="n">
+        <v>127</v>
+      </c>
+      <c r="D42" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E42" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L42</f>
+        <v>46360</v>
+      </c>
       <c r="F42" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M42</f>
+        <f aca="false">E42+D42-1</f>
         <v>46360</v>
       </c>
-      <c r="G42" s="13" t="n">
-        <f aca="false">F42+E42-1</f>
-        <v>46360</v>
-      </c>
-      <c r="H42" s="12" t="s">
-        <v>19</v>
+      <c r="G42" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H42" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="I42" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J42" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K42" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="L42" s="12"/>
-      <c r="M42" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J42" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="K42" s="12"/>
+      <c r="L42" s="0" t="n">
         <v>32</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
-      <c r="B43" s="23" t="n">
+      <c r="B43" s="22" t="n">
         <v>39</v>
       </c>
-      <c r="C43" s="21" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>169</v>
-      </c>
-      <c r="E43" s="23" t="n">
+      <c r="C43" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="D43" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="F43" s="22" t="n">
-        <f aca="false">说明与修订!$B$5+M43</f>
+      <c r="E43" s="21" t="n">
+        <f aca="false">说明与修订!$B$5+L43</f>
         <v>46361</v>
       </c>
-      <c r="G43" s="22" t="n">
-        <f aca="false">F43+E43-1</f>
+      <c r="F43" s="21" t="n">
+        <f aca="false">E43+D43-1</f>
         <v>46362</v>
       </c>
-      <c r="H43" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I43" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="J43" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="K43" s="21" t="s">
-        <v>170</v>
-      </c>
-      <c r="L43" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="M43" s="0" t="n">
+      <c r="G43" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H43" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I43" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="K43" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="L43" s="0" t="n">
         <v>33</v>
       </c>
     </row>
@@ -9809,75 +9375,69 @@
         <v>40</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="E44" s="14" t="n">
+        <v>132</v>
+      </c>
+      <c r="D44" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E44" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L44</f>
+        <v>46361</v>
+      </c>
       <c r="F44" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M44</f>
+        <f aca="false">E44+D44-1</f>
         <v>46361</v>
       </c>
-      <c r="G44" s="13" t="n">
-        <f aca="false">F44+E44-1</f>
-        <v>46361</v>
-      </c>
-      <c r="H44" s="12" t="s">
+      <c r="G44" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="H44" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I44" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="K44" s="12"/>
+      <c r="L44" s="0" t="n">
         <v>33</v>
       </c>
-      <c r="I44" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J44" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K44" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="L44" s="12"/>
-      <c r="M44" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
       <c r="B45" s="9" t="n">
         <v>41</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="E45" s="9" t="n">
+        <v>134</v>
+      </c>
+      <c r="D45" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E45" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L45</f>
+        <v>46363</v>
+      </c>
       <c r="F45" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M45</f>
+        <f aca="false">E45+D45-1</f>
         <v>46363</v>
       </c>
-      <c r="G45" s="8" t="n">
-        <f aca="false">F45+E45-1</f>
-        <v>46363</v>
-      </c>
-      <c r="H45" s="7" t="s">
-        <v>33</v>
+      <c r="G45" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>30</v>
       </c>
       <c r="I45" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J45" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="K45" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="L45" s="7"/>
-      <c r="M45" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="K45" s="7"/>
+      <c r="L45" s="0" t="n">
         <v>35</v>
       </c>
     </row>
@@ -9887,243 +9447,225 @@
         <v>42</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>179</v>
-      </c>
-      <c r="E46" s="18" t="n">
+        <v>136</v>
+      </c>
+      <c r="D46" s="18" t="n">
         <v>2</v>
       </c>
+      <c r="E46" s="17" t="n">
+        <f aca="false">说明与修订!$B$5+L46</f>
+        <v>46363</v>
+      </c>
       <c r="F46" s="17" t="n">
-        <f aca="false">说明与修订!$B$5+M46</f>
-        <v>46363</v>
-      </c>
-      <c r="G46" s="17" t="n">
-        <f aca="false">F46+E46-1</f>
+        <f aca="false">E46+D46-1</f>
         <v>46364</v>
       </c>
-      <c r="H46" s="16" t="s">
-        <v>33</v>
+      <c r="G46" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H46" s="18" t="s">
+        <v>30</v>
       </c>
       <c r="I46" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="J46" s="18" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J46" s="16" t="s">
+        <v>137</v>
       </c>
       <c r="K46" s="16" t="s">
-        <v>180</v>
-      </c>
-      <c r="L46" s="16" t="s">
-        <v>181</v>
-      </c>
-      <c r="M46" s="0" t="n">
+        <v>138</v>
+      </c>
+      <c r="L46" s="0" t="n">
         <v>35</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
-      <c r="B47" s="23" t="n">
+      <c r="B47" s="22" t="n">
         <v>43</v>
       </c>
-      <c r="C47" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="D47" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="E47" s="23" t="n">
+      <c r="C47" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D47" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="22" t="n">
-        <f aca="false">说明与修订!$B$5+M47</f>
+      <c r="E47" s="21" t="n">
+        <f aca="false">说明与修订!$B$5+L47</f>
         <v>46364</v>
       </c>
-      <c r="G47" s="22" t="n">
-        <f aca="false">F47+E47-1</f>
+      <c r="F47" s="21" t="n">
+        <f aca="false">E47+D47-1</f>
         <v>46364</v>
       </c>
-      <c r="H47" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I47" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="J47" s="27" t="s">
-        <v>184</v>
-      </c>
-      <c r="K47" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="L47" s="21" t="s">
-        <v>186</v>
-      </c>
-      <c r="M47" s="0" t="n">
+      <c r="G47" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="27" t="s">
+        <v>140</v>
+      </c>
+      <c r="J47" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="K47" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="L47" s="0" t="n">
         <v>36</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
       <c r="B48" s="14" t="n">
         <v>44</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>187</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="E48" s="14" t="n">
+        <v>143</v>
+      </c>
+      <c r="D48" s="14" t="n">
         <v>1</v>
       </c>
+      <c r="E48" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L48</f>
+        <v>46365</v>
+      </c>
       <c r="F48" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M48</f>
+        <f aca="false">E48+D48-1</f>
         <v>46365</v>
       </c>
-      <c r="G48" s="13" t="n">
-        <f aca="false">F48+E48-1</f>
-        <v>46365</v>
-      </c>
-      <c r="H48" s="12" t="s">
-        <v>18</v>
+      <c r="G48" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="H48" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="I48" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J48" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="K48" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="L48" s="12"/>
-      <c r="M48" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="J48" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="K48" s="12"/>
+      <c r="L48" s="0" t="n">
         <v>37</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="B49" s="9" t="n">
         <v>45</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="D49" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="E49" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="D49" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="E49" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L49</f>
+        <v>46366</v>
+      </c>
       <c r="F49" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M49</f>
-        <v>46366</v>
-      </c>
-      <c r="G49" s="8" t="n">
-        <f aca="false">F49+E49-1</f>
+        <f aca="false">E49+D49-1</f>
         <v>46385</v>
       </c>
-      <c r="H49" s="7" t="s">
-        <v>33</v>
+      <c r="G49" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49" s="9" t="s">
+        <v>147</v>
       </c>
       <c r="I49" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="J49" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>148</v>
       </c>
       <c r="K49" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="L49" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="M49" s="0" t="n">
+        <v>149</v>
+      </c>
+      <c r="L49" s="0" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
       <c r="B50" s="14" t="n">
         <v>46</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="E50" s="14" t="n">
+        <v>150</v>
+      </c>
+      <c r="D50" s="14" t="n">
         <v>90</v>
       </c>
+      <c r="E50" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L50</f>
+        <v>46366</v>
+      </c>
       <c r="F50" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M50</f>
-        <v>46366</v>
-      </c>
-      <c r="G50" s="13" t="n">
-        <f aca="false">F50+E50-1</f>
+        <f aca="false">E50+D50-1</f>
         <v>46455</v>
       </c>
-      <c r="H50" s="12" t="s">
-        <v>19</v>
+      <c r="G50" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="H50" s="14" t="s">
+        <v>17</v>
       </c>
       <c r="I50" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J50" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J50" s="12" t="s">
+        <v>151</v>
       </c>
       <c r="K50" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="L50" s="12" t="s">
-        <v>199</v>
-      </c>
-      <c r="M50" s="0" t="n">
+        <v>152</v>
+      </c>
+      <c r="L50" s="0" t="n">
         <v>38</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
       <c r="B51" s="9" t="n">
         <v>47</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="D51" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="E51" s="9" t="n">
+        <v>153</v>
+      </c>
+      <c r="D51" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="E51" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L51</f>
+        <v>46456</v>
+      </c>
       <c r="F51" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+M51</f>
+        <f aca="false">E51+D51-1</f>
         <v>46456</v>
       </c>
-      <c r="G51" s="8" t="n">
-        <f aca="false">F51+E51-1</f>
-        <v>46456</v>
-      </c>
-      <c r="H51" s="7" t="s">
-        <v>19</v>
+      <c r="G51" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H51" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="I51" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="J51" s="9" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>154</v>
       </c>
       <c r="K51" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="L51" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="M51" s="0" t="n">
+        <v>155</v>
+      </c>
+      <c r="L51" s="0" t="n">
         <v>128</v>
       </c>
     </row>
@@ -10133,44 +9675,41 @@
         <v>48</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>204</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="E52" s="14" t="n">
+        <v>156</v>
+      </c>
+      <c r="D52" s="14" t="n">
         <v>365</v>
       </c>
+      <c r="E52" s="13" t="n">
+        <f aca="false">说明与修订!$B$5+L52</f>
+        <v>46457</v>
+      </c>
       <c r="F52" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+M52</f>
-        <v>46457</v>
-      </c>
-      <c r="G52" s="13" t="n">
-        <f aca="false">F52+E52-1</f>
+        <f aca="false">E52+D52-1</f>
         <v>46821</v>
       </c>
-      <c r="H52" s="12" t="s">
-        <v>34</v>
+      <c r="G52" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="H52" s="14" t="s">
+        <v>30</v>
       </c>
       <c r="I52" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="J52" s="14" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="J52" s="12" t="s">
+        <v>157</v>
       </c>
       <c r="K52" s="12" t="s">
-        <v>206</v>
-      </c>
-      <c r="L52" s="12" t="s">
-        <v>207</v>
-      </c>
-      <c r="M52" s="0" t="n">
+        <v>158</v>
+      </c>
+      <c r="L52" s="0" t="n">
         <v>129</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="28" t="s">
-        <v>208</v>
+        <v>159</v>
       </c>
       <c r="B53" s="28"/>
       <c r="C53" s="28"/>
@@ -10182,14 +9721,13 @@
       <c r="I53" s="29"/>
       <c r="J53" s="29"/>
       <c r="K53" s="29"/>
-      <c r="L53" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L52"/>
+  <autoFilter ref="A4:K52"/>
   <mergeCells count="9">
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
     <mergeCell ref="A6:A14"/>
     <mergeCell ref="A15:A28"/>
     <mergeCell ref="A29:A39"/>
@@ -10198,7 +9736,7 @@
     <mergeCell ref="A53:D53"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J5:J52" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I5:I52" type="list">
       <formula1>"未开始,进行中,已完成,受阻,待客户确认,待确认"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10231,7 +9769,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>209</v>
+        <v>160</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -10268,7 +9806,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>210</v>
+        <v>161</v>
       </c>
       <c r="E2" s="32" t="str">
         <f aca="false">TEXT(说明与修订!$B$5+7*0,"mm/dd")</f>
@@ -10356,10 +9894,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="D3" s="33" t="n">
         <v>2</v>
@@ -10390,10 +9928,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>212</v>
+        <v>163</v>
       </c>
       <c r="D4" s="33" t="n">
         <v>2</v>
@@ -10424,10 +9962,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>213</v>
+        <v>164</v>
       </c>
       <c r="D5" s="33" t="n">
         <v>1</v>
@@ -10458,10 +9996,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>214</v>
+        <v>165</v>
       </c>
       <c r="D6" s="33" t="n">
         <v>1</v>
@@ -10492,10 +10030,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>215</v>
+        <v>166</v>
       </c>
       <c r="D7" s="33" t="n">
         <v>2</v>
@@ -10526,10 +10064,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>216</v>
+        <v>167</v>
       </c>
       <c r="D8" s="33" t="n">
         <v>4</v>
@@ -10560,10 +10098,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>217</v>
+        <v>168</v>
       </c>
       <c r="D9" s="33" t="n">
         <v>3</v>
@@ -10594,10 +10132,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>218</v>
+        <v>169</v>
       </c>
       <c r="D10" s="33" t="n">
         <v>1</v>
@@ -10628,10 +10166,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>219</v>
+        <v>170</v>
       </c>
       <c r="D11" s="33" t="n">
         <v>2</v>
@@ -10662,10 +10200,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="34" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D12" s="33" t="n">
         <v>2</v>
@@ -10696,10 +10234,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>221</v>
+        <v>172</v>
       </c>
       <c r="D13" s="33" t="n">
         <v>2</v>
@@ -10730,10 +10268,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>222</v>
+        <v>173</v>
       </c>
       <c r="D14" s="33" t="n">
         <v>2</v>
@@ -10764,10 +10302,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D15" s="33" t="n">
         <v>1</v>
@@ -10798,10 +10336,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>223</v>
+        <v>174</v>
       </c>
       <c r="D16" s="33" t="n">
         <v>1</v>
@@ -10832,10 +10370,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="D17" s="33" t="n">
         <v>1</v>
@@ -10866,10 +10404,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>86</v>
+        <v>70</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>1</v>
@@ -10900,10 +10438,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="D19" s="33" t="n">
         <v>1</v>
@@ -10934,10 +10472,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D20" s="33" t="n">
         <v>1</v>
@@ -10968,10 +10506,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>225</v>
+        <v>176</v>
       </c>
       <c r="D21" s="33" t="n">
         <v>1</v>
@@ -11002,10 +10540,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="D22" s="33" t="n">
         <v>1</v>
@@ -11036,10 +10574,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="D23" s="33" t="n">
         <v>2</v>
@@ -11070,10 +10608,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="D24" s="33" t="n">
         <v>1</v>
@@ -11104,10 +10642,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>227</v>
+        <v>178</v>
       </c>
       <c r="D25" s="33" t="n">
         <v>1</v>
@@ -11138,10 +10676,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>220</v>
+        <v>171</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>228</v>
+        <v>179</v>
       </c>
       <c r="D26" s="33" t="n">
         <v>1</v>
@@ -11172,10 +10710,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>117</v>
+        <v>92</v>
       </c>
       <c r="D27" s="33" t="n">
         <v>1</v>
@@ -11206,10 +10744,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>229</v>
+        <v>180</v>
       </c>
       <c r="D28" s="33" t="n">
         <v>2</v>
@@ -11240,10 +10778,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>230</v>
+        <v>181</v>
       </c>
       <c r="D29" s="33" t="n">
         <v>1</v>
@@ -11274,10 +10812,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C30" s="35" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D30" s="33" t="n">
         <v>1</v>
@@ -11308,10 +10846,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>131</v>
+        <v>102</v>
       </c>
       <c r="D31" s="33" t="n">
         <v>1</v>
@@ -11342,10 +10880,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="D32" s="33" t="n">
         <v>1</v>
@@ -11376,10 +10914,10 @@
         <v>31</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="D33" s="33" t="n">
         <v>2</v>
@@ -11410,10 +10948,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>231</v>
+        <v>182</v>
       </c>
       <c r="D34" s="33" t="n">
         <v>1</v>
@@ -11444,10 +10982,10 @@
         <v>33</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>232</v>
+        <v>183</v>
       </c>
       <c r="D35" s="33" t="n">
         <v>1</v>
@@ -11478,10 +11016,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>233</v>
+        <v>184</v>
       </c>
       <c r="D36" s="33" t="n">
         <v>1</v>
@@ -11512,10 +11050,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="D37" s="33" t="n">
         <v>1</v>
@@ -11546,10 +11084,10 @@
         <v>36</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C38" s="42" t="s">
-        <v>235</v>
+        <v>186</v>
       </c>
       <c r="D38" s="33" t="n">
         <v>2</v>
@@ -11580,10 +11118,10 @@
         <v>37</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C39" s="42" t="s">
-        <v>236</v>
+        <v>187</v>
       </c>
       <c r="D39" s="33" t="n">
         <v>1</v>
@@ -11614,10 +11152,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>165</v>
+        <v>127</v>
       </c>
       <c r="D40" s="33" t="n">
         <v>1</v>
@@ -11648,10 +11186,10 @@
         <v>39</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>237</v>
+        <v>188</v>
       </c>
       <c r="D41" s="33" t="n">
         <v>2</v>
@@ -11682,10 +11220,10 @@
         <v>40</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="D42" s="33" t="n">
         <v>1</v>
@@ -11716,10 +11254,10 @@
         <v>41</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>238</v>
+        <v>189</v>
       </c>
       <c r="D43" s="33" t="n">
         <v>1</v>
@@ -11750,10 +11288,10 @@
         <v>42</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C44" s="35" t="s">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="D44" s="33" t="n">
         <v>2</v>
@@ -11784,10 +11322,10 @@
         <v>43</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C45" s="35" t="s">
-        <v>182</v>
+        <v>139</v>
       </c>
       <c r="D45" s="33" t="n">
         <v>1</v>
@@ -11818,10 +11356,10 @@
         <v>44</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="D46" s="33" t="n">
         <v>1</v>
@@ -11852,10 +11390,10 @@
         <v>45</v>
       </c>
       <c r="B47" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="35" t="s">
         <v>190</v>
-      </c>
-      <c r="C47" s="35" t="s">
-        <v>239</v>
       </c>
       <c r="D47" s="33" t="n">
         <v>20</v>
@@ -11886,10 +11424,10 @@
         <v>46</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>196</v>
+        <v>150</v>
       </c>
       <c r="D48" s="33" t="n">
         <v>90</v>
@@ -11920,10 +11458,10 @@
         <v>47</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="D49" s="33" t="n">
         <v>1</v>
@@ -11951,7 +11489,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="45" t="s">
-        <v>240</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -11990,7 +11528,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>241</v>
+        <v>192</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -12005,507 +11543,507 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>242</v>
+        <v>193</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>243</v>
+        <v>194</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>244</v>
+        <v>195</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>245</v>
+        <v>196</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>246</v>
+        <v>197</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>247</v>
+        <v>198</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>248</v>
+        <v>199</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>249</v>
+        <v>200</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>251</v>
+        <v>202</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>252</v>
+        <v>203</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="48" t="s">
-        <v>253</v>
+        <v>204</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G3" s="50" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H3" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I3" s="50" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J3" s="50"/>
       <c r="K3" s="50"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="51" t="s">
-        <v>257</v>
+        <v>208</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E4" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I4" s="53" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J4" s="53"/>
       <c r="K4" s="53"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>258</v>
+        <v>209</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G5" s="50" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I5" s="50" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J5" s="50"/>
       <c r="K5" s="50"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>259</v>
+        <v>210</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I6" s="53" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J6" s="53"/>
       <c r="K6" s="53"/>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="48" t="s">
-        <v>260</v>
+        <v>211</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G7" s="50" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I7" s="50" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J7" s="50"/>
       <c r="K7" s="50"/>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>261</v>
+        <v>212</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I8" s="53" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J8" s="53"/>
       <c r="K8" s="53"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>262</v>
+        <v>213</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H9" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I9" s="50" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J9" s="50"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
-        <v>263</v>
+        <v>214</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J10" s="53"/>
       <c r="K10" s="53"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>264</v>
+        <v>215</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F11" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H11" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J11" s="50"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="51" t="s">
-        <v>265</v>
+        <v>216</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>255</v>
+        <v>206</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I12" s="53" t="s">
-        <v>256</v>
+        <v>207</v>
       </c>
       <c r="J12" s="53"/>
       <c r="K12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>266</v>
+        <v>217</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H13" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I13" s="55" t="s">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="J13" s="50"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>269</v>
+        <v>220</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I14" s="55" t="s">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="J14" s="53"/>
       <c r="K14" s="53"/>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>270</v>
+        <v>221</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G15" s="54" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H15" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I15" s="55" t="s">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="J15" s="50"/>
       <c r="K15" s="50"/>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="51" t="s">
-        <v>271</v>
+        <v>222</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G16" s="54" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I16" s="55" t="s">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="J16" s="53"/>
       <c r="K16" s="53"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>272</v>
+        <v>223</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>267</v>
+        <v>218</v>
       </c>
       <c r="H17" s="49" t="s">
-        <v>254</v>
+        <v>205</v>
       </c>
       <c r="I17" s="55" t="s">
-        <v>268</v>
+        <v>219</v>
       </c>
       <c r="J17" s="50"/>
       <c r="K17" s="50"/>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="56" t="s">
-        <v>273</v>
+        <v>224</v>
       </c>
       <c r="B19" s="56"/>
       <c r="C19" s="56"/>
@@ -12554,7 +12092,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="57" t="s">
-        <v>274</v>
+        <v>225</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -12570,36 +12108,36 @@
         <v>4</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>275</v>
+        <v>226</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>276</v>
+        <v>227</v>
       </c>
       <c r="D2" s="58" t="s">
-        <v>277</v>
+        <v>228</v>
       </c>
       <c r="E2" s="58" t="s">
-        <v>278</v>
+        <v>229</v>
       </c>
       <c r="F2" s="58" t="s">
-        <v>279</v>
+        <v>230</v>
       </c>
       <c r="G2" s="58" t="s">
-        <v>280</v>
+        <v>231</v>
       </c>
       <c r="H2" s="58" t="s">
-        <v>281</v>
+        <v>232</v>
       </c>
       <c r="I2" s="58" t="s">
-        <v>282</v>
+        <v>233</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="59" t="s">
-        <v>283</v>
+        <v>234</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>284</v>
+        <v>235</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -12614,25 +12152,25 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>285</v>
+        <v>236</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="D4" s="26" t="s">
-        <v>287</v>
+        <v>237</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>238</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -12641,25 +12179,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="26" t="s">
-        <v>291</v>
+        <v>241</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>242</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>292</v>
+        <v>243</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -12668,25 +12206,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>294</v>
+        <v>244</v>
+      </c>
+      <c r="C6" s="25" t="s">
+        <v>245</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -12695,25 +12233,25 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>298</v>
+        <v>248</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>249</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>295</v>
+        <v>246</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I7" s="7"/>
     </row>
@@ -12722,25 +12260,25 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>300</v>
+        <v>250</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>251</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>301</v>
+        <v>252</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I8" s="7"/>
     </row>
@@ -12749,63 +12287,63 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>303</v>
+        <v>253</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>254</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>304</v>
+        <v>255</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>306</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="D10" s="26" t="s">
-        <v>309</v>
+      <c r="B10" s="25" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>259</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>260</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>310</v>
+        <v>261</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>311</v>
+        <v>262</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -12820,7 +12358,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>312</v>
+        <v>263</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -12835,28 +12373,28 @@
         <v>1.1</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="C13" s="26" t="s">
-        <v>314</v>
+        <v>264</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>265</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>315</v>
+        <v>266</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="H13" s="61" t="s">
-        <v>316</v>
+        <v>267</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>317</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12864,28 +12402,28 @@
         <v>2</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>319</v>
+        <v>269</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>270</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>320</v>
+        <v>271</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="H14" s="62" t="s">
-        <v>321</v>
+        <v>272</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>322</v>
+        <v>273</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12893,25 +12431,25 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C15" s="26" t="s">
-        <v>324</v>
+        <v>274</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>275</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I15" s="7"/>
     </row>
@@ -12920,23 +12458,23 @@
         <v>5</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="9" t="s">
-        <v>288</v>
+        <v>239</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -12945,32 +12483,32 @@
         <v>6</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>329</v>
+        <v>280</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>305</v>
+        <v>256</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>289</v>
+        <v>240</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>330</v>
+        <v>281</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>331</v>
+        <v>282</v>
       </c>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
@@ -12985,23 +12523,23 @@
         <v>1</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>333</v>
+        <v>284</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I19" s="7"/>
     </row>
@@ -13010,26 +12548,26 @@
         <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>335</v>
+        <v>286</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>337</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13037,23 +12575,23 @@
         <v>3</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>338</v>
+        <v>289</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>339</v>
+        <v>290</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I21" s="7"/>
     </row>
@@ -13062,23 +12600,23 @@
         <v>4</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>340</v>
+        <v>291</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I22" s="7"/>
     </row>
@@ -13087,23 +12625,23 @@
         <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>343</v>
+        <v>294</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I23" s="7"/>
     </row>
@@ -13112,23 +12650,23 @@
         <v>6</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>344</v>
+        <v>295</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>345</v>
+        <v>296</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I24" s="7"/>
     </row>
@@ -13137,23 +12675,23 @@
         <v>7</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>346</v>
+        <v>297</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>347</v>
+        <v>298</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I25" s="7"/>
     </row>
@@ -13162,23 +12700,23 @@
         <v>8</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I26" s="7"/>
     </row>
@@ -13187,21 +12725,21 @@
         <v>9</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>350</v>
+        <v>301</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I27" s="7"/>
     </row>
@@ -13210,26 +12748,26 @@
         <v>9.1</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>351</v>
+        <v>302</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>352</v>
+        <v>303</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>5</v>
       </c>
       <c r="G28" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="I28" s="26" t="s">
-        <v>353</v>
+        <v>285</v>
+      </c>
+      <c r="I28" s="25" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13237,26 +12775,26 @@
         <v>9.2</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="C29" s="26" t="s">
-        <v>355</v>
+        <v>305</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>306</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>356</v>
+        <v>285</v>
+      </c>
+      <c r="I29" s="25" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13264,23 +12802,23 @@
         <v>9.3</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>358</v>
+        <v>309</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I30" s="7"/>
     </row>
@@ -13289,23 +12827,23 @@
         <v>9.4</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>359</v>
+        <v>310</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>360</v>
+        <v>311</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="9" t="s">
-        <v>296</v>
+        <v>247</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
       <c r="I31" s="7"/>
     </row>
@@ -13338,187 +12876,187 @@
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>361</v>
+        <v>312</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="63" t="s">
-        <v>362</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="64" t="s">
-        <v>363</v>
+        <v>314</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>364</v>
+        <v>315</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>365</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="65" t="s">
-        <v>366</v>
+        <v>317</v>
       </c>
       <c r="B5" s="66" t="n">
         <v>46328</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>367</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="65" t="s">
-        <v>368</v>
+        <v>319</v>
       </c>
       <c r="B6" s="65" t="n">
-        <f aca="false">MAX(计划!G5:G48)-MIN(计划!F5:F48)+1</f>
+        <f aca="false">MAX(计划!F5:F48)-MIN(计划!E5:E48)+1</f>
         <v>38</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>369</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="65" t="s">
-        <v>370</v>
+        <v>321</v>
       </c>
       <c r="B7" s="65" t="n">
         <v>90</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>371</v>
+        <v>322</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="65" t="s">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>373</v>
+        <v>324</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>374</v>
+        <v>325</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="63" t="s">
-        <v>375</v>
+        <v>326</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>376</v>
+        <v>327</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>377</v>
+        <v>328</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>378</v>
+        <v>329</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="65" t="s">
-        <v>379</v>
+        <v>330</v>
       </c>
       <c r="B12" s="68" t="n">
-        <f aca="false">计划!G5</f>
+        <f aca="false">计划!F5</f>
         <v>46329</v>
       </c>
       <c r="C12" s="65" t="s">
-        <v>380</v>
+        <v>331</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="65" t="s">
-        <v>381</v>
+        <v>332</v>
       </c>
       <c r="B13" s="68" t="n">
-        <f aca="false">计划!G7</f>
+        <f aca="false">计划!F7</f>
         <v>46332</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>382</v>
+        <v>333</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>383</v>
+        <v>334</v>
       </c>
       <c r="B14" s="68" t="n">
-        <f aca="false">计划!G16</f>
+        <f aca="false">计划!F16</f>
         <v>46341</v>
       </c>
       <c r="C14" s="67" t="s">
-        <v>384</v>
+        <v>335</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>385</v>
+        <v>336</v>
       </c>
       <c r="B15" s="68" t="n">
-        <f aca="false">计划!G28</f>
+        <f aca="false">计划!F28</f>
         <v>46349</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>386</v>
+        <v>337</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="65" t="s">
-        <v>387</v>
+        <v>338</v>
       </c>
       <c r="B16" s="68" t="n">
-        <f aca="false">计划!G39</f>
+        <f aca="false">计划!F39</f>
         <v>46357</v>
       </c>
       <c r="C16" s="65" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="65" t="s">
-        <v>389</v>
+        <v>340</v>
       </c>
       <c r="B17" s="68" t="n">
-        <f aca="false">计划!G43</f>
+        <f aca="false">计划!F43</f>
         <v>46362</v>
       </c>
       <c r="C17" s="65" t="s">
-        <v>390</v>
+        <v>341</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="65" t="s">
-        <v>391</v>
+        <v>342</v>
       </c>
       <c r="B18" s="68" t="n">
-        <f aca="false">计划!G48</f>
+        <f aca="false">计划!F48</f>
         <v>46365</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>392</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="65" t="s">
-        <v>393</v>
+        <v>344</v>
       </c>
       <c r="B19" s="68" t="n">
-        <f aca="false">计划!G51</f>
+        <f aca="false">计划!F51</f>
         <v>46456</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>394</v>
+        <v>345</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="63" t="s">
-        <v>395</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13526,10 +13064,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>396</v>
+        <v>347</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>397</v>
+        <v>348</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13537,10 +13075,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>398</v>
+        <v>349</v>
       </c>
       <c r="C23" s="70" t="s">
-        <v>399</v>
+        <v>350</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13548,10 +13086,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="70" t="s">
-        <v>400</v>
+        <v>351</v>
       </c>
       <c r="C24" s="70" t="s">
-        <v>401</v>
+        <v>352</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13559,10 +13097,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="70" t="s">
-        <v>402</v>
+        <v>353</v>
       </c>
       <c r="C25" s="70" t="s">
-        <v>403</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13570,10 +13108,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="70" t="s">
-        <v>404</v>
+        <v>355</v>
       </c>
       <c r="C26" s="70" t="s">
-        <v>405</v>
+        <v>356</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13581,10 +13119,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="70" t="s">
-        <v>406</v>
+        <v>357</v>
       </c>
       <c r="C27" s="70" t="s">
-        <v>407</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13592,10 +13130,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="70" t="s">
-        <v>408</v>
+        <v>359</v>
       </c>
       <c r="C28" s="70" t="s">
-        <v>409</v>
+        <v>360</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13603,10 +13141,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="70" t="s">
-        <v>410</v>
+        <v>361</v>
       </c>
       <c r="C29" s="70" t="s">
-        <v>411</v>
+        <v>362</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13614,10 +13152,10 @@
         <v>8</v>
       </c>
       <c r="B30" s="70" t="s">
-        <v>412</v>
+        <v>363</v>
       </c>
       <c r="C30" s="70" t="s">
-        <v>413</v>
+        <v>364</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13625,10 +13163,10 @@
         <v>9</v>
       </c>
       <c r="B31" s="70" t="s">
-        <v>414</v>
+        <v>365</v>
       </c>
       <c r="C31" s="70" t="s">
-        <v>415</v>
+        <v>366</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13636,10 +13174,10 @@
         <v>10</v>
       </c>
       <c r="B32" s="70" t="s">
-        <v>416</v>
+        <v>367</v>
       </c>
       <c r="C32" s="70" t="s">
-        <v>417</v>
+        <v>368</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13647,10 +13185,10 @@
         <v>11</v>
       </c>
       <c r="B33" s="70" t="s">
-        <v>418</v>
+        <v>369</v>
       </c>
       <c r="C33" s="70" t="s">
-        <v>419</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13658,10 +13196,10 @@
         <v>12</v>
       </c>
       <c r="B34" s="70" t="s">
-        <v>420</v>
+        <v>371</v>
       </c>
       <c r="C34" s="70" t="s">
-        <v>421</v>
+        <v>372</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13669,10 +13207,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="70" t="s">
-        <v>422</v>
+        <v>373</v>
       </c>
       <c r="C35" s="70" t="s">
-        <v>423</v>
+        <v>374</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13680,10 +13218,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="70" t="s">
-        <v>424</v>
+        <v>375</v>
       </c>
       <c r="C36" s="70" t="s">
-        <v>425</v>
+        <v>376</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13691,10 +13229,10 @@
         <v>15</v>
       </c>
       <c r="B37" s="70" t="s">
-        <v>426</v>
+        <v>377</v>
       </c>
       <c r="C37" s="70" t="s">
-        <v>427</v>
+        <v>378</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13702,10 +13240,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="70" t="s">
-        <v>428</v>
+        <v>379</v>
       </c>
       <c r="C38" s="70" t="s">
-        <v>429</v>
+        <v>380</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13713,123 +13251,123 @@
         <v>17</v>
       </c>
       <c r="B39" s="70" t="s">
-        <v>430</v>
+        <v>381</v>
       </c>
       <c r="C39" s="70" t="s">
-        <v>431</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="63" t="s">
-        <v>432</v>
+        <v>383</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="71" t="s">
-        <v>433</v>
+        <v>384</v>
       </c>
       <c r="B42" s="71"/>
       <c r="C42" s="71"/>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="71" t="s">
-        <v>434</v>
+        <v>385</v>
       </c>
       <c r="B43" s="71"/>
       <c r="C43" s="71"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="71" t="s">
-        <v>435</v>
+        <v>386</v>
       </c>
       <c r="B44" s="71"/>
       <c r="C44" s="71"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="71" t="s">
-        <v>436</v>
+        <v>387</v>
       </c>
       <c r="B45" s="71"/>
       <c r="C45" s="71"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="71" t="s">
-        <v>437</v>
+        <v>388</v>
       </c>
       <c r="B46" s="71"/>
       <c r="C46" s="71"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="71" t="s">
-        <v>438</v>
+        <v>389</v>
       </c>
       <c r="B47" s="71"/>
       <c r="C47" s="71"/>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="71" t="s">
-        <v>439</v>
+        <v>390</v>
       </c>
       <c r="B48" s="71"/>
       <c r="C48" s="71"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="63" t="s">
-        <v>440</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="72"/>
       <c r="B51" s="65" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C51" s="73" t="s">
-        <v>441</v>
+        <v>392</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="74"/>
       <c r="B52" s="65" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C52" s="73" t="s">
-        <v>442</v>
+        <v>393</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="75"/>
       <c r="B53" s="67" t="s">
-        <v>443</v>
+        <v>394</v>
       </c>
       <c r="C53" s="73" t="s">
-        <v>444</v>
+        <v>395</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="76"/>
       <c r="B54" s="65" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="C54" s="73" t="s">
-        <v>445</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="77"/>
       <c r="B55" s="65" t="s">
-        <v>157</v>
+        <v>121</v>
       </c>
       <c r="C55" s="78" t="s">
-        <v>446</v>
+        <v>397</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="79"/>
       <c r="B56" s="65" t="s">
-        <v>190</v>
+        <v>145</v>
       </c>
       <c r="C56" s="73" t="s">
-        <v>447</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>

--- a/CVT-MES项目资料/04_墨西哥CVT线现场实施计划_V2.xlsx
+++ b/CVT-MES项目资料/04_墨西哥CVT线现场实施计划_V2.xlsx
@@ -165,7 +165,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">V2.1</t>
+      <t xml:space="preserve">V2.2</t>
     </r>
     <r>
       <rPr>
@@ -1149,13 +1149,152 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配合调试上线打码</t>
+    <t xml:space="preserve">检查桥架、网线、电源线等安装辅材，确认工位网络与供电稳定</t>
+  </si>
+  <si>
+    <t xml:space="preserve">辅材到位，现场施工完成</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">软件部署与基础配置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部署</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服务端：软件包、组件、依赖环境，初始化数据库</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服务器系统、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SQL Server</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">就绪</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部署工控机客户端到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个工位一体机，配置启动项、客户端参数</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">工位一体机系统与网络就绪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一体机后到货，客户端镜像建议用同型号测试机提前验证</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配置系统语言：中文、西班牙文切换</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服务端部署完成</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">协议要求软件支持中西文切换</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置用户管理：用户、角色、权限、员工、工位技能、班组长</t>
     </r>
     <r>
       <rPr>
@@ -1172,286 +1311,123 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">标签打印：标签模板、条码规则、总成二维码打印</t>
+      <t xml:space="preserve">质检</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">出库等角色</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最终用户提供组织架构与权限需求</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置主动轮工艺：产品型号、编号、组件、厂商、重量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">扭力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动平衡上下限</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">最终用户提供主动轮工艺参数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配置从动轮工艺：产品型号、编号、组件、厂商、工艺参数上下限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">最终用户提供从动轮工艺参数</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配置条码规则、标签模板、上线打印功能</t>
+  </si>
+  <si>
+    <t xml:space="preserve">条码规则、标签模板确认</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上线打码</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">标签打印统一调试（全部硬件上电、模板配置完成后进行）：标签模板、条码规则、总成二维码打印</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">甲方提供打码设备</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">打印</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">打码设备到位，条码规则确认</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">★合同仅含标签打印与条码规则，打码硬件未在供货清单，需甲方提供</t>
-  </si>
-  <si>
-    <t xml:space="preserve">检查桥架、网线、电源线等安装辅材，确认工位网络与供电稳定</t>
-  </si>
-  <si>
-    <t xml:space="preserve">辅材到位，现场施工完成</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">软件部署与基础配置</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部署</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服务端：软件包、组件、依赖环境，初始化数据库</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服务器系统、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SQL Server</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">就绪</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部署工控机客户端到</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">个工位一体机，配置启动项、客户端参数</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">工位一体机系统与网络就绪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">一体机后到货，客户端镜像建议用同型号测试机提前验证</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置系统语言：中文、西班牙文切换</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">服务端部署完成</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">协议要求软件支持中西文切换</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置用户管理：用户、角色、权限、员工、工位技能、班组长</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">质检</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出库等角色</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供组织架构与权限需求</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置主动轮工艺：产品型号、编号、组件、厂商、重量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">扭力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动平衡上下限</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供主动轮工艺参数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置从动轮工艺：产品型号、编号、组件、厂商、工艺参数上下限</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供从动轮工艺参数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置条码规则、标签模板、上线打印功能</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条码规则、标签模板确认</t>
+    <t xml:space="preserve">一体机、扫码枪、大屏全部上电且网络连通；打码设备到位、标签模板配置完成</t>
+  </si>
+  <si>
+    <t xml:space="preserve">★待硬件上电具备条件后统一调试，不随安装并行；合同仅含标签打印与条码规则，打码硬件由甲方提供</t>
   </si>
   <si>
     <t xml:space="preserve">配置工艺路线、工序、工位、启用状态、异常关联工位、干涉工位跳过逻辑</t>
@@ -3259,14 +3235,87 @@
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配合调试上线打码</t>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">软件部署与基础配置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部署</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">服务端：软件包、组件、依赖环境，初始化数据库</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">部署工控机客户端到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个工位一体机，配置启动项、客户端参数</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置用户管理：用户、角色、权限、员工、工位技能、班组长</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="微软雅黑"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3279,10 +3328,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">标签打印：标签模板、条码规则、总成二维码打印</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">质检</t>
+    </r>
     <r>
       <rPr>
         <sz val="8"/>
@@ -3290,7 +3337,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MES</t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -3298,7 +3345,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">软件部署与基础配置</t>
+      <t xml:space="preserve">出库等角色</t>
     </r>
   </si>
   <si>
@@ -3308,7 +3355,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">部署</t>
+      <t xml:space="preserve">配置主动轮工艺：产品型号、编号、组件、厂商、重量</t>
     </r>
     <r>
       <rPr>
@@ -3317,7 +3364,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">MES</t>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
@@ -3325,122 +3372,51 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">服务端：软件包、组件、依赖环境，初始化数据库</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">扭力</t>
+    </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">部署工控机客户端到</t>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">15</t>
-    </r>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动平衡上下限</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="8"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">个工位一体机，配置启动项、客户端参数</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">上线打码</t>
+    </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置用户管理：用户、角色、权限、员工、工位技能、班组长</t>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">质检</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">出库等角色</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置主动轮工艺：产品型号、编号、组件、厂商、重量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">扭力</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">动平衡上下限</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">标签打印统一调试（全部硬件上电、模板配置完成后进行）：标签模板、条码规则、总成二维码打印</t>
     </r>
   </si>
   <si>
@@ -5765,7 +5741,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">合同仅含“标签打印、条码规则管理”，打码硬件未在供货清单：改为“配合调试”，设备由甲方提供</t>
+    <t xml:space="preserve">合同仅含“标签打印、条码规则管理”，打码硬件未在供货清单：改为“硬件全部上电后统一调试”，设备由甲方提供</t>
   </si>
   <si>
     <t xml:space="preserve">无培训任务</t>
@@ -7286,11 +7262,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -8221,7 +8197,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="9" t="n">
         <v>9</v>
@@ -8234,76 +8210,74 @@
       </c>
       <c r="E13" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L13</f>
-        <v>46338</v>
+        <v>46333</v>
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">E13+D13-1</f>
-        <v>46339</v>
+        <v>46334</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="H13" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J13" s="7" t="s">
+      <c r="K13" s="7"/>
+      <c r="L13" s="0" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="K13" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5"/>
       <c r="B14" s="14" t="n">
         <v>10</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" s="14" t="n">
         <v>2</v>
       </c>
       <c r="E14" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L14</f>
-        <v>46333</v>
+        <v>46340</v>
       </c>
       <c r="F14" s="13" t="n">
         <f aca="false">E14+D14-1</f>
-        <v>46334</v>
+        <v>46341</v>
       </c>
       <c r="G14" s="12" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="I14" s="14" t="s">
         <v>25</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K14" s="12"/>
       <c r="L14" s="0" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>57</v>
-      </c>
+      <c r="A15" s="24"/>
       <c r="B15" s="9" t="n">
         <v>11</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>2</v>
@@ -8326,31 +8300,33 @@
         <v>25</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="7"/>
+        <v>57</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>58</v>
+      </c>
       <c r="L15" s="0" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24"/>
       <c r="B16" s="14" t="n">
         <v>12</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L16</f>
-        <v>46340</v>
+        <v>46342</v>
       </c>
       <c r="F16" s="13" t="n">
         <f aca="false">E16+D16-1</f>
-        <v>46341</v>
+        <v>46342</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>29</v>
@@ -8361,23 +8337,23 @@
       <c r="I16" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="J16" s="12" t="s">
+      <c r="J16" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="K16" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="K16" s="12" t="s">
-        <v>62</v>
-      </c>
       <c r="L16" s="0" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24"/>
       <c r="B17" s="9" t="n">
         <v>13</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>1</v>
@@ -8399,12 +8375,10 @@
       <c r="I17" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J17" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>65</v>
-      </c>
+      <c r="J17" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K17" s="7"/>
       <c r="L17" s="0" t="n">
         <v>14</v>
       </c>
@@ -8415,18 +8389,18 @@
         <v>14</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L18</f>
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="F18" s="13" t="n">
         <f aca="false">E18+D18-1</f>
-        <v>46342</v>
+        <v>46343</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>29</v>
@@ -8438,11 +8412,11 @@
         <v>25</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K18" s="12"/>
       <c r="L18" s="0" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8451,18 +8425,18 @@
         <v>15</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E19" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L19</f>
-        <v>46343</v>
+        <v>46344</v>
       </c>
       <c r="F19" s="8" t="n">
         <f aca="false">E19+D19-1</f>
-        <v>46343</v>
+        <v>46344</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>29</v>
@@ -8474,20 +8448,20 @@
         <v>25</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="0" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="24"/>
       <c r="B20" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
@@ -8510,47 +8484,49 @@
         <v>25</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K20" s="12"/>
       <c r="L20" s="0" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="24"/>
       <c r="B21" s="9" t="n">
         <v>17</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L21</f>
-        <v>46344</v>
+        <v>46345</v>
       </c>
       <c r="F21" s="8" t="n">
         <f aca="false">E21+D21-1</f>
-        <v>46344</v>
+        <v>46346</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>29</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>25</v>
+        <v>71</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K21" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="K21" s="7"/>
       <c r="L21" s="0" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8617,7 +8593,7 @@
       <c r="I23" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="25" t="s">
+      <c r="J23" s="26" t="s">
         <v>77</v>
       </c>
       <c r="K23" s="7"/>
@@ -8656,7 +8632,7 @@
       <c r="J24" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="K24" s="25" t="s">
         <v>80</v>
       </c>
       <c r="L24" s="0" t="n">
@@ -9028,7 +9004,7 @@
       <c r="J34" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="K34" s="26" t="s">
+      <c r="K34" s="25" t="s">
         <v>106</v>
       </c>
       <c r="L34" s="0" t="n">
@@ -9226,7 +9202,7 @@
       <c r="B40" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="C40" s="26" t="s">
+      <c r="C40" s="25" t="s">
         <v>122</v>
       </c>
       <c r="D40" s="14" t="n">
@@ -9262,7 +9238,7 @@
       <c r="B41" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="C41" s="25" t="s">
+      <c r="C41" s="26" t="s">
         <v>124</v>
       </c>
       <c r="D41" s="9" t="n">
@@ -9728,8 +9704,8 @@
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="A15:A28"/>
+    <mergeCell ref="A6:A13"/>
+    <mergeCell ref="A14:A28"/>
     <mergeCell ref="A29:A39"/>
     <mergeCell ref="A40:A48"/>
     <mergeCell ref="A49:A52"/>
@@ -10169,13 +10145,13 @@
         <v>21</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>170</v>
+        <v>51</v>
       </c>
       <c r="D11" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="37"/>
       <c r="G11" s="37"/>
       <c r="H11" s="37"/>
       <c r="I11" s="37"/>
@@ -10199,17 +10175,17 @@
       <c r="A12" s="33" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="34" t="s">
-        <v>21</v>
+      <c r="B12" s="39" t="s">
+        <v>170</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>55</v>
+        <v>171</v>
       </c>
       <c r="D12" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="40"/>
       <c r="G12" s="37"/>
       <c r="H12" s="37"/>
       <c r="I12" s="37"/>
@@ -10234,7 +10210,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C13" s="35" t="s">
         <v>172</v>
@@ -10268,17 +10244,17 @@
         <v>12</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>173</v>
+        <v>59</v>
       </c>
       <c r="D14" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="37"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="40"/>
       <c r="H14" s="37"/>
       <c r="I14" s="37"/>
       <c r="J14" s="37"/>
@@ -10302,10 +10278,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="D15" s="33" t="n">
         <v>1</v>
@@ -10336,7 +10312,7 @@
         <v>14</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C16" s="35" t="s">
         <v>174</v>
@@ -10370,10 +10346,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>175</v>
+        <v>66</v>
       </c>
       <c r="D17" s="33" t="n">
         <v>1</v>
@@ -10404,10 +10380,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>1</v>
@@ -10438,13 +10414,13 @@
         <v>17</v>
       </c>
       <c r="B19" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>72</v>
+        <v>175</v>
       </c>
       <c r="D19" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="37"/>
       <c r="F19" s="37"/>
@@ -10472,7 +10448,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C20" s="35" t="s">
         <v>74</v>
@@ -10506,7 +10482,7 @@
         <v>19</v>
       </c>
       <c r="B21" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C21" s="35" t="s">
         <v>176</v>
@@ -10540,7 +10516,7 @@
         <v>20</v>
       </c>
       <c r="B22" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C22" s="35" t="s">
         <v>78</v>
@@ -10574,7 +10550,7 @@
         <v>21</v>
       </c>
       <c r="B23" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C23" s="35" t="s">
         <v>177</v>
@@ -10608,7 +10584,7 @@
         <v>22</v>
       </c>
       <c r="B24" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="35" t="s">
         <v>84</v>
@@ -10642,7 +10618,7 @@
         <v>23</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C25" s="35" t="s">
         <v>178</v>
@@ -10676,7 +10652,7 @@
         <v>24</v>
       </c>
       <c r="B26" s="39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C26" s="35" t="s">
         <v>179</v>
@@ -12157,7 +12133,7 @@
       <c r="C4" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="D4" s="25" t="s">
+      <c r="D4" s="26" t="s">
         <v>238</v>
       </c>
       <c r="E4" s="9" t="s">
@@ -12181,7 +12157,7 @@
       <c r="B5" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="26" t="s">
         <v>242</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -12208,7 +12184,7 @@
       <c r="B6" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="26" t="s">
         <v>245</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -12235,7 +12211,7 @@
       <c r="B7" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C7" s="25" t="s">
+      <c r="C7" s="26" t="s">
         <v>249</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -12262,7 +12238,7 @@
       <c r="B8" s="7" t="s">
         <v>250</v>
       </c>
-      <c r="C8" s="25" t="s">
+      <c r="C8" s="26" t="s">
         <v>251</v>
       </c>
       <c r="D8" s="7" t="s">
@@ -12289,7 +12265,7 @@
       <c r="B9" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C9" s="26" t="s">
         <v>254</v>
       </c>
       <c r="D9" s="7" t="s">
@@ -12315,13 +12291,13 @@
       <c r="A10" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="26" t="s">
         <v>258</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="26" t="s">
         <v>259</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="26" t="s">
         <v>260</v>
       </c>
       <c r="E10" s="9" t="s">
@@ -12375,7 +12351,7 @@
       <c r="B13" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="26" t="s">
         <v>265</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -12404,7 +12380,7 @@
       <c r="B14" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="26" t="s">
         <v>270</v>
       </c>
       <c r="D14" s="7" t="s">
@@ -12433,7 +12409,7 @@
       <c r="B15" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="26" t="s">
         <v>275</v>
       </c>
       <c r="D15" s="7" t="s">
@@ -12766,7 +12742,7 @@
       <c r="H28" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="I28" s="25" t="s">
+      <c r="I28" s="26" t="s">
         <v>304</v>
       </c>
     </row>
@@ -12777,7 +12753,7 @@
       <c r="B29" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="26" t="s">
         <v>306</v>
       </c>
       <c r="D29" s="7"/>
@@ -12793,7 +12769,7 @@
       <c r="H29" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="I29" s="25" t="s">
+      <c r="I29" s="26" t="s">
         <v>307</v>
       </c>
     </row>
@@ -12987,7 +12963,7 @@
         <v>334</v>
       </c>
       <c r="B14" s="68" t="n">
-        <f aca="false">计划!F16</f>
+        <f aca="false">计划!F15</f>
         <v>46341</v>
       </c>
       <c r="C14" s="67" t="s">

--- a/CVT-MES项目资料/04_墨西哥CVT线现场实施计划_V2.xlsx
+++ b/CVT-MES项目资料/04_墨西哥CVT线现场实施计划_V2.xlsx
@@ -19,7 +19,7 @@
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'甘特（周）'!$1:$2</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">硬件清单!$1:$2</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Titles" vbProcedure="false">计划!$1:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">计划!$A$4:$K$52</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">计划!$A$4:$K$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="379">
   <si>
     <r>
       <rPr>
@@ -165,7 +165,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">V2.2</t>
+      <t xml:space="preserve">V2.3</t>
     </r>
     <r>
       <rPr>
@@ -1263,7 +1263,150 @@
     <t xml:space="preserve">一体机后到货，客户端镜像建议用同型号测试机提前验证</t>
   </si>
   <si>
-    <t xml:space="preserve">配置系统语言：中文、西班牙文切换</t>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基础数据与工艺建模（一次性完成）：系统语言中</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">西切换、用户</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">角色</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">权限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">员工与工位技能；主动轮、从动轮产品型号与工艺参数（组件、厂商、重量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">扭力</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">动平衡上下限）；工艺路线、工序、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工位启用与干涉跳过；电子作业指导（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">图、预装提示、按车型切换）；拧紧工艺配方（枪、程序号、数量、不合格次数、使能）</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1281,20 +1424,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">服务端部署完成</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">协议要求软件支持中西文切换</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置用户管理：用户、角色、权限、员工、工位技能、班组长</t>
+      <t xml:space="preserve">服务端部署完成；甲方提供组织架构、主动轮</t>
     </r>
     <r>
       <rPr>
@@ -1311,7 +1441,51 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">质检</t>
+      <t xml:space="preserve">从动轮工艺参数、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">图与作业指导书</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条（语言</t>
     </r>
     <r>
       <rPr>
@@ -1328,20 +1502,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">出库等角色</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供组织架构与权限需求</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置主动轮工艺：产品型号、编号、组件、厂商、重量</t>
+      <t xml:space="preserve">权限</t>
     </r>
     <r>
       <rPr>
@@ -1358,7 +1519,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">扭力</t>
+      <t xml:space="preserve">主动轮</t>
     </r>
     <r>
       <rPr>
@@ -1375,23 +1536,201 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">动平衡上下限</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供主动轮工艺参数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置从动轮工艺：产品型号、编号、组件、厂商、工艺参数上下限</t>
-  </si>
-  <si>
-    <t xml:space="preserve">最终用户提供从动轮工艺参数</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置条码规则、标签模板、上线打印功能</t>
-  </si>
-  <si>
-    <t xml:space="preserve">条码规则、标签模板确认</t>
+      <t xml:space="preserve">从动轮</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工艺路线</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/ESOP/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">拧紧）合并为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个工作包，按产品型号整体建模、一次校验</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">业务规则与报表看板配置：条码规则与标签模板、上线打印；订单管理（生产计划、工单、编号规则、终端客户）；质量报表、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、电子看板、日志与追溯；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES-SAP/PLC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">预留接口</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">基础数据与工艺建模完成；条码规则、报表格式、看板内容确认</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">原</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条（条码规则</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">订单</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">报表</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">看板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">预留接口）合并；报表与看板样式需甲方确认</t>
+    </r>
   </si>
   <si>
     <r>
@@ -1417,7 +1756,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">标签打印统一调试（全部硬件上电、模板配置完成后进行）：标签模板、条码规则、总成二维码打印</t>
+      <t xml:space="preserve">标签打印统一调试（全部硬件上电、标签模板配置完成后进行）：标签模板、条码规则、总成二维码打印</t>
     </r>
   </si>
   <si>
@@ -1427,101 +1766,34 @@
     <t xml:space="preserve">一体机、扫码枪、大屏全部上电且网络连通；打码设备到位、标签模板配置完成</t>
   </si>
   <si>
-    <t xml:space="preserve">★待硬件上电具备条件后统一调试，不随安装并行；合同仅含标签打印与条码规则，打码硬件由甲方提供</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配置工艺路线、工序、工位、启用状态、异常关联工位、干涉工位跳过逻辑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">工艺路线、工位定义确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置电子作业指导书：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PDM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">图、预装提示、按车型</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工序切换</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PDM</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">图、作业指导书资料齐全</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">配置拧紧工艺：拧紧枪、程序号、拧紧数量、不合格次数、使能控制、数据采集</t>
-  </si>
-  <si>
-    <t xml:space="preserve">拧紧枪接口协议、程序号确认</t>
-  </si>
-  <si>
+    <t xml:space="preserve">★独立保留：依赖硬件上电与甲方打码设备，不并入配置包；合同仅含标签打印与条码规则</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">配置设备采集接口：伺服压机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台、</t>
+    </r>
     <r>
       <rPr>
         <sz val="9"/>
@@ -1554,17 +1826,54 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">把（主动轮）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置设备采集接口：伺服压机</t>
+      <t xml:space="preserve">把、检测设备</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">四类信号通讯参数</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">设备接口协议、数据字典与通讯参数确认</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">★独立保留：依赖设备协议，协议缺失即转为遗留项；压机</t>
     </r>
     <r>
       <rPr>
@@ -1581,267 +1890,8 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">台、拧紧枪</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">把、检测设备</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通讯参数</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">设备接口协议、通讯参数确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">压机</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">CVT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">二线；国外调试费用未含，需甲方</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">设备商配合</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">配置订单管理：生产计划、工单、计划编号规则、终端客户、产品型号、数量</t>
-  </si>
-  <si>
-    <t xml:space="preserve">订单管理规则确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置质量报表、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SPC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">统计、电子看板、日志管理、追溯查询</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">报表格式、看板内容确认</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与工厂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES/SAP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">预留接口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">标准接口协议</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">工厂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES/SAP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">接口文档、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">协议确认</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">预留接口，联调视甲方系统可用性</t>
+      <t xml:space="preserve">台仅国内调试</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">工位单机与设备采集调试</t>
@@ -3311,7 +3361,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">配置用户管理：用户、角色、权限、员工、工位技能、班组长</t>
+      <t xml:space="preserve">基础数据与工艺建模（一次性完成）：系统语言中</t>
     </r>
     <r>
       <rPr>
@@ -3328,7 +3378,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">质检</t>
+      <t xml:space="preserve">西切换、用户</t>
     </r>
     <r>
       <rPr>
@@ -3345,21 +3395,28 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">出库等角色</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">角色</t>
+    </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置主动轮工艺：产品型号、编号、组件、厂商、重量</t>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">权限</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="微软雅黑"/>
         <family val="0"/>
         <charset val="1"/>
@@ -3372,6 +3429,23 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">员工与工位技能；主动轮、从动轮产品型号与工艺参数（组件、厂商、重量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">扭力</t>
     </r>
     <r>
@@ -3389,13 +3463,91 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">动平衡上下限</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">动平衡上下限）；工艺路线、工序、</t>
+    </r>
     <r>
       <rPr>
         <sz val="8"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">15</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">工位启用与干涉跳过；电子作业指导（</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PDM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">图、预装提示、按车型切换）；拧紧工艺配方（枪、程序号、数量、不合格次数、使能）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">业务规则与报表看板配置：条码规则与标签模板、上线打印；订单管理（生产计划、工单、编号规则、终端客户）；质量报表、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SPC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、电子看板、日志与追溯；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES-SAP/PLC </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">预留接口</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -3416,7 +3568,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">标签打印统一调试（全部硬件上电、模板配置完成后进行）：标签模板、条码规则、总成二维码打印</t>
+      <t xml:space="preserve">标签打印统一调试（全部硬件上电、标签模板配置完成后进行）：标签模板、条码规则、总成二维码打印</t>
     </r>
   </si>
   <si>
@@ -3426,7 +3578,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">配置电子作业指导书：</t>
+      <t xml:space="preserve">配置设备采集接口：伺服压机</t>
     </r>
     <r>
       <rPr>
@@ -3435,7 +3587,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">PDM</t>
+      <t xml:space="preserve">5</t>
     </r>
     <r>
       <rPr>
@@ -3443,7 +3595,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">图、预装提示、按车型</t>
+      <t xml:space="preserve">台、</t>
     </r>
     <r>
       <rPr>
@@ -3452,7 +3604,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">ATLAS</t>
     </r>
     <r>
       <rPr>
@@ -3460,7 +3612,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">工位</t>
+      <t xml:space="preserve">拧紧枪</t>
     </r>
     <r>
       <rPr>
@@ -3469,7 +3621,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">/</t>
+      <t xml:space="preserve">1</t>
     </r>
     <r>
       <rPr>
@@ -3477,173 +3629,41 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">工序切换</t>
-    </r>
-  </si>
-  <si>
+      <t xml:space="preserve">把、检测设备</t>
+    </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置设备采集接口：伺服压机</t>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">5</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">台、</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台、拧紧枪</t>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PLC</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">把、检测设备</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">台、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">通讯参数</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置质量报表、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">SPC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">统计、电子看板、日志管理、追溯查询</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">配置</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">与工厂</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">MES/SAP</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">预留接口、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="微软雅黑"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PLC</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">标准接口协议</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">四类信号通讯参数</t>
     </r>
   </si>
   <si>
@@ -5418,7 +5438,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">基础数据与工艺确认</t>
+    <t xml:space="preserve">基础数据、业务规则与接口配置完成</t>
   </si>
   <si>
     <t xml:space="preserve">单机与采集调试完成</t>
@@ -6481,6 +6501,128 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">配置基线恢复兜底；仅硬件变更时才重新安装</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">基础配置拆成 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">11 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">条（语言、权限、主动轮、从动轮、条码、工艺路线、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ESOP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">、拧紧、接口、订单、报表）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">按</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MES</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">实施惯例合并为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">个工作包：①基础数据与工艺建模</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天 ②业务规则与报表看板</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="微软雅黑"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">天；打码联调、设备采集接口因外部依赖独立保留</t>
     </r>
   </si>
   <si>
@@ -7795,7 +7937,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:L53"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
@@ -8309,7 +8451,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="84" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24"/>
       <c r="B16" s="14" t="n">
         <v>12</v>
@@ -8318,7 +8460,7 @@
         <v>59</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L16</f>
@@ -8326,7 +8468,7 @@
       </c>
       <c r="F16" s="13" t="n">
         <f aca="false">E16+D16-1</f>
-        <v>46342</v>
+        <v>46344</v>
       </c>
       <c r="G16" s="12" t="s">
         <v>29</v>
@@ -8347,7 +8489,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" customFormat="false" ht="67.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24"/>
       <c r="B17" s="9" t="n">
         <v>13</v>
@@ -8356,15 +8498,15 @@
         <v>62</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L17</f>
-        <v>46342</v>
+        <v>46345</v>
       </c>
       <c r="F17" s="8" t="n">
         <f aca="false">E17+D17-1</f>
-        <v>46342</v>
+        <v>46346</v>
       </c>
       <c r="G17" s="7" t="s">
         <v>29</v>
@@ -8378,45 +8520,49 @@
       <c r="J17" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K17" s="7"/>
+      <c r="K17" s="7" t="s">
+        <v>64</v>
+      </c>
       <c r="L17" s="0" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24"/>
       <c r="B18" s="14" t="n">
         <v>14</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L18</f>
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="F18" s="13" t="n">
         <f aca="false">E18+D18-1</f>
-        <v>46343</v>
+        <v>46347</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>29</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="14" t="s">
-        <v>25</v>
+        <v>66</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>18</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="K18" s="12"/>
+        <v>67</v>
+      </c>
+      <c r="K18" s="12" t="s">
+        <v>68</v>
+      </c>
       <c r="L18" s="0" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8425,18 +8571,18 @@
         <v>15</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L19</f>
-        <v>46344</v>
+        <v>46348</v>
       </c>
       <c r="F19" s="8" t="n">
         <f aca="false">E19+D19-1</f>
-        <v>46344</v>
+        <v>46349</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>29</v>
@@ -8448,31 +8594,35 @@
         <v>25</v>
       </c>
       <c r="J19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="K19" s="7"/>
+        <v>70</v>
+      </c>
+      <c r="K19" s="7" t="s">
+        <v>71</v>
+      </c>
       <c r="L19" s="0" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="24"/>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>72</v>
+      </c>
       <c r="B20" s="14" t="n">
         <v>16</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D20" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L20</f>
-        <v>46344</v>
+        <v>46350</v>
       </c>
       <c r="F20" s="13" t="n">
         <f aca="false">E20+D20-1</f>
-        <v>46344</v>
+        <v>46350</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>29</v>
@@ -8484,105 +8634,105 @@
         <v>25</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="K20" s="12"/>
       <c r="L20" s="0" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5"/>
       <c r="B21" s="9" t="n">
         <v>17</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>2</v>
       </c>
       <c r="E21" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L21</f>
-        <v>46345</v>
+        <v>46351</v>
       </c>
       <c r="F21" s="8" t="n">
         <f aca="false">E21+D21-1</f>
-        <v>46346</v>
+        <v>46352</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>29</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>18</v>
+        <v>30</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="K21" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L21" s="0" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="24"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5"/>
       <c r="B22" s="14" t="n">
         <v>18</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="D22" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L22</f>
-        <v>46345</v>
+        <v>46351</v>
       </c>
       <c r="F22" s="13" t="n">
         <f aca="false">E22+D22-1</f>
-        <v>46345</v>
+        <v>46351</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>29</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I22" s="14" t="s">
         <v>25</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="K22" s="12"/>
       <c r="L22" s="0" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24"/>
+      <c r="A23" s="5"/>
       <c r="B23" s="9" t="n">
         <v>19</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E23" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L23</f>
-        <v>46346</v>
+        <v>46352</v>
       </c>
       <c r="F23" s="8" t="n">
         <f aca="false">E23+D23-1</f>
-        <v>46346</v>
+        <v>46352</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>29</v>
@@ -8593,32 +8743,34 @@
       <c r="I23" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J23" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="K23" s="7"/>
+      <c r="J23" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="K23" s="7" t="s">
+        <v>82</v>
+      </c>
       <c r="L23" s="0" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="24"/>
+      <c r="A24" s="5"/>
       <c r="B24" s="14" t="n">
         <v>20</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D24" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E24" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L24</f>
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="F24" s="13" t="n">
         <f aca="false">E24+D24-1</f>
-        <v>46346</v>
+        <v>46353</v>
       </c>
       <c r="G24" s="12" t="s">
         <v>29</v>
@@ -8630,33 +8782,31 @@
         <v>25</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="K24" s="25" t="s">
-        <v>80</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="K24" s="12"/>
       <c r="L24" s="0" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="24"/>
+      <c r="A25" s="5"/>
       <c r="B25" s="9" t="n">
         <v>21</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L25</f>
-        <v>46347</v>
+        <v>46354</v>
       </c>
       <c r="F25" s="8" t="n">
         <f aca="false">E25+D25-1</f>
-        <v>46348</v>
+        <v>46354</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>29</v>
@@ -8668,69 +8818,71 @@
         <v>25</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>83</v>
+        <v>86</v>
+      </c>
+      <c r="K25" s="26" t="s">
+        <v>87</v>
       </c>
       <c r="L25" s="0" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="24"/>
-      <c r="B26" s="14" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="5"/>
+      <c r="B26" s="18" t="n">
         <v>22</v>
       </c>
-      <c r="C26" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="13" t="n">
+      <c r="C26" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E26" s="17" t="n">
         <f aca="false">说明与修订!$B$5+L26</f>
-        <v>46347</v>
-      </c>
-      <c r="F26" s="13" t="n">
+        <v>46354</v>
+      </c>
+      <c r="F26" s="17" t="n">
         <f aca="false">E26+D26-1</f>
-        <v>46347</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="K26" s="12"/>
+        <v>46355</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="H26" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="K26" s="16" t="s">
+        <v>92</v>
+      </c>
       <c r="L26" s="0" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24"/>
+      <c r="A27" s="5"/>
       <c r="B27" s="9" t="n">
         <v>23</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="D27" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E27" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L27</f>
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="F27" s="8" t="n">
         <f aca="false">E27+D27-1</f>
-        <v>46348</v>
+        <v>46355</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>29</v>
@@ -8742,31 +8894,31 @@
         <v>25</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="0" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="24"/>
+      <c r="A28" s="5"/>
       <c r="B28" s="14" t="n">
         <v>24</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="D28" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E28" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L28</f>
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="F28" s="13" t="n">
         <f aca="false">E28+D28-1</f>
-        <v>46349</v>
+        <v>46356</v>
       </c>
       <c r="G28" s="12" t="s">
         <v>29</v>
@@ -8778,35 +8930,31 @@
         <v>25</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>90</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="K28" s="12"/>
       <c r="L28" s="0" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="5" t="s">
-        <v>91</v>
-      </c>
+      <c r="A29" s="5"/>
       <c r="B29" s="9" t="n">
         <v>25</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E29" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L29</f>
-        <v>46350</v>
+        <v>46356</v>
       </c>
       <c r="F29" s="8" t="n">
         <f aca="false">E29+D29-1</f>
-        <v>46350</v>
+        <v>46356</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>29</v>
@@ -8818,11 +8966,11 @@
         <v>25</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="0" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8831,18 +8979,18 @@
         <v>26</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E30" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L30</f>
-        <v>46351</v>
+        <v>46357</v>
       </c>
       <c r="F30" s="13" t="n">
         <f aca="false">E30+D30-1</f>
-        <v>46352</v>
+        <v>46357</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>29</v>
@@ -8854,33 +9002,35 @@
         <v>25</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="K30" s="12" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="L30" s="0" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="5"/>
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="5" t="s">
+        <v>102</v>
+      </c>
       <c r="B31" s="9" t="n">
         <v>27</v>
       </c>
-      <c r="C31" s="7" t="s">
-        <v>97</v>
+      <c r="C31" s="26" t="s">
+        <v>103</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L31</f>
-        <v>46351</v>
+        <v>46358</v>
       </c>
       <c r="F31" s="8" t="n">
         <f aca="false">E31+D31-1</f>
-        <v>46351</v>
+        <v>46359</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>29</v>
@@ -8892,49 +9042,49 @@
         <v>25</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="0" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
       <c r="B32" s="14" t="n">
         <v>28</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>99</v>
+      <c r="C32" s="25" t="s">
+        <v>105</v>
       </c>
       <c r="D32" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E32" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L32</f>
-        <v>46352</v>
+        <v>46359</v>
       </c>
       <c r="F32" s="13" t="n">
         <f aca="false">E32+D32-1</f>
-        <v>46352</v>
+        <v>46359</v>
       </c>
       <c r="G32" s="12" t="s">
         <v>29</v>
       </c>
       <c r="H32" s="14" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I32" s="14" t="s">
         <v>25</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K32" s="12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="L32" s="0" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8943,110 +9093,108 @@
         <v>29</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D33" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E33" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L33</f>
-        <v>46353</v>
+        <v>46360</v>
       </c>
       <c r="F33" s="8" t="n">
         <f aca="false">E33+D33-1</f>
-        <v>46353</v>
+        <v>46360</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I33" s="9" t="s">
         <v>25</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="0" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
-      <c r="B34" s="14" t="n">
+      <c r="B34" s="18" t="n">
         <v>30</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D34" s="14" t="n">
+      <c r="C34" s="16" t="s">
+        <v>110</v>
+      </c>
+      <c r="D34" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <f aca="false">说明与修订!$B$5+L34</f>
+        <v>46361</v>
+      </c>
+      <c r="F34" s="17" t="n">
+        <f aca="false">E34+D34-1</f>
+        <v>46362</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="K34" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="L34" s="0" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="5"/>
+      <c r="B35" s="9" t="n">
+        <v>31</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D35" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="E34" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+L34</f>
-        <v>46354</v>
-      </c>
-      <c r="F34" s="13" t="n">
-        <f aca="false">E34+D34-1</f>
-        <v>46354</v>
-      </c>
-      <c r="G34" s="12" t="s">
+      <c r="E35" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L35</f>
+        <v>46361</v>
+      </c>
+      <c r="F35" s="8" t="n">
+        <f aca="false">E35+D35-1</f>
+        <v>46361</v>
+      </c>
+      <c r="G35" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H34" s="14" t="s">
+      <c r="H35" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I34" s="14" t="s">
+      <c r="I35" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="J34" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="K34" s="25" t="s">
-        <v>106</v>
-      </c>
-      <c r="L34" s="0" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="52.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="5"/>
-      <c r="B35" s="22" t="n">
-        <v>31</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="D35" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E35" s="21" t="n">
-        <f aca="false">说明与修订!$B$5+L35</f>
-        <v>46354</v>
-      </c>
-      <c r="F35" s="21" t="n">
-        <f aca="false">E35+D35-1</f>
-        <v>46355</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="H35" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J35" s="20" t="s">
-        <v>110</v>
-      </c>
-      <c r="K35" s="20" t="s">
-        <v>111</v>
-      </c>
+      <c r="J35" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="K35" s="7"/>
       <c r="L35" s="0" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9055,18 +9203,18 @@
         <v>32</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D36" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E36" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L36</f>
-        <v>46355</v>
+        <v>46363</v>
       </c>
       <c r="F36" s="13" t="n">
         <f aca="false">E36+D36-1</f>
-        <v>46355</v>
+        <v>46363</v>
       </c>
       <c r="G36" s="12" t="s">
         <v>29</v>
@@ -9078,159 +9226,163 @@
         <v>25</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="K36" s="12"/>
       <c r="L36" s="0" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
-      <c r="B37" s="9" t="n">
+      <c r="B37" s="22" t="n">
         <v>33</v>
       </c>
-      <c r="C37" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="8" t="n">
+      <c r="C37" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" s="21" t="n">
         <f aca="false">说明与修订!$B$5+L37</f>
-        <v>46356</v>
-      </c>
-      <c r="F37" s="8" t="n">
+        <v>46363</v>
+      </c>
+      <c r="F37" s="21" t="n">
         <f aca="false">E37+D37-1</f>
-        <v>46356</v>
-      </c>
-      <c r="G37" s="7" t="s">
+        <v>46364</v>
+      </c>
+      <c r="G37" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="H37" s="9" t="s">
+      <c r="H37" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="I37" s="9" t="s">
+      <c r="I37" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="J37" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="K37" s="7"/>
+      <c r="J37" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="K37" s="20" t="s">
+        <v>119</v>
+      </c>
       <c r="L37" s="0" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
-      <c r="B38" s="14" t="n">
+      <c r="B38" s="18" t="n">
         <v>34</v>
       </c>
-      <c r="C38" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="D38" s="14" t="n">
+      <c r="C38" s="16" t="s">
+        <v>120</v>
+      </c>
+      <c r="D38" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="17" t="n">
         <f aca="false">说明与修订!$B$5+L38</f>
-        <v>46356</v>
-      </c>
-      <c r="F38" s="13" t="n">
+        <v>46364</v>
+      </c>
+      <c r="F38" s="17" t="n">
         <f aca="false">E38+D38-1</f>
-        <v>46356</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H38" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J38" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="K38" s="12"/>
+        <v>46364</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="I38" s="27" t="s">
+        <v>121</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="K38" s="16" t="s">
+        <v>123</v>
+      </c>
       <c r="L38" s="0" t="n">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
       <c r="B39" s="9" t="n">
         <v>35</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D39" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E39" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L39</f>
-        <v>46357</v>
+        <v>46365</v>
       </c>
       <c r="F39" s="8" t="n">
         <f aca="false">E39+D39-1</f>
-        <v>46357</v>
+        <v>46365</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I39" s="9" t="s">
         <v>25</v>
       </c>
       <c r="J39" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="K39" s="7" t="s">
-        <v>120</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="K39" s="7"/>
       <c r="L39" s="0" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B40" s="14" t="n">
         <v>36</v>
       </c>
-      <c r="C40" s="25" t="s">
-        <v>122</v>
+      <c r="C40" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E40" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L40</f>
-        <v>46358</v>
+        <v>46366</v>
       </c>
       <c r="F40" s="13" t="n">
         <f aca="false">E40+D40-1</f>
-        <v>46359</v>
+        <v>46385</v>
       </c>
       <c r="G40" s="12" t="s">
         <v>29</v>
       </c>
       <c r="H40" s="14" t="s">
-        <v>17</v>
+        <v>128</v>
       </c>
       <c r="I40" s="14" t="s">
         <v>25</v>
       </c>
       <c r="J40" s="12" t="s">
-        <v>123</v>
-      </c>
-      <c r="K40" s="12"/>
+        <v>129</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>130</v>
+      </c>
       <c r="L40" s="0" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9238,22 +9390,22 @@
       <c r="B41" s="9" t="n">
         <v>37</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>124</v>
+      <c r="C41" s="7" t="s">
+        <v>131</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="E41" s="8" t="n">
         <f aca="false">说明与修订!$B$5+L41</f>
-        <v>46359</v>
+        <v>46366</v>
       </c>
       <c r="F41" s="8" t="n">
         <f aca="false">E41+D41-1</f>
-        <v>46359</v>
+        <v>46455</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="H41" s="9" t="s">
         <v>17</v>
@@ -9262,33 +9414,33 @@
         <v>25</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="K41" s="7" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="L41" s="0" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
       <c r="B42" s="14" t="n">
         <v>38</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D42" s="14" t="n">
         <v>1</v>
       </c>
       <c r="E42" s="13" t="n">
         <f aca="false">说明与修订!$B$5+L42</f>
-        <v>46360</v>
+        <v>46456</v>
       </c>
       <c r="F42" s="13" t="n">
         <f aca="false">E42+D42-1</f>
-        <v>46360</v>
+        <v>46456</v>
       </c>
       <c r="G42" s="12" t="s">
         <v>17</v>
@@ -9300,419 +9452,83 @@
         <v>25</v>
       </c>
       <c r="J42" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="K42" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="L42" s="0" t="n">
         <v>128</v>
-      </c>
-      <c r="K42" s="12"/>
-      <c r="L42" s="0" t="n">
-        <v>32</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
-      <c r="B43" s="22" t="n">
+      <c r="B43" s="9" t="n">
         <v>39</v>
       </c>
-      <c r="C43" s="20" t="s">
+      <c r="C43" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <f aca="false">说明与修订!$B$5+L43</f>
+        <v>46457</v>
+      </c>
+      <c r="F43" s="8" t="n">
+        <f aca="false">E43+D43-1</f>
+        <v>46821</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I43" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="K43" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="L43" s="0" t="n">
         <v>129</v>
       </c>
-      <c r="D43" s="22" t="n">
-        <v>2</v>
-      </c>
-      <c r="E43" s="21" t="n">
-        <f aca="false">说明与修订!$B$5+L43</f>
-        <v>46361</v>
-      </c>
-      <c r="F43" s="21" t="n">
-        <f aca="false">E43+D43-1</f>
-        <v>46362</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H43" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I43" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="J43" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="K43" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="L43" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="5"/>
-      <c r="B44" s="14" t="n">
-        <v>40</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>132</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+L44</f>
-        <v>46361</v>
-      </c>
-      <c r="F44" s="13" t="n">
-        <f aca="false">E44+D44-1</f>
-        <v>46361</v>
-      </c>
-      <c r="G44" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H44" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I44" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="12" t="s">
-        <v>133</v>
-      </c>
-      <c r="K44" s="12"/>
-      <c r="L44" s="0" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="5"/>
-      <c r="B45" s="9" t="n">
-        <v>41</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="D45" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+L45</f>
-        <v>46363</v>
-      </c>
-      <c r="F45" s="8" t="n">
-        <f aca="false">E45+D45-1</f>
-        <v>46363</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I45" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J45" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="K45" s="7"/>
-      <c r="L45" s="0" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="5"/>
-      <c r="B46" s="18" t="n">
-        <v>42</v>
-      </c>
-      <c r="C46" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="D46" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <f aca="false">说明与修订!$B$5+L46</f>
-        <v>46363</v>
-      </c>
-      <c r="F46" s="17" t="n">
-        <f aca="false">E46+D46-1</f>
-        <v>46364</v>
-      </c>
-      <c r="G46" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="H46" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="J46" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="K46" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="L46" s="0" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="5"/>
-      <c r="B47" s="22" t="n">
-        <v>43</v>
-      </c>
-      <c r="C47" s="20" t="s">
-        <v>139</v>
-      </c>
-      <c r="D47" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="21" t="n">
-        <f aca="false">说明与修订!$B$5+L47</f>
-        <v>46364</v>
-      </c>
-      <c r="F47" s="21" t="n">
-        <f aca="false">E47+D47-1</f>
-        <v>46364</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" s="22" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="27" t="s">
+    </row>
+    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="J47" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="K47" s="20" t="s">
-        <v>142</v>
-      </c>
-      <c r="L47" s="0" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="5"/>
-      <c r="B48" s="14" t="n">
-        <v>44</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>143</v>
-      </c>
-      <c r="D48" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+L48</f>
-        <v>46365</v>
-      </c>
-      <c r="F48" s="13" t="n">
-        <f aca="false">E48+D48-1</f>
-        <v>46365</v>
-      </c>
-      <c r="G48" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H48" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I48" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J48" s="12" t="s">
-        <v>144</v>
-      </c>
-      <c r="K48" s="12"/>
-      <c r="L48" s="0" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="B49" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="C49" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="D49" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+L49</f>
-        <v>46366</v>
-      </c>
-      <c r="F49" s="8" t="n">
-        <f aca="false">E49+D49-1</f>
-        <v>46385</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="H49" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="I49" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J49" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="K49" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="L49" s="0" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="5"/>
-      <c r="B50" s="14" t="n">
-        <v>46</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="D50" s="14" t="n">
-        <v>90</v>
-      </c>
-      <c r="E50" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+L50</f>
-        <v>46366</v>
-      </c>
-      <c r="F50" s="13" t="n">
-        <f aca="false">E50+D50-1</f>
-        <v>46455</v>
-      </c>
-      <c r="G50" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="H50" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="I50" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J50" s="12" t="s">
-        <v>151</v>
-      </c>
-      <c r="K50" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="L50" s="0" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="5"/>
-      <c r="B51" s="9" t="n">
-        <v>47</v>
-      </c>
-      <c r="C51" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="D51" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <f aca="false">说明与修订!$B$5+L51</f>
-        <v>46456</v>
-      </c>
-      <c r="F51" s="8" t="n">
-        <f aca="false">E51+D51-1</f>
-        <v>46456</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H51" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="I51" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="J51" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="K51" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="L51" s="0" t="n">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="5"/>
-      <c r="B52" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="D52" s="14" t="n">
-        <v>365</v>
-      </c>
-      <c r="E52" s="13" t="n">
-        <f aca="false">说明与修订!$B$5+L52</f>
-        <v>46457</v>
-      </c>
-      <c r="F52" s="13" t="n">
-        <f aca="false">E52+D52-1</f>
-        <v>46821</v>
-      </c>
-      <c r="G52" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="H52" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="I52" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="J52" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="K52" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="L52" s="0" t="n">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="29"/>
-      <c r="F53" s="29"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="29"/>
-      <c r="I53" s="29"/>
-      <c r="J53" s="29"/>
-      <c r="K53" s="29"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29"/>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29"/>
+      <c r="J44" s="29"/>
+      <c r="K44" s="29"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K52"/>
+  <autoFilter ref="A4:K43"/>
   <mergeCells count="9">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A6:A13"/>
-    <mergeCell ref="A14:A28"/>
-    <mergeCell ref="A29:A39"/>
-    <mergeCell ref="A40:A48"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A20:A30"/>
+    <mergeCell ref="A31:A39"/>
+    <mergeCell ref="A40:A43"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I5:I52" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="I5:I43" type="list">
       <formula1>"未开始,进行中,已完成,受阻,待客户确认,待确认"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9733,7 +9549,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:X51"/>
+  <dimension ref="A1:X42"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -9745,7 +9561,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>160</v>
+        <v>141</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
@@ -9782,7 +9598,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="31" t="s">
-        <v>161</v>
+        <v>142</v>
       </c>
       <c r="E2" s="32" t="str">
         <f aca="false">TEXT(说明与修订!$B$5+7*0,"mm/dd")</f>
@@ -9873,7 +9689,7 @@
         <v>14</v>
       </c>
       <c r="C3" s="35" t="s">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="D3" s="33" t="n">
         <v>2</v>
@@ -9907,7 +9723,7 @@
         <v>21</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>163</v>
+        <v>144</v>
       </c>
       <c r="D4" s="33" t="n">
         <v>2</v>
@@ -9941,7 +9757,7 @@
         <v>21</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>164</v>
+        <v>145</v>
       </c>
       <c r="D5" s="33" t="n">
         <v>1</v>
@@ -9975,7 +9791,7 @@
         <v>21</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>165</v>
+        <v>146</v>
       </c>
       <c r="D6" s="33" t="n">
         <v>1</v>
@@ -10009,7 +9825,7 @@
         <v>21</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>166</v>
+        <v>147</v>
       </c>
       <c r="D7" s="33" t="n">
         <v>2</v>
@@ -10043,7 +9859,7 @@
         <v>21</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="D8" s="33" t="n">
         <v>4</v>
@@ -10077,7 +9893,7 @@
         <v>21</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>168</v>
+        <v>149</v>
       </c>
       <c r="D9" s="33" t="n">
         <v>3</v>
@@ -10111,7 +9927,7 @@
         <v>21</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="D10" s="33" t="n">
         <v>1</v>
@@ -10176,10 +9992,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="39" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>171</v>
+        <v>152</v>
       </c>
       <c r="D12" s="33" t="n">
         <v>2</v>
@@ -10210,10 +10026,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="39" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>172</v>
+        <v>153</v>
       </c>
       <c r="D13" s="33" t="n">
         <v>2</v>
@@ -10244,13 +10060,13 @@
         <v>12</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="D14" s="33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" s="37"/>
       <c r="F14" s="37"/>
@@ -10278,13 +10094,13 @@
         <v>13</v>
       </c>
       <c r="B15" s="39" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D15" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="37"/>
       <c r="F15" s="37"/>
@@ -10312,10 +10128,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="39" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="D16" s="33" t="n">
         <v>1</v>
@@ -10346,18 +10162,18 @@
         <v>15</v>
       </c>
       <c r="B17" s="39" t="s">
-        <v>170</v>
+        <v>151</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>66</v>
+        <v>157</v>
       </c>
       <c r="D17" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="37"/>
       <c r="F17" s="37"/>
       <c r="G17" s="40"/>
-      <c r="H17" s="37"/>
+      <c r="H17" s="40"/>
       <c r="I17" s="37"/>
       <c r="J17" s="37"/>
       <c r="K17" s="37"/>
@@ -10379,19 +10195,19 @@
       <c r="A18" s="33" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="39" t="s">
-        <v>170</v>
+      <c r="B18" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="D18" s="33" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="37"/>
       <c r="F18" s="37"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="37"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="37"/>
       <c r="J18" s="37"/>
       <c r="K18" s="37"/>
@@ -10413,19 +10229,19 @@
       <c r="A19" s="33" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="39" t="s">
-        <v>170</v>
+      <c r="B19" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D19" s="33" t="n">
         <v>2</v>
       </c>
       <c r="E19" s="37"/>
       <c r="F19" s="37"/>
-      <c r="G19" s="40"/>
-      <c r="H19" s="37"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="41"/>
       <c r="I19" s="37"/>
       <c r="J19" s="37"/>
       <c r="K19" s="37"/>
@@ -10447,19 +10263,19 @@
       <c r="A20" s="33" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="39" t="s">
-        <v>170</v>
+      <c r="B20" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>74</v>
+        <v>159</v>
       </c>
       <c r="D20" s="33" t="n">
         <v>1</v>
       </c>
       <c r="E20" s="37"/>
       <c r="F20" s="37"/>
-      <c r="G20" s="40"/>
-      <c r="H20" s="37"/>
+      <c r="G20" s="37"/>
+      <c r="H20" s="41"/>
       <c r="I20" s="37"/>
       <c r="J20" s="37"/>
       <c r="K20" s="37"/>
@@ -10481,19 +10297,19 @@
       <c r="A21" s="33" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="39" t="s">
-        <v>170</v>
+      <c r="B21" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>176</v>
+        <v>80</v>
       </c>
       <c r="D21" s="33" t="n">
         <v>1</v>
       </c>
       <c r="E21" s="37"/>
       <c r="F21" s="37"/>
-      <c r="G21" s="40"/>
-      <c r="H21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="41"/>
       <c r="I21" s="37"/>
       <c r="J21" s="37"/>
       <c r="K21" s="37"/>
@@ -10515,19 +10331,19 @@
       <c r="A22" s="33" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="39" t="s">
-        <v>170</v>
+      <c r="B22" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D22" s="33" t="n">
         <v>1</v>
       </c>
       <c r="E22" s="37"/>
       <c r="F22" s="37"/>
-      <c r="G22" s="40"/>
-      <c r="H22" s="37"/>
+      <c r="G22" s="37"/>
+      <c r="H22" s="41"/>
       <c r="I22" s="37"/>
       <c r="J22" s="37"/>
       <c r="K22" s="37"/>
@@ -10549,19 +10365,19 @@
       <c r="A23" s="33" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="39" t="s">
-        <v>170</v>
+      <c r="B23" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>177</v>
+        <v>85</v>
       </c>
       <c r="D23" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="37"/>
       <c r="F23" s="37"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="37"/>
+      <c r="G23" s="37"/>
+      <c r="H23" s="41"/>
       <c r="I23" s="37"/>
       <c r="J23" s="37"/>
       <c r="K23" s="37"/>
@@ -10583,19 +10399,19 @@
       <c r="A24" s="33" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="39" t="s">
-        <v>170</v>
+      <c r="B24" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D24" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="37"/>
       <c r="F24" s="37"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="37"/>
+      <c r="G24" s="37"/>
+      <c r="H24" s="41"/>
       <c r="I24" s="37"/>
       <c r="J24" s="37"/>
       <c r="K24" s="37"/>
@@ -10617,19 +10433,19 @@
       <c r="A25" s="33" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="39" t="s">
-        <v>170</v>
+      <c r="B25" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="D25" s="33" t="n">
         <v>1</v>
       </c>
       <c r="E25" s="37"/>
       <c r="F25" s="37"/>
-      <c r="G25" s="40"/>
-      <c r="H25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="41"/>
       <c r="I25" s="37"/>
       <c r="J25" s="37"/>
       <c r="K25" s="37"/>
@@ -10651,11 +10467,11 @@
       <c r="A26" s="33" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="39" t="s">
-        <v>170</v>
+      <c r="B26" s="34" t="s">
+        <v>72</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="D26" s="33" t="n">
         <v>1</v>
@@ -10663,8 +10479,8 @@
       <c r="E26" s="37"/>
       <c r="F26" s="37"/>
       <c r="G26" s="37"/>
-      <c r="H26" s="40"/>
-      <c r="I26" s="37"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="41"/>
       <c r="J26" s="37"/>
       <c r="K26" s="37"/>
       <c r="L26" s="37"/>
@@ -10686,10 +10502,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="34" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C27" s="35" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="D27" s="33" t="n">
         <v>1</v>
@@ -10697,8 +10513,8 @@
       <c r="E27" s="37"/>
       <c r="F27" s="37"/>
       <c r="G27" s="37"/>
-      <c r="H27" s="41"/>
-      <c r="I27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="41"/>
       <c r="J27" s="37"/>
       <c r="K27" s="37"/>
       <c r="L27" s="37"/>
@@ -10720,19 +10536,19 @@
         <v>26</v>
       </c>
       <c r="B28" s="34" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="D28" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E28" s="37"/>
       <c r="F28" s="37"/>
       <c r="G28" s="37"/>
-      <c r="H28" s="41"/>
-      <c r="I28" s="37"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="41"/>
       <c r="J28" s="37"/>
       <c r="K28" s="37"/>
       <c r="L28" s="37"/>
@@ -10754,19 +10570,19 @@
         <v>27</v>
       </c>
       <c r="B29" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>181</v>
+        <v>102</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>164</v>
       </c>
       <c r="D29" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="37"/>
       <c r="F29" s="37"/>
       <c r="G29" s="37"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="37"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="43"/>
       <c r="J29" s="37"/>
       <c r="K29" s="37"/>
       <c r="L29" s="37"/>
@@ -10788,10 +10604,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" s="35" t="s">
-        <v>99</v>
+        <v>102</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>165</v>
       </c>
       <c r="D30" s="33" t="n">
         <v>1</v>
@@ -10799,8 +10615,8 @@
       <c r="E30" s="37"/>
       <c r="F30" s="37"/>
       <c r="G30" s="37"/>
-      <c r="H30" s="41"/>
-      <c r="I30" s="37"/>
+      <c r="H30" s="37"/>
+      <c r="I30" s="43"/>
       <c r="J30" s="37"/>
       <c r="K30" s="37"/>
       <c r="L30" s="37"/>
@@ -10822,10 +10638,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="D31" s="33" t="n">
         <v>1</v>
@@ -10833,8 +10649,8 @@
       <c r="E31" s="37"/>
       <c r="F31" s="37"/>
       <c r="G31" s="37"/>
-      <c r="H31" s="41"/>
-      <c r="I31" s="37"/>
+      <c r="H31" s="37"/>
+      <c r="I31" s="43"/>
       <c r="J31" s="37"/>
       <c r="K31" s="37"/>
       <c r="L31" s="37"/>
@@ -10856,19 +10672,19 @@
         <v>30</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="D32" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="37"/>
       <c r="F32" s="37"/>
       <c r="G32" s="37"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="37"/>
+      <c r="H32" s="37"/>
+      <c r="I32" s="43"/>
       <c r="J32" s="37"/>
       <c r="K32" s="37"/>
       <c r="L32" s="37"/>
@@ -10890,19 +10706,19 @@
         <v>31</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="D33" s="33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E33" s="37"/>
       <c r="F33" s="37"/>
       <c r="G33" s="37"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="43"/>
       <c r="J33" s="37"/>
       <c r="K33" s="37"/>
       <c r="L33" s="37"/>
@@ -10924,10 +10740,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="D34" s="33" t="n">
         <v>1</v>
@@ -10935,9 +10751,9 @@
       <c r="E34" s="37"/>
       <c r="F34" s="37"/>
       <c r="G34" s="37"/>
-      <c r="H34" s="41"/>
+      <c r="H34" s="37"/>
       <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
+      <c r="J34" s="43"/>
       <c r="K34" s="37"/>
       <c r="L34" s="37"/>
       <c r="M34" s="37"/>
@@ -10958,20 +10774,20 @@
         <v>33</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>183</v>
+        <v>117</v>
       </c>
       <c r="D35" s="33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="37"/>
       <c r="F35" s="37"/>
       <c r="G35" s="37"/>
       <c r="H35" s="37"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="43"/>
       <c r="K35" s="37"/>
       <c r="L35" s="37"/>
       <c r="M35" s="37"/>
@@ -10992,10 +10808,10 @@
         <v>34</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>184</v>
+        <v>120</v>
       </c>
       <c r="D36" s="33" t="n">
         <v>1</v>
@@ -11004,8 +10820,8 @@
       <c r="F36" s="37"/>
       <c r="G36" s="37"/>
       <c r="H36" s="37"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="43"/>
       <c r="K36" s="37"/>
       <c r="L36" s="37"/>
       <c r="M36" s="37"/>
@@ -11026,10 +10842,10 @@
         <v>35</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>185</v>
+        <v>124</v>
       </c>
       <c r="D37" s="33" t="n">
         <v>1</v>
@@ -11038,8 +10854,8 @@
       <c r="F37" s="37"/>
       <c r="G37" s="37"/>
       <c r="H37" s="37"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="43"/>
       <c r="K37" s="37"/>
       <c r="L37" s="37"/>
       <c r="M37" s="37"/>
@@ -11060,23 +10876,23 @@
         <v>36</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C38" s="42" t="s">
-        <v>186</v>
+        <v>126</v>
+      </c>
+      <c r="C38" s="35" t="s">
+        <v>168</v>
       </c>
       <c r="D38" s="33" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="E38" s="37"/>
       <c r="F38" s="37"/>
       <c r="G38" s="37"/>
       <c r="H38" s="37"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="37"/>
-      <c r="K38" s="37"/>
-      <c r="L38" s="37"/>
-      <c r="M38" s="37"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="44"/>
+      <c r="K38" s="44"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="44"/>
       <c r="N38" s="37"/>
       <c r="O38" s="37"/>
       <c r="P38" s="37"/>
@@ -11094,33 +10910,33 @@
         <v>37</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C39" s="42" t="s">
-        <v>187</v>
+        <v>126</v>
+      </c>
+      <c r="C39" s="35" t="s">
+        <v>131</v>
       </c>
       <c r="D39" s="33" t="n">
-        <v>1</v>
+        <v>90</v>
       </c>
       <c r="E39" s="37"/>
       <c r="F39" s="37"/>
       <c r="G39" s="37"/>
       <c r="H39" s="37"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="37"/>
-      <c r="K39" s="37"/>
-      <c r="L39" s="37"/>
-      <c r="M39" s="37"/>
-      <c r="N39" s="37"/>
-      <c r="O39" s="37"/>
-      <c r="P39" s="37"/>
-      <c r="Q39" s="37"/>
-      <c r="R39" s="37"/>
-      <c r="S39" s="37"/>
-      <c r="T39" s="37"/>
-      <c r="U39" s="37"/>
-      <c r="V39" s="37"/>
-      <c r="W39" s="37"/>
+      <c r="I39" s="37"/>
+      <c r="J39" s="44"/>
+      <c r="K39" s="44"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
+      <c r="O39" s="44"/>
+      <c r="P39" s="44"/>
+      <c r="Q39" s="44"/>
+      <c r="R39" s="44"/>
+      <c r="S39" s="44"/>
+      <c r="T39" s="44"/>
+      <c r="U39" s="44"/>
+      <c r="V39" s="44"/>
+      <c r="W39" s="44"/>
       <c r="X39" s="37"/>
     </row>
     <row r="40" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11128,10 +10944,10 @@
         <v>38</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D40" s="33" t="n">
         <v>1</v>
@@ -11140,7 +10956,7 @@
       <c r="F40" s="37"/>
       <c r="G40" s="37"/>
       <c r="H40" s="37"/>
-      <c r="I40" s="43"/>
+      <c r="I40" s="37"/>
       <c r="J40" s="37"/>
       <c r="K40" s="37"/>
       <c r="L40" s="37"/>
@@ -11154,318 +10970,12 @@
       <c r="T40" s="37"/>
       <c r="U40" s="37"/>
       <c r="V40" s="37"/>
-      <c r="W40" s="37"/>
+      <c r="W40" s="44"/>
       <c r="X40" s="37"/>
     </row>
-    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="33" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>188</v>
-      </c>
-      <c r="D41" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E41" s="37"/>
-      <c r="F41" s="37"/>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="37"/>
-      <c r="K41" s="37"/>
-      <c r="L41" s="37"/>
-      <c r="M41" s="37"/>
-      <c r="N41" s="37"/>
-      <c r="O41" s="37"/>
-      <c r="P41" s="37"/>
-      <c r="Q41" s="37"/>
-      <c r="R41" s="37"/>
-      <c r="S41" s="37"/>
-      <c r="T41" s="37"/>
-      <c r="U41" s="37"/>
-      <c r="V41" s="37"/>
-      <c r="W41" s="37"/>
-      <c r="X41" s="37"/>
-    </row>
-    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="33" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C42" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D42" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" s="37"/>
-      <c r="F42" s="37"/>
-      <c r="G42" s="37"/>
-      <c r="H42" s="37"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="37"/>
-      <c r="K42" s="37"/>
-      <c r="L42" s="37"/>
-      <c r="M42" s="37"/>
-      <c r="N42" s="37"/>
-      <c r="O42" s="37"/>
-      <c r="P42" s="37"/>
-      <c r="Q42" s="37"/>
-      <c r="R42" s="37"/>
-      <c r="S42" s="37"/>
-      <c r="T42" s="37"/>
-      <c r="U42" s="37"/>
-      <c r="V42" s="37"/>
-      <c r="W42" s="37"/>
-      <c r="X42" s="37"/>
-    </row>
-    <row r="43" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="33" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C43" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="D43" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="37"/>
-      <c r="F43" s="37"/>
-      <c r="G43" s="37"/>
-      <c r="H43" s="37"/>
-      <c r="I43" s="37"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="37"/>
-      <c r="L43" s="37"/>
-      <c r="M43" s="37"/>
-      <c r="N43" s="37"/>
-      <c r="O43" s="37"/>
-      <c r="P43" s="37"/>
-      <c r="Q43" s="37"/>
-      <c r="R43" s="37"/>
-      <c r="S43" s="37"/>
-      <c r="T43" s="37"/>
-      <c r="U43" s="37"/>
-      <c r="V43" s="37"/>
-      <c r="W43" s="37"/>
-      <c r="X43" s="37"/>
-    </row>
-    <row r="44" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="33" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C44" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="D44" s="33" t="n">
-        <v>2</v>
-      </c>
-      <c r="E44" s="37"/>
-      <c r="F44" s="37"/>
-      <c r="G44" s="37"/>
-      <c r="H44" s="37"/>
-      <c r="I44" s="37"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="37"/>
-      <c r="L44" s="37"/>
-      <c r="M44" s="37"/>
-      <c r="N44" s="37"/>
-      <c r="O44" s="37"/>
-      <c r="P44" s="37"/>
-      <c r="Q44" s="37"/>
-      <c r="R44" s="37"/>
-      <c r="S44" s="37"/>
-      <c r="T44" s="37"/>
-      <c r="U44" s="37"/>
-      <c r="V44" s="37"/>
-      <c r="W44" s="37"/>
-      <c r="X44" s="37"/>
-    </row>
-    <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="33" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C45" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="D45" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" s="37"/>
-      <c r="F45" s="37"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="37"/>
-      <c r="I45" s="37"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="37"/>
-      <c r="L45" s="37"/>
-      <c r="M45" s="37"/>
-      <c r="N45" s="37"/>
-      <c r="O45" s="37"/>
-      <c r="P45" s="37"/>
-      <c r="Q45" s="37"/>
-      <c r="R45" s="37"/>
-      <c r="S45" s="37"/>
-      <c r="T45" s="37"/>
-      <c r="U45" s="37"/>
-      <c r="V45" s="37"/>
-      <c r="W45" s="37"/>
-      <c r="X45" s="37"/>
-    </row>
-    <row r="46" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="33" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="C46" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="D46" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37"/>
-      <c r="H46" s="37"/>
-      <c r="I46" s="37"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="37"/>
-      <c r="L46" s="37"/>
-      <c r="M46" s="37"/>
-      <c r="N46" s="37"/>
-      <c r="O46" s="37"/>
-      <c r="P46" s="37"/>
-      <c r="Q46" s="37"/>
-      <c r="R46" s="37"/>
-      <c r="S46" s="37"/>
-      <c r="T46" s="37"/>
-      <c r="U46" s="37"/>
-      <c r="V46" s="37"/>
-      <c r="W46" s="37"/>
-      <c r="X46" s="37"/>
-    </row>
-    <row r="47" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="33" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="C47" s="35" t="s">
-        <v>190</v>
-      </c>
-      <c r="D47" s="33" t="n">
-        <v>20</v>
-      </c>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="44"/>
-      <c r="K47" s="44"/>
-      <c r="L47" s="44"/>
-      <c r="M47" s="44"/>
-      <c r="N47" s="37"/>
-      <c r="O47" s="37"/>
-      <c r="P47" s="37"/>
-      <c r="Q47" s="37"/>
-      <c r="R47" s="37"/>
-      <c r="S47" s="37"/>
-      <c r="T47" s="37"/>
-      <c r="U47" s="37"/>
-      <c r="V47" s="37"/>
-      <c r="W47" s="37"/>
-      <c r="X47" s="37"/>
-    </row>
-    <row r="48" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="33" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="C48" s="35" t="s">
-        <v>150</v>
-      </c>
-      <c r="D48" s="33" t="n">
-        <v>90</v>
-      </c>
-      <c r="E48" s="37"/>
-      <c r="F48" s="37"/>
-      <c r="G48" s="37"/>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="44"/>
-      <c r="L48" s="44"/>
-      <c r="M48" s="44"/>
-      <c r="N48" s="44"/>
-      <c r="O48" s="44"/>
-      <c r="P48" s="44"/>
-      <c r="Q48" s="44"/>
-      <c r="R48" s="44"/>
-      <c r="S48" s="44"/>
-      <c r="T48" s="44"/>
-      <c r="U48" s="44"/>
-      <c r="V48" s="44"/>
-      <c r="W48" s="44"/>
-      <c r="X48" s="37"/>
-    </row>
-    <row r="49" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="33" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="34" t="s">
-        <v>145</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="D49" s="33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" s="37"/>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37"/>
-      <c r="H49" s="37"/>
-      <c r="I49" s="37"/>
-      <c r="J49" s="37"/>
-      <c r="K49" s="37"/>
-      <c r="L49" s="37"/>
-      <c r="M49" s="37"/>
-      <c r="N49" s="37"/>
-      <c r="O49" s="37"/>
-      <c r="P49" s="37"/>
-      <c r="Q49" s="37"/>
-      <c r="R49" s="37"/>
-      <c r="S49" s="37"/>
-      <c r="T49" s="37"/>
-      <c r="U49" s="37"/>
-      <c r="V49" s="37"/>
-      <c r="W49" s="44"/>
-      <c r="X49" s="37"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="45" t="s">
-        <v>191</v>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="45" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -11504,7 +11014,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="46" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="B1" s="46"/>
       <c r="C1" s="46"/>
@@ -11519,507 +11029,507 @@
     </row>
     <row r="2" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>193</v>
+        <v>171</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>194</v>
+        <v>172</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>195</v>
+        <v>173</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>196</v>
+        <v>174</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>197</v>
+        <v>175</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>200</v>
+        <v>178</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>202</v>
+        <v>180</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="48" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="B3" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D3" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F3" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G3" s="50" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H3" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I3" s="50" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J3" s="50"/>
       <c r="K3" s="50"/>
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="51" t="s">
-        <v>208</v>
+        <v>186</v>
       </c>
       <c r="B4" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C4" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E4" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F4" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G4" s="53" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H4" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I4" s="53" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J4" s="53"/>
       <c r="K4" s="53"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="48" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="B5" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C5" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D5" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F5" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G5" s="50" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H5" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I5" s="50" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J5" s="50"/>
       <c r="K5" s="50"/>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="51" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="B6" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C6" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E6" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F6" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G6" s="53" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H6" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I6" s="53" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J6" s="53"/>
       <c r="K6" s="53"/>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="48" t="s">
-        <v>211</v>
+        <v>189</v>
       </c>
       <c r="B7" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D7" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E7" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F7" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G7" s="50" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H7" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I7" s="50" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J7" s="50"/>
       <c r="K7" s="50"/>
     </row>
     <row r="8" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="51" t="s">
-        <v>212</v>
+        <v>190</v>
       </c>
       <c r="B8" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C8" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E8" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F8" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G8" s="53" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H8" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I8" s="53" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J8" s="53"/>
       <c r="K8" s="53"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="48" t="s">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="B9" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D9" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E9" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F9" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G9" s="50" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H9" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I9" s="50" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J9" s="50"/>
       <c r="K9" s="50"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="51" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="B10" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C10" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E10" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F10" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G10" s="53" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H10" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I10" s="53" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J10" s="53"/>
       <c r="K10" s="53"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="48" t="s">
-        <v>215</v>
+        <v>193</v>
       </c>
       <c r="B11" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D11" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E11" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F11" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G11" s="50" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H11" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I11" s="50" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J11" s="50"/>
       <c r="K11" s="50"/>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="51" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="B12" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C12" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G12" s="53" t="s">
-        <v>206</v>
+        <v>184</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I12" s="53" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="J12" s="53"/>
       <c r="K12" s="53"/>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="48" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B13" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C13" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D13" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E13" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="H13" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I13" s="55" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="J13" s="50"/>
       <c r="K13" s="50"/>
     </row>
     <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="51" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B14" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C14" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E14" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F14" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G14" s="54" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="H14" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I14" s="55" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="J14" s="53"/>
       <c r="K14" s="53"/>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="48" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="B15" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C15" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D15" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E15" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G15" s="54" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="H15" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I15" s="55" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="J15" s="50"/>
       <c r="K15" s="50"/>
     </row>
     <row r="16" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="51" t="s">
-        <v>222</v>
+        <v>200</v>
       </c>
       <c r="B16" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C16" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E16" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F16" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G16" s="54" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="H16" s="52" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I16" s="55" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="J16" s="53"/>
       <c r="K16" s="53"/>
     </row>
     <row r="17" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="48" t="s">
-        <v>223</v>
+        <v>201</v>
       </c>
       <c r="B17" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="D17" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="E17" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="H17" s="49" t="s">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I17" s="55" t="s">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="J17" s="50"/>
       <c r="K17" s="50"/>
     </row>
     <row r="19" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="56" t="s">
-        <v>224</v>
+        <v>202</v>
       </c>
       <c r="B19" s="56"/>
       <c r="C19" s="56"/>
@@ -12068,7 +11578,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="57" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="B1" s="57"/>
       <c r="C1" s="57"/>
@@ -12084,36 +11594,36 @@
         <v>4</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>226</v>
+        <v>204</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>227</v>
+        <v>205</v>
       </c>
       <c r="D2" s="58" t="s">
-        <v>228</v>
+        <v>206</v>
       </c>
       <c r="E2" s="58" t="s">
-        <v>229</v>
+        <v>207</v>
       </c>
       <c r="F2" s="58" t="s">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="G2" s="58" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="H2" s="58" t="s">
-        <v>232</v>
+        <v>210</v>
       </c>
       <c r="I2" s="58" t="s">
-        <v>233</v>
+        <v>211</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="59" t="s">
-        <v>234</v>
+        <v>212</v>
       </c>
       <c r="B3" s="60" t="s">
-        <v>235</v>
+        <v>213</v>
       </c>
       <c r="C3" s="60"/>
       <c r="D3" s="60"/>
@@ -12128,16 +11638,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>236</v>
+        <v>214</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>237</v>
+        <v>215</v>
       </c>
       <c r="D4" s="26" t="s">
-        <v>238</v>
+        <v>216</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F4" s="9" t="n">
         <v>1</v>
@@ -12146,7 +11656,7 @@
         <v>30</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I4" s="7"/>
     </row>
@@ -12155,16 +11665,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>241</v>
+        <v>219</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>242</v>
+        <v>220</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F5" s="9" t="n">
         <v>1</v>
@@ -12173,7 +11683,7 @@
         <v>30</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I5" s="7"/>
     </row>
@@ -12182,16 +11692,16 @@
         <v>3</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>245</v>
+        <v>223</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>1</v>
@@ -12200,7 +11710,7 @@
         <v>30</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I6" s="7"/>
     </row>
@@ -12209,16 +11719,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F7" s="9" t="n">
         <v>1</v>
@@ -12227,7 +11737,7 @@
         <v>30</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I7" s="7"/>
     </row>
@@ -12236,16 +11746,16 @@
         <v>5</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>250</v>
+        <v>228</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>251</v>
+        <v>229</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F8" s="9" t="n">
         <v>1</v>
@@ -12254,7 +11764,7 @@
         <v>30</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I8" s="7"/>
     </row>
@@ -12263,28 +11773,28 @@
         <v>6</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>253</v>
+        <v>231</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>254</v>
+        <v>232</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F9" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>257</v>
+        <v>235</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12292,16 +11802,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>258</v>
+        <v>236</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>259</v>
+        <v>237</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>260</v>
+        <v>238</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F10" s="9" t="n">
         <v>1</v>
@@ -12310,16 +11820,16 @@
         <v>30</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="59" t="s">
-        <v>261</v>
+        <v>239</v>
       </c>
       <c r="B11" s="60" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="C11" s="60"/>
       <c r="D11" s="60"/>
@@ -12334,7 +11844,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -12349,28 +11859,28 @@
         <v>1.1</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F13" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="H13" s="61" t="s">
-        <v>267</v>
+        <v>245</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12378,28 +11888,28 @@
         <v>2</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F14" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="H14" s="62" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12407,25 +11917,25 @@
         <v>4</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I15" s="7"/>
     </row>
@@ -12434,23 +11944,23 @@
         <v>5</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="D16" s="7"/>
       <c r="E16" s="9" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="F16" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -12459,32 +11969,32 @@
         <v>6</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="D17" s="7"/>
       <c r="E17" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F17" s="9" t="n">
         <v>15</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>256</v>
+        <v>234</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>240</v>
+        <v>218</v>
       </c>
       <c r="I17" s="7"/>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="59" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="B18" s="60" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
@@ -12499,14 +12009,14 @@
         <v>1</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>284</v>
+        <v>262</v>
       </c>
       <c r="D19" s="7"/>
       <c r="E19" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F19" s="9" t="n">
         <v>1</v>
@@ -12515,7 +12025,7 @@
         <v>30</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I19" s="7"/>
     </row>
@@ -12524,14 +12034,14 @@
         <v>2</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="D20" s="7"/>
       <c r="E20" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F20" s="9" t="n">
         <v>1</v>
@@ -12540,10 +12050,10 @@
         <v>30</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>288</v>
+        <v>266</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12551,14 +12061,14 @@
         <v>3</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>289</v>
+        <v>267</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>290</v>
+        <v>268</v>
       </c>
       <c r="D21" s="7"/>
       <c r="E21" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F21" s="9" t="n">
         <v>1</v>
@@ -12567,7 +12077,7 @@
         <v>30</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I21" s="7"/>
     </row>
@@ -12576,14 +12086,14 @@
         <v>4</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>291</v>
+        <v>269</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>292</v>
+        <v>270</v>
       </c>
       <c r="D22" s="7"/>
       <c r="E22" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F22" s="9" t="n">
         <v>1</v>
@@ -12592,7 +12102,7 @@
         <v>30</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I22" s="7"/>
     </row>
@@ -12601,14 +12111,14 @@
         <v>5</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>293</v>
+        <v>271</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="D23" s="7"/>
       <c r="E23" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F23" s="9" t="n">
         <v>1</v>
@@ -12617,7 +12127,7 @@
         <v>30</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I23" s="7"/>
     </row>
@@ -12626,14 +12136,14 @@
         <v>6</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="D24" s="7"/>
       <c r="E24" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F24" s="9" t="n">
         <v>1</v>
@@ -12642,7 +12152,7 @@
         <v>30</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I24" s="7"/>
     </row>
@@ -12651,14 +12161,14 @@
         <v>7</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>297</v>
+        <v>275</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="D25" s="7"/>
       <c r="E25" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F25" s="9" t="n">
         <v>1</v>
@@ -12667,7 +12177,7 @@
         <v>30</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I25" s="7"/>
     </row>
@@ -12676,14 +12186,14 @@
         <v>8</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>300</v>
+        <v>278</v>
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F26" s="9" t="n">
         <v>1</v>
@@ -12692,7 +12202,7 @@
         <v>30</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I26" s="7"/>
     </row>
@@ -12701,12 +12211,12 @@
         <v>9</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F27" s="9" t="n">
         <v>1</v>
@@ -12715,7 +12225,7 @@
         <v>30</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I27" s="7"/>
     </row>
@@ -12724,14 +12234,14 @@
         <v>9.1</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>303</v>
+        <v>281</v>
       </c>
       <c r="D28" s="7"/>
       <c r="E28" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F28" s="9" t="n">
         <v>5</v>
@@ -12740,10 +12250,10 @@
         <v>30</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>304</v>
+        <v>282</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12751,14 +12261,14 @@
         <v>9.2</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>305</v>
+        <v>283</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>306</v>
+        <v>284</v>
       </c>
       <c r="D29" s="7"/>
       <c r="E29" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F29" s="9" t="n">
         <v>1</v>
@@ -12767,10 +12277,10 @@
         <v>30</v>
       </c>
       <c r="H29" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="I29" s="26" t="s">
         <v>285</v>
-      </c>
-      <c r="I29" s="26" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12778,14 +12288,14 @@
         <v>9.3</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>308</v>
+        <v>286</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="D30" s="7"/>
       <c r="E30" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F30" s="9" t="n">
         <v>1</v>
@@ -12794,7 +12304,7 @@
         <v>30</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I30" s="7"/>
     </row>
@@ -12803,14 +12313,14 @@
         <v>9.4</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>310</v>
+        <v>288</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="D31" s="7"/>
       <c r="E31" s="9" t="s">
-        <v>247</v>
+        <v>225</v>
       </c>
       <c r="F31" s="9" t="n">
         <v>2</v>
@@ -12819,7 +12329,7 @@
         <v>30</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>285</v>
+        <v>263</v>
       </c>
       <c r="I31" s="7"/>
     </row>
@@ -12842,7 +12352,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C57"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -12852,187 +12362,187 @@
   <sheetData>
     <row r="1" customFormat="false" ht="37.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="30" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="B1" s="30"/>
       <c r="C1" s="30"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="63" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="64" t="s">
-        <v>314</v>
+        <v>292</v>
       </c>
       <c r="B4" s="64" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="C4" s="64" t="s">
-        <v>316</v>
+        <v>294</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="65" t="s">
-        <v>317</v>
+        <v>295</v>
       </c>
       <c r="B5" s="66" t="n">
         <v>46328</v>
       </c>
       <c r="C5" s="65" t="s">
-        <v>318</v>
+        <v>296</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="65" t="s">
-        <v>319</v>
+        <v>297</v>
       </c>
       <c r="B6" s="65" t="n">
-        <f aca="false">MAX(计划!F5:F48)-MIN(计划!E5:E48)+1</f>
+        <f aca="false">MAX(计划!F5:F39)-MIN(计划!E5:E39)+1</f>
         <v>38</v>
       </c>
       <c r="C6" s="65" t="s">
-        <v>320</v>
+        <v>298</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="65" t="s">
-        <v>321</v>
+        <v>299</v>
       </c>
       <c r="B7" s="65" t="n">
         <v>90</v>
       </c>
       <c r="C7" s="65" t="s">
-        <v>322</v>
+        <v>300</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="65" t="s">
-        <v>323</v>
+        <v>301</v>
       </c>
       <c r="B8" s="67" t="s">
-        <v>324</v>
+        <v>302</v>
       </c>
       <c r="C8" s="65" t="s">
-        <v>325</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="63" t="s">
-        <v>326</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="58" t="s">
-        <v>327</v>
+        <v>305</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>328</v>
+        <v>306</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>329</v>
+        <v>307</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="65" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="B12" s="68" t="n">
         <f aca="false">计划!F5</f>
         <v>46329</v>
       </c>
       <c r="C12" s="65" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="65" t="s">
-        <v>332</v>
+        <v>310</v>
       </c>
       <c r="B13" s="68" t="n">
         <f aca="false">计划!F7</f>
         <v>46332</v>
       </c>
       <c r="C13" s="65" t="s">
-        <v>333</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="67" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="B14" s="68" t="n">
         <f aca="false">计划!F15</f>
         <v>46341</v>
       </c>
       <c r="C14" s="67" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="67" t="s">
-        <v>336</v>
+        <v>314</v>
       </c>
       <c r="B15" s="68" t="n">
-        <f aca="false">计划!F28</f>
+        <f aca="false">计划!F19</f>
         <v>46349</v>
       </c>
       <c r="C15" s="65" t="s">
-        <v>337</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="65" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="B16" s="68" t="n">
-        <f aca="false">计划!F39</f>
+        <f aca="false">计划!F30</f>
         <v>46357</v>
       </c>
       <c r="C16" s="65" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="65" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="B17" s="68" t="n">
-        <f aca="false">计划!F43</f>
+        <f aca="false">计划!F34</f>
         <v>46362</v>
       </c>
       <c r="C17" s="65" t="s">
-        <v>341</v>
+        <v>319</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="65" t="s">
-        <v>342</v>
+        <v>320</v>
       </c>
       <c r="B18" s="68" t="n">
-        <f aca="false">计划!F48</f>
+        <f aca="false">计划!F39</f>
         <v>46365</v>
       </c>
       <c r="C18" s="65" t="s">
-        <v>343</v>
+        <v>321</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="65" t="s">
-        <v>344</v>
+        <v>322</v>
       </c>
       <c r="B19" s="68" t="n">
-        <f aca="false">计划!F51</f>
+        <f aca="false">计划!F42</f>
         <v>46456</v>
       </c>
       <c r="C19" s="65" t="s">
-        <v>345</v>
+        <v>323</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="63" t="s">
-        <v>346</v>
+        <v>324</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -13040,10 +12550,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="58" t="s">
-        <v>347</v>
+        <v>325</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>348</v>
+        <v>326</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13051,10 +12561,10 @@
         <v>1</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="C23" s="70" t="s">
-        <v>350</v>
+        <v>328</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13062,10 +12572,10 @@
         <v>2</v>
       </c>
       <c r="B24" s="70" t="s">
-        <v>351</v>
+        <v>329</v>
       </c>
       <c r="C24" s="70" t="s">
-        <v>352</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13073,10 +12583,10 @@
         <v>3</v>
       </c>
       <c r="B25" s="70" t="s">
-        <v>353</v>
+        <v>331</v>
       </c>
       <c r="C25" s="70" t="s">
-        <v>354</v>
+        <v>332</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13084,10 +12594,10 @@
         <v>4</v>
       </c>
       <c r="B26" s="70" t="s">
-        <v>355</v>
+        <v>333</v>
       </c>
       <c r="C26" s="70" t="s">
-        <v>356</v>
+        <v>334</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13095,10 +12605,10 @@
         <v>5</v>
       </c>
       <c r="B27" s="70" t="s">
-        <v>357</v>
+        <v>335</v>
       </c>
       <c r="C27" s="70" t="s">
-        <v>358</v>
+        <v>336</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13106,10 +12616,10 @@
         <v>6</v>
       </c>
       <c r="B28" s="70" t="s">
-        <v>359</v>
+        <v>337</v>
       </c>
       <c r="C28" s="70" t="s">
-        <v>360</v>
+        <v>338</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13117,10 +12627,10 @@
         <v>7</v>
       </c>
       <c r="B29" s="70" t="s">
-        <v>361</v>
+        <v>339</v>
       </c>
       <c r="C29" s="70" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13128,10 +12638,10 @@
         <v>8</v>
       </c>
       <c r="B30" s="70" t="s">
-        <v>363</v>
+        <v>341</v>
       </c>
       <c r="C30" s="70" t="s">
-        <v>364</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13139,10 +12649,10 @@
         <v>9</v>
       </c>
       <c r="B31" s="70" t="s">
-        <v>365</v>
+        <v>343</v>
       </c>
       <c r="C31" s="70" t="s">
-        <v>366</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13150,10 +12660,10 @@
         <v>10</v>
       </c>
       <c r="B32" s="70" t="s">
-        <v>367</v>
+        <v>345</v>
       </c>
       <c r="C32" s="70" t="s">
-        <v>368</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13161,10 +12671,10 @@
         <v>11</v>
       </c>
       <c r="B33" s="70" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="C33" s="70" t="s">
-        <v>370</v>
+        <v>348</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13172,10 +12682,10 @@
         <v>12</v>
       </c>
       <c r="B34" s="70" t="s">
-        <v>371</v>
+        <v>349</v>
       </c>
       <c r="C34" s="70" t="s">
-        <v>372</v>
+        <v>350</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13183,10 +12693,10 @@
         <v>13</v>
       </c>
       <c r="B35" s="70" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="C35" s="70" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13194,10 +12704,10 @@
         <v>14</v>
       </c>
       <c r="B36" s="70" t="s">
-        <v>375</v>
+        <v>353</v>
       </c>
       <c r="C36" s="70" t="s">
-        <v>376</v>
+        <v>354</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13205,10 +12715,10 @@
         <v>15</v>
       </c>
       <c r="B37" s="70" t="s">
-        <v>377</v>
+        <v>355</v>
       </c>
       <c r="C37" s="70" t="s">
-        <v>378</v>
+        <v>356</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13216,10 +12726,10 @@
         <v>16</v>
       </c>
       <c r="B38" s="70" t="s">
-        <v>379</v>
+        <v>357</v>
       </c>
       <c r="C38" s="70" t="s">
-        <v>380</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13227,135 +12737,146 @@
         <v>17</v>
       </c>
       <c r="B39" s="70" t="s">
-        <v>381</v>
+        <v>359</v>
       </c>
       <c r="C39" s="70" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="63" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="71" t="s">
-        <v>384</v>
-      </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+        <v>360</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="70" t="n">
+        <v>18</v>
+      </c>
+      <c r="B40" s="70" t="s">
+        <v>361</v>
+      </c>
+      <c r="C40" s="70" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="63" t="s">
+        <v>363</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="71" t="s">
-        <v>385</v>
+        <v>364</v>
       </c>
       <c r="B43" s="71"/>
       <c r="C43" s="71"/>
     </row>
     <row r="44" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="71" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="B44" s="71"/>
       <c r="C44" s="71"/>
     </row>
     <row r="45" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="71" t="s">
-        <v>387</v>
+        <v>366</v>
       </c>
       <c r="B45" s="71"/>
       <c r="C45" s="71"/>
     </row>
     <row r="46" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="71" t="s">
-        <v>388</v>
+        <v>367</v>
       </c>
       <c r="B46" s="71"/>
       <c r="C46" s="71"/>
     </row>
     <row r="47" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="71" t="s">
-        <v>389</v>
+        <v>368</v>
       </c>
       <c r="B47" s="71"/>
       <c r="C47" s="71"/>
     </row>
     <row r="48" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="71" t="s">
-        <v>390</v>
+        <v>369</v>
       </c>
       <c r="B48" s="71"/>
       <c r="C48" s="71"/>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="63" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="72"/>
-      <c r="B51" s="65" t="s">
+    <row r="49" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="71" t="s">
+        <v>370</v>
+      </c>
+      <c r="B49" s="71"/>
+      <c r="C49" s="71"/>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="63" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="72"/>
+      <c r="B52" s="65" t="s">
         <v>14</v>
       </c>
-      <c r="C51" s="73" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="74"/>
-      <c r="B52" s="65" t="s">
+      <c r="C52" s="73" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="74"/>
+      <c r="B53" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="C52" s="73" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="75"/>
-      <c r="B53" s="67" t="s">
-        <v>394</v>
-      </c>
       <c r="C53" s="73" t="s">
-        <v>395</v>
+        <v>373</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="76"/>
-      <c r="B54" s="65" t="s">
-        <v>91</v>
+      <c r="A54" s="75"/>
+      <c r="B54" s="67" t="s">
+        <v>374</v>
       </c>
       <c r="C54" s="73" t="s">
-        <v>396</v>
+        <v>375</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="77"/>
+      <c r="A55" s="76"/>
       <c r="B55" s="65" t="s">
-        <v>121</v>
-      </c>
-      <c r="C55" s="78" t="s">
-        <v>397</v>
+        <v>72</v>
+      </c>
+      <c r="C55" s="73" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="79"/>
+      <c r="A56" s="77"/>
       <c r="B56" s="65" t="s">
-        <v>145</v>
-      </c>
-      <c r="C56" s="73" t="s">
-        <v>398</v>
+        <v>102</v>
+      </c>
+      <c r="C56" s="78" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="79"/>
+      <c r="B57" s="65" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" s="73" t="s">
+        <v>378</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A42:C42"/>
     <mergeCell ref="A43:C43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
     <mergeCell ref="A47:C47"/>
     <mergeCell ref="A48:C48"/>
+    <mergeCell ref="A49:C49"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.3" right="0.3" top="0.4" bottom="0.4" header="0.511811023622047" footer="0.511811023622047"/>
